--- a/BSMA_Master_Coding_Sheet.xlsx
+++ b/BSMA_Master_Coding_Sheet.xlsx
@@ -501,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ100"/>
+  <dimension ref="A1:AZ96"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.25" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="10.5625" customWidth="1" style="12" min="1" max="2"/>
@@ -846,7 +846,7 @@
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>BSMA0001.1.1</t>
+          <t>BSMA0001.1.2</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
@@ -910,7 +910,7 @@
       <c r="Y4" s="8" t="n">
         <v>999</v>
       </c>
-      <c r="Z4" s="10" t="inlineStr">
+      <c r="Z4" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve"> employees of business
 organizations in various industries, including manufacturing, telecommunication, and
@@ -942,7 +942,7 @@
         </is>
       </c>
       <c r="AH4" s="8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AI4" s="8" t="n">
         <v>1</v>
@@ -962,7 +962,7 @@
       </c>
       <c r="AM4" s="8" t="inlineStr">
         <is>
-          <t>Chen et al. (2001)</t>
+          <t>Tepper (2000), Peng et al. (2014)</t>
         </is>
       </c>
       <c r="AO4" s="10" t="inlineStr">
@@ -982,361 +982,311 @@
       </c>
       <c r="AS4" s="8" t="inlineStr">
         <is>
-          <t>Subordinate's self-efficacy</t>
+          <t>Abusive Supervision</t>
         </is>
       </c>
       <c r="AT4" s="8" t="n">
-        <v>5.19</v>
+        <v>2.02</v>
       </c>
       <c r="AU4" s="8" t="n">
-        <v>0.77</v>
+        <v>1.09</v>
       </c>
       <c r="AV4" s="8" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="AW4" s="8" t="n">
-        <v>0.38</v>
+        <v>-0.57</v>
       </c>
     </row>
-    <row r="5" ht="15.75" customHeight="1" s="12">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>BSMA0001</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>BSMA0001.1</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>BSMA0001.1.2</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>1 = Include</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t>Drawing on the job demands–resources model, we suggest and test a motivational mechanism that underlies the relationship between leader boundary-spanning behavior and employee voice behavior. Based on the field survey data of 383 leader-employee pairs collected from various organizations in South Korea, the results of our mediation model showed that leader boundary-spanning behavior, as a potential job resource, enhances employee voice behavior by increasing employee self-efficacy. The results of our moderated mediation model also showed that the focal leader’s abusive supervision, as a potential job demand, could attenuate the beneficial effect of leader boundary-spanning behavior on employee voice behavior by diminishing employee self-efficacy. These findings highlight the importance of leader boundary-spanning behavior in enhancing employee voice behavior, the roles of employee self-efficacy as a key mediating mechanism, and the focal leader’s abusive supervision as a preventable boundary condition within these relationships. Theoretical and practical implications are discussed.</t>
-        </is>
-      </c>
-      <c r="H5" s="8" t="inlineStr">
-        <is>
-          <t>Leader Boundary-Spanning Behavior and Employee Voice Behavior: The Job Demands–Resources Perspective</t>
-        </is>
-      </c>
-      <c r="I5" s="8" t="inlineStr">
-        <is>
-          <t>Behavioral Sciences</t>
-        </is>
-      </c>
-      <c r="J5" s="8" t="inlineStr">
-        <is>
-          <t>Lee, J., Choi, D., &amp; Cheong, M.</t>
-        </is>
-      </c>
-      <c r="K5" s="8" t="n">
-        <v>2023</v>
-      </c>
-      <c r="L5" s="8" t="inlineStr">
+    <row r="5" ht="15.75" customHeight="1" s="12"/>
+    <row r="6" ht="15.75" customHeight="1" s="12">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>BSMA0002</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>BSMA0002.1</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>BSMA0002.1.1</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2 = Non-employee samples</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Comacchio, A., Bonesso, S., &amp; Pizzi, C.</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>2011</v>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>1 = Journal article</t>
         </is>
       </c>
-      <c r="Q5" s="8" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>1 = Cross-sectional</t>
         </is>
       </c>
-      <c r="S5" s="8" t="inlineStr">
-        <is>
-          <t>South Korea</t>
-        </is>
-      </c>
-      <c r="U5" s="8" t="inlineStr">
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
         <is>
           <t>1 = No (domestic only)</t>
         </is>
       </c>
-      <c r="V5" s="8" t="n">
-        <v>383</v>
-      </c>
-      <c r="W5" s="8" t="n">
-        <v>43.4</v>
-      </c>
-      <c r="X5" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="Y5" s="8" t="n">
+      <c r="V6" t="n">
+        <v>65</v>
+      </c>
+      <c r="W6" t="n">
         <v>999</v>
       </c>
-      <c r="Z5" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> employees of business
-organizations in various industries, including manufacturing, telecommunication, and
-service sectors</t>
-        </is>
-      </c>
-      <c r="AA5" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="AB5" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC5" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD5" s="8" t="inlineStr">
-        <is>
-          <t>3 = Others (e.g. coworker/peer subordinate customer/client)</t>
-        </is>
-      </c>
-      <c r="AE5" s="8" t="inlineStr">
-        <is>
-          <t>employees (subordinate)</t>
-        </is>
-      </c>
-      <c r="AF5" s="8" t="inlineStr">
-        <is>
-          <t>Marrone et al. (2007)</t>
-        </is>
-      </c>
-      <c r="AH5" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="AI5" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ5" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="AK5" s="8" t="inlineStr">
-        <is>
-          <t>3 = Others (e.g. coworker/peer subordinate customer/client)</t>
-        </is>
-      </c>
-      <c r="AL5" s="8" t="inlineStr">
-        <is>
-          <t>employees (subordinate)</t>
-        </is>
-      </c>
-      <c r="AM5" s="8" t="inlineStr">
-        <is>
-          <t>Tepper (2000), Peng et al. (2014)</t>
-        </is>
-      </c>
-      <c r="AO5" s="10" t="inlineStr">
-        <is>
-          <t>Leader Boundary-Spanning
-Behavior</t>
-        </is>
-      </c>
-      <c r="AP5" s="8" t="n">
-        <v>5.31</v>
-      </c>
-      <c r="AQ5" s="8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AR5" s="8" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="AS5" s="8" t="inlineStr">
-        <is>
-          <t>Abusive Supervision</t>
-        </is>
-      </c>
-      <c r="AT5" s="8" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AU5" s="8" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AV5" s="8" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="AW5" s="8" t="n">
-        <v>-0.57</v>
+      <c r="X6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>directors of technology transfer centres</t>
+        </is>
+      </c>
+      <c r="AA6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>1 = Self</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>The survey asked the Centres to indicate the universities they have engaged in joint projects. We coded this information into a dichotomous variable that takes the value 1 if the TTC has indicated at least one university, otherwise the variable takes the value 0.</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>999</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>1 = Self</t>
+        </is>
+      </c>
+      <c r="AM6" t="n">
+        <v>999</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Boundary spanning role</t>
+        </is>
+      </c>
+      <c r="AP6" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>999</v>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>Internal qualified human capital</t>
+        </is>
+      </c>
+      <c r="AT6" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>999</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0.354</v>
       </c>
     </row>
-    <row r="6" ht="15.75" customHeight="1" s="12">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>ALL</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>BSMA0001</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="inlineStr">
-        <is>
-          <t>BSMA0001.1</t>
-        </is>
-      </c>
-      <c r="D6" s="8" t="inlineStr">
-        <is>
-          <t>BSMA0001.1.3</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>1 = Include</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="n"/>
-      <c r="G6" s="8" t="inlineStr">
-        <is>
-          <t>Drawing on the job demands–resources model, we suggest and test a motivational mechanism that underlies the relationship between leader boundary-spanning behavior and employee voice behavior. Based on the field survey data of 383 leader-employee pairs collected from various organizations in South Korea, the results of our mediation model showed that leader boundary-spanning behavior, as a potential job resource, enhances employee voice behavior by increasing employee self-efficacy. The results of our moderated mediation model also showed that the focal leader’s abusive supervision, as a potential job demand, could attenuate the beneficial effect of leader boundary-spanning behavior on employee voice behavior by diminishing employee self-efficacy. These findings highlight the importance of leader boundary-spanning behavior in enhancing employee voice behavior, the roles of employee self-efficacy as a key mediating mechanism, and the focal leader’s abusive supervision as a preventable boundary condition within these relationships. Theoretical and practical implications are discussed.</t>
-        </is>
-      </c>
-      <c r="H6" s="8" t="inlineStr">
-        <is>
-          <t>Leader Boundary-Spanning Behavior and Employee Voice Behavior: The Job Demands–Resources Perspective</t>
-        </is>
-      </c>
-      <c r="I6" s="8" t="inlineStr">
-        <is>
-          <t>Behavioral Sciences</t>
-        </is>
-      </c>
-      <c r="J6" s="8" t="inlineStr">
-        <is>
-          <t>Lee, J., Choi, D., &amp; Cheong, M.</t>
-        </is>
-      </c>
-      <c r="K6" s="8" t="n">
-        <v>2023</v>
-      </c>
-      <c r="L6" s="8" t="inlineStr">
+    <row r="7" ht="15.75" customHeight="1" s="12">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>BSMA0002</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>BSMA0002.1</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>BSMA0002.1.2</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2 = Non-employee samples</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Comacchio, A., Bonesso, S., &amp; Pizzi, C.</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>2011</v>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>1 = Journal article</t>
         </is>
       </c>
-      <c r="Q6" s="9" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>1 = Cross-sectional</t>
         </is>
       </c>
-      <c r="S6" s="8" t="inlineStr">
-        <is>
-          <t>South Korea</t>
-        </is>
-      </c>
-      <c r="U6" s="9" t="inlineStr">
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
         <is>
           <t>1 = No (domestic only)</t>
         </is>
       </c>
-      <c r="V6" s="8" t="n">
-        <v>383</v>
-      </c>
-      <c r="W6" s="8" t="n">
-        <v>43.4</v>
-      </c>
-      <c r="X6" s="8" t="n">
-        <v>19</v>
-      </c>
-      <c r="Y6" s="8" t="n">
+      <c r="V7" t="n">
+        <v>65</v>
+      </c>
+      <c r="W7" t="n">
         <v>999</v>
       </c>
-      <c r="Z6" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> employees of business
-organizations in various industries, including manufacturing, telecommunication, and
-service sectors</t>
-        </is>
-      </c>
-      <c r="AA6" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="AB6" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC6" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD6" s="8" t="inlineStr">
-        <is>
-          <t>3 = Others (e.g. coworker/peer subordinate customer/client)</t>
-        </is>
-      </c>
-      <c r="AE6" s="8" t="inlineStr">
-        <is>
-          <t>employees (subordinate)</t>
-        </is>
-      </c>
-      <c r="AF6" s="8" t="inlineStr">
-        <is>
-          <t>Marrone et al. (2007)</t>
-        </is>
-      </c>
-      <c r="AH6" s="8" t="n">
-        <v>6</v>
-      </c>
-      <c r="AI6" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ6" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="AK6" s="8" t="inlineStr">
+      <c r="X7" t="n">
+        <v>999</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>directors of technology transfer centres</t>
+        </is>
+      </c>
+      <c r="AA7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD7" t="inlineStr">
         <is>
           <t>1 = Self</t>
         </is>
       </c>
-      <c r="AL6" s="8" t="n">
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>The survey asked the Centres to indicate the universities they have engaged in joint projects. We coded this information into a dichotomous variable that takes the value 1 if the TTC has indicated at least one university, otherwise the variable takes the value 0.</t>
+        </is>
+      </c>
+      <c r="AH7" t="n">
         <v>999</v>
       </c>
-      <c r="AM6" s="8" t="inlineStr">
-        <is>
-          <t>Van Dyne and LePine (1998)</t>
-        </is>
-      </c>
-      <c r="AO6" s="10" t="inlineStr">
-        <is>
-          <t>Leader Boundary-Spanning
-Behavior</t>
-        </is>
-      </c>
-      <c r="AP6" s="8" t="n">
-        <v>5.31</v>
-      </c>
-      <c r="AQ6" s="8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AR6" s="8" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="AS6" s="8" t="inlineStr">
-        <is>
-          <t>Subordinate's voice behavior</t>
-        </is>
-      </c>
-      <c r="AT6" s="8" t="n">
-        <v>4.77</v>
-      </c>
-      <c r="AU6" s="8" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="AV6" s="8" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="AW6" s="8" t="n">
-        <v>0.14</v>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>175</v>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>1 = Self</t>
+        </is>
+      </c>
+      <c r="AM7" t="n">
+        <v>999</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Boundary spanning role</t>
+        </is>
+      </c>
+      <c r="AP7" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>999</v>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>External human capital</t>
+        </is>
+      </c>
+      <c r="AT7" t="n">
+        <v>10.04</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>30.31</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>999</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0.423</v>
       </c>
     </row>
-    <row r="7" ht="15.75" customHeight="1" s="12"/>
     <row r="8" ht="15.75" customHeight="1" s="12">
       <c r="A8" t="inlineStr">
         <is>
@@ -1355,7 +1305,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>BSMA0002.1.1</t>
+          <t>BSMA0002.1.3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1465,20 +1415,20 @@
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>Internal qualified human capital</t>
+          <t>Research activities</t>
         </is>
       </c>
       <c r="AT8" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.27</v>
+        <v>0.5</v>
       </c>
       <c r="AV8" t="n">
         <v>999</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.354</v>
+        <v>0.419</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1" s="12">
@@ -1499,7 +1449,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>BSMA0002.1.2</t>
+          <t>BSMA0002.1.4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1583,7 +1533,7 @@
         <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>175</v>
+        <v>10</v>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
@@ -1609,20 +1559,20 @@
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>External human capital</t>
+          <t>Partners for joint projects</t>
         </is>
       </c>
       <c r="AT9" t="n">
-        <v>10.04</v>
+        <v>1.61</v>
       </c>
       <c r="AU9" t="n">
-        <v>30.31</v>
+        <v>1.99</v>
       </c>
       <c r="AV9" t="n">
         <v>999</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.423</v>
+        <v>0.362</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1" s="12">
@@ -1643,7 +1593,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>BSMA0002.1.3</t>
+          <t>BSMA0002.1.5</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1702,13 +1652,13 @@
         </is>
       </c>
       <c r="AA10" t="n">
-        <v>1</v>
+        <v>999</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="AC10" t="n">
-        <v>1</v>
+        <v>999</v>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
@@ -1724,10 +1674,10 @@
         <v>999</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1</v>
+        <v>133</v>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
@@ -1753,20 +1703,20 @@
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>Research activities</t>
+          <t>Age</t>
         </is>
       </c>
       <c r="AT10" t="n">
-        <v>0.58</v>
+        <v>19.32</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.5</v>
+        <v>20.48</v>
       </c>
       <c r="AV10" t="n">
         <v>999</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.419</v>
+        <v>-0.103</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1" s="12">
@@ -1787,7 +1737,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>BSMA0002.1.4</t>
+          <t>BSMA0002.1.6</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1846,13 +1796,13 @@
         </is>
       </c>
       <c r="AA11" t="n">
-        <v>1</v>
+        <v>999</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="AC11" t="n">
-        <v>1</v>
+        <v>999</v>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
@@ -1871,7 +1821,7 @@
         <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>10</v>
+        <v>262</v>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
@@ -1897,20 +1847,20 @@
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>Partners for joint projects</t>
+          <t>Size</t>
         </is>
       </c>
       <c r="AT11" t="n">
-        <v>1.61</v>
+        <v>18.07</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.99</v>
+        <v>36.61</v>
       </c>
       <c r="AV11" t="n">
         <v>999</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.362</v>
+        <v>0.108</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1" s="12">
@@ -1931,7 +1881,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>BSMA0002.1.5</t>
+          <t>BSMA0002.1.7</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1990,13 +1940,13 @@
         </is>
       </c>
       <c r="AA12" t="n">
-        <v>999</v>
+        <v>1</v>
       </c>
       <c r="AB12" t="n">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>999</v>
+        <v>1</v>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
@@ -2012,10 +1962,10 @@
         <v>999</v>
       </c>
       <c r="AI12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>133</v>
+        <v>1</v>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
@@ -2041,166 +1991,23 @@
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>Age</t>
+          <t>MHT sectors</t>
         </is>
       </c>
       <c r="AT12" t="n">
-        <v>19.32</v>
+        <v>0.45</v>
       </c>
       <c r="AU12" t="n">
-        <v>20.48</v>
+        <v>0.35</v>
       </c>
       <c r="AV12" t="n">
         <v>999</v>
       </c>
       <c r="AW12" t="n">
-        <v>-0.103</v>
+        <v>-0.095</v>
       </c>
     </row>
-    <row r="13" ht="15.75" customHeight="1" s="12">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>KY</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>BSMA0002</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>BSMA0002.1</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>BSMA0002.1.6</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0 = Exclude</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2 = Non-employee samples</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Comacchio, A., Bonesso, S., &amp; Pizzi, C.</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>2011</v>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>1 = Journal article</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>1 = Cross-sectional</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>Italy</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>1 = No (domestic only)</t>
-        </is>
-      </c>
-      <c r="V13" t="n">
-        <v>65</v>
-      </c>
-      <c r="W13" t="n">
-        <v>999</v>
-      </c>
-      <c r="X13" t="n">
-        <v>999</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>999</v>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>directors of technology transfer centres</t>
-        </is>
-      </c>
-      <c r="AA13" t="n">
-        <v>999</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>999</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>999</v>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>1 = Self</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>The survey asked the Centres to indicate the universities they have engaged in joint projects. We coded this information into a dichotomous variable that takes the value 1 if the TTC has indicated at least one university, otherwise the variable takes the value 0.</t>
-        </is>
-      </c>
-      <c r="AH13" t="n">
-        <v>999</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>262</v>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>1 = Self</t>
-        </is>
-      </c>
-      <c r="AM13" t="n">
-        <v>999</v>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Boundary spanning role</t>
-        </is>
-      </c>
-      <c r="AP13" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>999</v>
-      </c>
-      <c r="AS13" t="inlineStr">
-        <is>
-          <t>Size</t>
-        </is>
-      </c>
-      <c r="AT13" t="n">
-        <v>18.07</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>36.61</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>999</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0.108</v>
-      </c>
-    </row>
+    <row r="13" ht="15.75" customHeight="1" s="12"/>
     <row r="14" ht="15.75" customHeight="1" s="12">
       <c r="A14" t="inlineStr">
         <is>
@@ -2209,36 +2016,31 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BSMA0002</t>
+          <t>BSMA0003</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BSMA0002.1</t>
+          <t>BSMA0003.1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>BSMA0002.1.7</t>
+          <t>BSMA0003.1.1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0 = Exclude</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2 = Non-employee samples</t>
+          <t>1 = Include</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Comacchio, A., Bonesso, S., &amp; Pizzi, C.</t>
+          <t>Liu Songbo et al.</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>2011</v>
+        <v>2018</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -2252,7 +2054,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>China</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -2261,91 +2063,233 @@
         </is>
       </c>
       <c r="V14" t="n">
-        <v>65</v>
+        <v>272</v>
       </c>
       <c r="W14" t="n">
+        <v>28.64</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>employees from IT companies</t>
+        </is>
+      </c>
+      <c r="AA14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>1 = Self</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>We measured individual BSBs with five items following Marrone et al.'s (2007) approach.</t>
+        </is>
+      </c>
+      <c r="AH14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>6</v>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>1 = Self</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Three items written by Lee, Pillutla, and Law (2000) were used to measure individual power distance orientation in this study.</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Boundary spanning behavior</t>
+        </is>
+      </c>
+      <c r="AP14" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0.881</v>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>Group power distance</t>
+        </is>
+      </c>
+      <c r="AT14" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0.894</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="15" ht="15.75" customHeight="1" s="12">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>BSMA0003</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>BSMA0003.1</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>BSMA0003.1.2</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1 = Include</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Liu Songbo et al.</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>2018</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>1 = Journal article</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1 = Cross-sectional</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>1 = No (domestic only)</t>
+        </is>
+      </c>
+      <c r="V15" t="n">
+        <v>272</v>
+      </c>
+      <c r="W15" t="n">
+        <v>28.64</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>employees from IT companies</t>
+        </is>
+      </c>
+      <c r="AA15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>1 = Self</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>We measured individual BSBs with five items following Marrone et al.'s (2007) approach.</t>
+        </is>
+      </c>
+      <c r="AH15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>3 = Others (e.g. coworker/peer subordinate customer/client)</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>We measured informal leader emergence following a social network approach and used the 1-item measure following Zhang et al.'s (2012) method.</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Boundary spanning behavior</t>
+        </is>
+      </c>
+      <c r="AP15" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0.881</v>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>Informal leader emergence</t>
+        </is>
+      </c>
+      <c r="AT15" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AV15" t="n">
         <v>999</v>
       </c>
-      <c r="X14" t="n">
-        <v>999</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>999</v>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>directors of technology transfer centres</t>
-        </is>
-      </c>
-      <c r="AA14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>1 = Self</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>The survey asked the Centres to indicate the universities they have engaged in joint projects. We coded this information into a dichotomous variable that takes the value 1 if the TTC has indicated at least one university, otherwise the variable takes the value 0.</t>
-        </is>
-      </c>
-      <c r="AH14" t="n">
-        <v>999</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>1 = Self</t>
-        </is>
-      </c>
-      <c r="AM14" t="n">
-        <v>999</v>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Boundary spanning role</t>
-        </is>
-      </c>
-      <c r="AP14" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>999</v>
-      </c>
-      <c r="AS14" t="inlineStr">
-        <is>
-          <t>MHT sectors</t>
-        </is>
-      </c>
-      <c r="AT14" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>999</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>-0.095</v>
+      <c r="AW15" t="n">
+        <v>0.23</v>
       </c>
     </row>
-    <row r="15" ht="15.75" customHeight="1" s="12"/>
     <row r="16" ht="15.75" customHeight="1" s="12">
       <c r="A16" t="inlineStr">
         <is>
@@ -2364,7 +2308,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>BSMA0003.1.1</t>
+          <t>BSMA0003.1.3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2437,22 +2381,22 @@
         </is>
       </c>
       <c r="AH16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI16" t="n">
         <v>1</v>
       </c>
       <c r="AJ16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>1 = Self</t>
+          <t>3 = Others (e.g. coworker/peer subordinate customer/client)</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Three items written by Lee, Pillutla, and Law (2000) were used to measure individual power distance orientation in this study.</t>
+          <t>Task performance was assessed through leader ratings of the target individual. Four items were used from Williams and Anderson's (1991) original scale.</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -2471,20 +2415,20 @@
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>Group power distance</t>
+          <t>Task performance</t>
         </is>
       </c>
       <c r="AT16" t="n">
-        <v>3.78</v>
+        <v>5.61</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.68</v>
+        <v>0.77</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.894</v>
+        <v>0.919</v>
       </c>
       <c r="AW16" t="n">
-        <v>-0.02</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1" s="12">
@@ -2505,7 +2449,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>BSMA0003.1.2</t>
+          <t>BSMA0003.1.4</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2559,13 +2503,13 @@
         </is>
       </c>
       <c r="AA17" t="n">
-        <v>5</v>
+        <v>999</v>
       </c>
       <c r="AB17" t="n">
-        <v>1</v>
+        <v>999</v>
       </c>
       <c r="AC17" t="n">
-        <v>7</v>
+        <v>999</v>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
@@ -2581,19 +2525,19 @@
         <v>1</v>
       </c>
       <c r="AI17" t="n">
-        <v>1</v>
+        <v>999</v>
       </c>
       <c r="AJ17" t="n">
-        <v>5</v>
+        <v>999</v>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>3 = Others (e.g. coworker/peer subordinate customer/client)</t>
+          <t>1 = Self</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>We measured informal leader emergence following a social network approach and used the 1-item measure following Zhang et al.'s (2012) method.</t>
+          <t>Three items written by Lee, Pillutla, and Law (2000) were used to measure individual power distance orientation in this study.</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -2612,20 +2556,20 @@
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>Informal leader emergence</t>
+          <t>Age</t>
         </is>
       </c>
       <c r="AT17" t="n">
-        <v>3.05</v>
+        <v>28.64</v>
       </c>
       <c r="AU17" t="n">
-        <v>0.68</v>
+        <v>5.4</v>
       </c>
       <c r="AV17" t="n">
         <v>999</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.23</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1" s="12">
@@ -2646,7 +2590,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>BSMA0003.1.3</t>
+          <t>BSMA0003.1.5</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2700,13 +2644,13 @@
         </is>
       </c>
       <c r="AA18" t="n">
-        <v>5</v>
+        <v>999</v>
       </c>
       <c r="AB18" t="n">
-        <v>1</v>
+        <v>999</v>
       </c>
       <c r="AC18" t="n">
-        <v>7</v>
+        <v>999</v>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
@@ -2719,17 +2663,17 @@
         </is>
       </c>
       <c r="AH18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AI18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>3 = Others (e.g. coworker/peer subordinate customer/client)</t>
+          <t>1 = Self</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -2753,20 +2697,20 @@
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>Task performance</t>
+          <t>Gender</t>
         </is>
       </c>
       <c r="AT18" t="n">
-        <v>5.61</v>
+        <v>0.43</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.77</v>
+        <v>0.5</v>
       </c>
       <c r="AV18" t="n">
-        <v>0.919</v>
+        <v>999</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.3</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1" s="12">
@@ -2787,7 +2731,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>BSMA0003.1.4</t>
+          <t>BSMA0003.1.6</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2863,10 +2807,10 @@
         <v>1</v>
       </c>
       <c r="AI19" t="n">
-        <v>999</v>
+        <v>1</v>
       </c>
       <c r="AJ19" t="n">
-        <v>999</v>
+        <v>6</v>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
@@ -2894,20 +2838,20 @@
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>Age</t>
+          <t>Education</t>
         </is>
       </c>
       <c r="AT19" t="n">
-        <v>28.64</v>
+        <v>3.28</v>
       </c>
       <c r="AU19" t="n">
-        <v>5.4</v>
+        <v>0.84</v>
       </c>
       <c r="AV19" t="n">
         <v>999</v>
       </c>
       <c r="AW19" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.02</v>
       </c>
     </row>
     <row r="20" ht="15.75" customHeight="1" s="12">
@@ -2928,7 +2872,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>BSMA0003.1.5</t>
+          <t>BSMA0003.1.7</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -3004,10 +2948,10 @@
         <v>1</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1</v>
+        <v>999</v>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
@@ -3035,163 +2979,23 @@
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>Gender</t>
+          <t>Tenure in team</t>
         </is>
       </c>
       <c r="AT20" t="n">
-        <v>0.43</v>
+        <v>2.83</v>
       </c>
       <c r="AU20" t="n">
-        <v>0.5</v>
+        <v>18.77</v>
       </c>
       <c r="AV20" t="n">
         <v>999</v>
       </c>
       <c r="AW20" t="n">
-        <v>-0.09</v>
+        <v>0.03</v>
       </c>
     </row>
-    <row r="21" ht="15.75" customHeight="1" s="12">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>KY</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>BSMA0003</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>BSMA0003.1</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>BSMA0003.1.6</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>1 = Include</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Liu Songbo et al.</t>
-        </is>
-      </c>
-      <c r="K21" t="n">
-        <v>2018</v>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>1 = Journal article</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>1 = Cross-sectional</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>1 = No (domestic only)</t>
-        </is>
-      </c>
-      <c r="V21" t="n">
-        <v>272</v>
-      </c>
-      <c r="W21" t="n">
-        <v>28.64</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>employees from IT companies</t>
-        </is>
-      </c>
-      <c r="AA21" t="n">
-        <v>999</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>999</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>999</v>
-      </c>
-      <c r="AD21" t="inlineStr">
-        <is>
-          <t>1 = Self</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>We measured individual BSBs with five items following Marrone et al.'s (2007) approach.</t>
-        </is>
-      </c>
-      <c r="AH21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>6</v>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>1 = Self</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Three items written by Lee, Pillutla, and Law (2000) were used to measure individual power distance orientation in this study.</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Boundary spanning behavior</t>
-        </is>
-      </c>
-      <c r="AP21" t="n">
-        <v>5.03</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>0.881</v>
-      </c>
-      <c r="AS21" t="inlineStr">
-        <is>
-          <t>Education</t>
-        </is>
-      </c>
-      <c r="AT21" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>999</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>-0.02</v>
-      </c>
-    </row>
+    <row r="21" ht="15.75" customHeight="1" s="12"/>
     <row r="22" ht="15.75" customHeight="1" s="12">
       <c r="A22" t="inlineStr">
         <is>
@@ -3200,137 +3004,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BSMA0003</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>BSMA0003.1</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>BSMA0003.1.7</t>
+          <t>BSMA0004</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1 = Include</t>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>4 = No correlation matrix</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Liu Songbo et al.</t>
-        </is>
-      </c>
-      <c r="K22" t="n">
-        <v>2018</v>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>1 = Journal article</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>1 = Cross-sectional</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>1 = No (domestic only)</t>
-        </is>
-      </c>
-      <c r="V22" t="n">
-        <v>272</v>
-      </c>
-      <c r="W22" t="n">
-        <v>28.64</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>employees from IT companies</t>
-        </is>
-      </c>
-      <c r="AA22" t="n">
-        <v>999</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>999</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>999</v>
-      </c>
-      <c r="AD22" t="inlineStr">
-        <is>
-          <t>1 = Self</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>We measured individual BSBs with five items following Marrone et al.'s (2007) approach.</t>
-        </is>
-      </c>
-      <c r="AH22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>999</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>999</v>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>1 = Self</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Task performance was assessed through leader ratings of the target individual. Four items were used from Williams and Anderson's (1991) original scale.</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Boundary spanning behavior</t>
-        </is>
-      </c>
-      <c r="AP22" t="n">
-        <v>5.03</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>0.881</v>
-      </c>
-      <c r="AS22" t="inlineStr">
-        <is>
-          <t>Tenure in team</t>
-        </is>
-      </c>
-      <c r="AT22" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>18.77</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>999</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>0.03</v>
+          <t>Lifshitz-Assaf Hila</t>
+        </is>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="12"/>
@@ -3342,26 +3032,280 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BSMA0004</t>
+          <t>BSMA0005</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>BSMA0005.1</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>BSMA0005.1.1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0 = Exclude</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>4 = No correlation matrix</t>
+          <t>1 = Include</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Lifshitz-Assaf Hila</t>
-        </is>
+          <t>Zhang Jianru et al.</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>2022</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>1 = Journal article</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>1 = Cross-sectional</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>1 = No (domestic only)</t>
+        </is>
+      </c>
+      <c r="V24" t="n">
+        <v>202</v>
+      </c>
+      <c r="W24" t="n">
+        <v>999</v>
+      </c>
+      <c r="X24" t="n">
+        <v>27</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>employees from telecommunications and IT corporation</t>
+        </is>
+      </c>
+      <c r="AA24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>1 = Self</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>Faraj and Yan (2009)</t>
+        </is>
+      </c>
+      <c r="AH24" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>7</v>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>1 = Self</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Addas &amp; Pinsonneault (2018)</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Individual boundary spanning</t>
+        </is>
+      </c>
+      <c r="AP24" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="AS24" t="inlineStr">
+        <is>
+          <t>Mindfulness</t>
+        </is>
+      </c>
+      <c r="AT24" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>0.898</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>0.331</v>
       </c>
     </row>
-    <row r="25" ht="15.75" customHeight="1" s="12"/>
+    <row r="25" ht="15.75" customHeight="1" s="12">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>BSMA0005</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>BSMA0005.1</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>BSMA0005.1.2</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>1 = Include</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Zhang Jianru et al.</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>2022</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>1 = Journal article</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>1 = Cross-sectional</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>1 = No (domestic only)</t>
+        </is>
+      </c>
+      <c r="V25" t="n">
+        <v>202</v>
+      </c>
+      <c r="W25" t="n">
+        <v>999</v>
+      </c>
+      <c r="X25" t="n">
+        <v>27</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>999</v>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>employees from telecommunications and IT corporation</t>
+        </is>
+      </c>
+      <c r="AA25" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>1 = Self</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>Faraj and Yan (2009)</t>
+        </is>
+      </c>
+      <c r="AH25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>7</v>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>1 = Self</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Zhang et al. (2016)</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Individual boundary spanning</t>
+        </is>
+      </c>
+      <c r="AP25" t="n">
+        <v>4.89</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="AS25" t="inlineStr">
+        <is>
+          <t>Information overload</t>
+        </is>
+      </c>
+      <c r="AT25" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>0.944</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>0.31</v>
+      </c>
+    </row>
     <row r="26" ht="15.75" customHeight="1" s="12">
       <c r="A26" t="inlineStr">
         <is>
@@ -3380,7 +3324,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>BSMA0005.1.1</t>
+          <t>BSMA0005.1.3</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3453,7 +3397,7 @@
         </is>
       </c>
       <c r="AH26" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AI26" t="n">
         <v>1</v>
@@ -3466,10 +3410,8 @@
           <t>1 = Self</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Addas &amp; Pinsonneault (2018)</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>999</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -3487,20 +3429,20 @@
       </c>
       <c r="AS26" t="inlineStr">
         <is>
-          <t>Mindfulness</t>
+          <t>Individual work performance</t>
         </is>
       </c>
       <c r="AT26" t="n">
-        <v>5.48</v>
+        <v>5.22</v>
       </c>
       <c r="AU26" t="n">
-        <v>0.87</v>
+        <v>1.02</v>
       </c>
       <c r="AV26" t="n">
-        <v>0.898</v>
+        <v>0.916</v>
       </c>
       <c r="AW26" t="n">
-        <v>0.331</v>
+        <v>0.149</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1" s="12">
@@ -3521,7 +3463,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>BSMA0005.1.2</t>
+          <t>BSMA0005.1.4</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3594,7 +3536,7 @@
         </is>
       </c>
       <c r="AH27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AI27" t="n">
         <v>1</v>
@@ -3609,7 +3551,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Zhang et al. (2016)</t>
+          <t>Faraj and Yan (2009)</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -3628,159 +3570,27 @@
       </c>
       <c r="AS27" t="inlineStr">
         <is>
-          <t>Information overload</t>
+          <t>Individual boundary buffering</t>
         </is>
       </c>
       <c r="AT27" t="n">
-        <v>3.44</v>
+        <v>3.86</v>
       </c>
       <c r="AU27" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AV27" t="n">
-        <v>0.944</v>
+        <v>0.846</v>
       </c>
       <c r="AW27" t="n">
-        <v>0.31</v>
+        <v>0.252</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" s="12">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>KY</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>BSMA0005</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>BSMA0005.1</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>BSMA0005.1.3</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>1 = Include</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>Zhang Jianru et al.</t>
-        </is>
-      </c>
-      <c r="K28" t="n">
-        <v>2022</v>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>1 = Journal article</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>1 = Cross-sectional</t>
-        </is>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>1 = No (domestic only)</t>
-        </is>
-      </c>
-      <c r="V28" t="n">
-        <v>202</v>
-      </c>
-      <c r="W28" t="n">
-        <v>999</v>
-      </c>
-      <c r="X28" t="n">
-        <v>27</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>999</v>
-      </c>
       <c r="Z28" t="inlineStr">
         <is>
           <t>employees from telecommunications and IT corporation</t>
         </is>
-      </c>
-      <c r="AA28" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD28" t="inlineStr">
-        <is>
-          <t>1 = Self</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>Faraj and Yan (2009)</t>
-        </is>
-      </c>
-      <c r="AH28" t="n">
-        <v>4</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>7</v>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>1 = Self</t>
-        </is>
-      </c>
-      <c r="AM28" t="n">
-        <v>999</v>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Individual boundary spanning</t>
-        </is>
-      </c>
-      <c r="AP28" t="n">
-        <v>4.89</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>0.867</v>
-      </c>
-      <c r="AS28" t="inlineStr">
-        <is>
-          <t>Individual work performance</t>
-        </is>
-      </c>
-      <c r="AT28" t="n">
-        <v>5.22</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>0.916</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>0.149</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1" s="12">
@@ -3791,17 +3601,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BSMA0005</t>
+          <t>BSMA0006</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>BSMA0005.1</t>
+          <t>BSMA0006.1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>BSMA0005.1.4</t>
+          <t>BSMA0006.1.1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3809,13 +3619,23 @@
           <t>1 = Include</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Expatriates' boundary-spanning: double-edged effects in multinational enterprises</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Journal of International Business Studies</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Zhang Jianru et al.</t>
+          <t>Liu, T., Sekiguchi, T., Qin, J., &amp; Shen, Y. X.</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -3824,7 +3644,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>1 = Cross-sectional</t>
+          <t>2 = Longitudinal</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
@@ -3834,28 +3654,28 @@
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>1 = No (domestic only)</t>
+          <t>2 = Yes (international)</t>
         </is>
       </c>
       <c r="V29" t="n">
-        <v>202</v>
+        <v>177</v>
       </c>
       <c r="W29" t="n">
-        <v>999</v>
+        <v>33.91</v>
       </c>
       <c r="X29" t="n">
-        <v>27</v>
+        <v>50.28</v>
       </c>
       <c r="Y29" t="n">
-        <v>999</v>
+        <v>2.63</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>employees from telecommunications and IT corporation</t>
+          <t>Expatriate employees and host-country coworkers in energy engineering MNEs</t>
         </is>
       </c>
       <c r="AA29" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AB29" t="n">
         <v>1</v>
@@ -3865,16 +3685,21 @@
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>1 = Self</t>
+          <t>3 = Others (e.g. coworker/peer subordinate customer/client)</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>host-country coworkers</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>Faraj and Yan (2009)</t>
+          <t>Liu et al. (2024) - newly developed</t>
         </is>
       </c>
       <c r="AH29" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="AI29" t="n">
         <v>1</v>
@@ -3884,51 +3709,210 @@
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>1 = Self</t>
+          <t>3 = Others (e.g. coworker/peer subordinate customer/client)</t>
+        </is>
+      </c>
+      <c r="AL29" t="inlineStr">
+        <is>
+          <t>host-country coworkers</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>Faraj and Yan (2009)</t>
+          <t>Liu et al. (2024)</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>Individual boundary spanning</t>
+          <t>Functional boundary-spanning</t>
         </is>
       </c>
       <c r="AP29" t="n">
-        <v>4.89</v>
+        <v>5.51</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.26</v>
+        <v>0.77</v>
       </c>
       <c r="AR29" t="n">
-        <v>0.867</v>
+        <v>0.91</v>
       </c>
       <c r="AS29" t="inlineStr">
         <is>
-          <t>Individual boundary buffering</t>
+          <t>Expatriates’ boundary-spanning</t>
         </is>
       </c>
       <c r="AT29" t="n">
-        <v>3.86</v>
+        <v>5.27</v>
       </c>
       <c r="AU29" t="n">
-        <v>1.62</v>
+        <v>0.74</v>
       </c>
       <c r="AV29" t="n">
-        <v>0.846</v>
+        <v>0.96</v>
       </c>
       <c r="AW29" t="n">
-        <v>0.252</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1" s="12">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>BSMA0006</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>BSMA0006.1</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>BSMA0006.1.2</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>1 = Include</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Expatriates' boundary-spanning: double-edged effects in multinational enterprises</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Journal of International Business Studies</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Liu, T., Sekiguchi, T., Qin, J., &amp; Shen, Y. X.</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>2024</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>1 = Journal article</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>2 = Longitudinal</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>2 = Yes (international)</t>
+        </is>
+      </c>
+      <c r="V30" t="n">
+        <v>177</v>
+      </c>
+      <c r="W30" t="n">
+        <v>33.91</v>
+      </c>
+      <c r="X30" t="n">
+        <v>50.28</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>2.63</v>
+      </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>employees from telecommunications and IT corporation</t>
-        </is>
+          <t>Expatriate employees and host-country coworkers in energy engineering MNEs</t>
+        </is>
+      </c>
+      <c r="AA30" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>3 = Others (e.g. coworker/peer subordinate customer/client)</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>host-country coworkers</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>Liu et al. (2024) - newly developed</t>
+        </is>
+      </c>
+      <c r="AH30" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>7</v>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>3 = Others (e.g. coworker/peer subordinate customer/client)</t>
+        </is>
+      </c>
+      <c r="AL30" t="inlineStr">
+        <is>
+          <t>host-country coworkers</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Liu et al. (2024)</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Linguistic boundary-spanning</t>
+        </is>
+      </c>
+      <c r="AP30" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AS30" t="inlineStr">
+        <is>
+          <t>Expatriates’ boundary-spanning</t>
+        </is>
+      </c>
+      <c r="AT30" t="n">
+        <v>5.27</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>0.84</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1" s="12">
@@ -3949,7 +3933,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>BSMA0006.1.1</t>
+          <t>BSMA0006.1.3</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -4013,48 +3997,48 @@
         </is>
       </c>
       <c r="AA31" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>3 = Others (e.g. coworker/peer subordinate customer/client)</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>host-country coworkers</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>Liu et al. (2024) - newly developed</t>
+        </is>
+      </c>
+      <c r="AH31" t="n">
         <v>9</v>
       </c>
-      <c r="AB31" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD31" t="inlineStr">
+      <c r="AI31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>7</v>
+      </c>
+      <c r="AK31" t="inlineStr">
         <is>
           <t>3 = Others (e.g. coworker/peer subordinate customer/client)</t>
         </is>
       </c>
-      <c r="AE31" t="inlineStr">
+      <c r="AL31" t="inlineStr">
         <is>
           <t>host-country coworkers</t>
         </is>
       </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>Liu et al. (2024) - newly developed</t>
-        </is>
-      </c>
-      <c r="AH31" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>7</v>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>3 = Others (e.g. coworker/peer subordinate customer/client)</t>
-        </is>
-      </c>
-      <c r="AL31" t="inlineStr">
-        <is>
-          <t>host-country coworkers</t>
-        </is>
-      </c>
       <c r="AM31" t="inlineStr">
         <is>
           <t>Liu et al. (2024)</t>
@@ -4062,34 +4046,34 @@
       </c>
       <c r="AO31" t="inlineStr">
         <is>
+          <t>Linguistic boundary-spanning</t>
+        </is>
+      </c>
+      <c r="AP31" t="n">
+        <v>5.04</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AS31" t="inlineStr">
+        <is>
           <t>Functional boundary-spanning</t>
         </is>
       </c>
-      <c r="AP31" t="n">
+      <c r="AT31" t="n">
         <v>5.51</v>
       </c>
-      <c r="AQ31" t="n">
+      <c r="AU31" t="n">
         <v>0.77</v>
       </c>
-      <c r="AR31" t="n">
+      <c r="AV31" t="n">
         <v>0.91</v>
       </c>
-      <c r="AS31" t="inlineStr">
-        <is>
-          <t>Expatriates’ boundary-spanning</t>
-        </is>
-      </c>
-      <c r="AT31" t="n">
-        <v>5.27</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>0.96</v>
-      </c>
       <c r="AW31" t="n">
-        <v>0.79</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1" s="12">
@@ -4110,7 +4094,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>BSMA0006.1.2</t>
+          <t>BSMA0006.1.4</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -4174,7 +4158,7 @@
         </is>
       </c>
       <c r="AA32" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB32" t="n">
         <v>1</v>
@@ -4223,17 +4207,17 @@
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>Linguistic boundary-spanning</t>
+          <t>Cultural boundary-spanning</t>
         </is>
       </c>
       <c r="AP32" t="n">
-        <v>5.04</v>
+        <v>5.22</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.03</v>
+        <v>0.83</v>
       </c>
       <c r="AR32" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="AS32" t="inlineStr">
         <is>
@@ -4250,7 +4234,7 @@
         <v>0.96</v>
       </c>
       <c r="AW32" t="n">
-        <v>0.84</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1" s="12">
@@ -4271,7 +4255,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>BSMA0006.1.3</t>
+          <t>BSMA0006.1.5</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -4335,7 +4319,7 @@
         </is>
       </c>
       <c r="AA33" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AB33" t="n">
         <v>1</v>
@@ -4384,17 +4368,17 @@
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Linguistic boundary-spanning</t>
+          <t>Cultural boundary-spanning</t>
         </is>
       </c>
       <c r="AP33" t="n">
-        <v>5.04</v>
+        <v>5.22</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.03</v>
+        <v>0.83</v>
       </c>
       <c r="AR33" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="AS33" t="inlineStr">
         <is>
@@ -4411,7 +4395,7 @@
         <v>0.91</v>
       </c>
       <c r="AW33" t="n">
-        <v>0.42</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1" s="12">
@@ -4432,7 +4416,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>BSMA0006.1.4</t>
+          <t>BSMA0006.1.6</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -4520,7 +4504,7 @@
         </is>
       </c>
       <c r="AH34" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="AI34" t="n">
         <v>1</v>
@@ -4559,20 +4543,20 @@
       </c>
       <c r="AS34" t="inlineStr">
         <is>
-          <t>Expatriates’ boundary-spanning</t>
+          <t>Linguistic boundary-spanning</t>
         </is>
       </c>
       <c r="AT34" t="n">
-        <v>5.27</v>
+        <v>5.04</v>
       </c>
       <c r="AU34" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AW34" t="n">
         <v>0.74</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1" s="12">
@@ -4593,7 +4577,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>BSMA0006.1.5</t>
+          <t>BSMA0006.1.7</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -4657,7 +4641,7 @@
         </is>
       </c>
       <c r="AA35" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="AB35" t="n">
         <v>1</v>
@@ -4681,7 +4665,7 @@
         </is>
       </c>
       <c r="AH35" t="n">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="AI35" t="n">
         <v>1</v>
@@ -4706,34 +4690,34 @@
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>Cultural boundary-spanning</t>
+          <t>Mutual trust</t>
         </is>
       </c>
       <c r="AP35" t="n">
-        <v>5.22</v>
+        <v>5.25</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0.83</v>
+        <v>0.68</v>
       </c>
       <c r="AR35" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="AS35" t="inlineStr">
         <is>
-          <t>Functional boundary-spanning</t>
+          <t>Expatriates’ boundary-spanning</t>
         </is>
       </c>
       <c r="AT35" t="n">
-        <v>5.51</v>
+        <v>5.27</v>
       </c>
       <c r="AU35" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="AV35" t="n">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="AW35" t="n">
-        <v>0.64</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1" s="12">
@@ -4754,7 +4738,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>BSMA0006.1.6</t>
+          <t>BSMA0006.1.8</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -4818,7 +4802,7 @@
         </is>
       </c>
       <c r="AA36" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="AB36" t="n">
         <v>1</v>
@@ -4842,7 +4826,7 @@
         </is>
       </c>
       <c r="AH36" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AI36" t="n">
         <v>1</v>
@@ -4867,34 +4851,34 @@
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Cultural boundary-spanning</t>
+          <t>Mutual trust</t>
         </is>
       </c>
       <c r="AP36" t="n">
-        <v>5.22</v>
+        <v>5.25</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0.83</v>
+        <v>0.68</v>
       </c>
       <c r="AR36" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="AS36" t="inlineStr">
         <is>
-          <t>Linguistic boundary-spanning</t>
+          <t>Functional boundary-spanning</t>
         </is>
       </c>
       <c r="AT36" t="n">
-        <v>5.04</v>
+        <v>5.51</v>
       </c>
       <c r="AU36" t="n">
-        <v>1.03</v>
+        <v>0.77</v>
       </c>
       <c r="AV36" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.91</v>
       </c>
       <c r="AW36" t="n">
-        <v>0.74</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1" s="12">
@@ -4915,7 +4899,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>BSMA0006.1.7</t>
+          <t>BSMA0006.1.9</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -5003,7 +4987,7 @@
         </is>
       </c>
       <c r="AH37" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="AI37" t="n">
         <v>1</v>
@@ -5042,20 +5026,20 @@
       </c>
       <c r="AS37" t="inlineStr">
         <is>
-          <t>Expatriates’ boundary-spanning</t>
+          <t>Linguistic boundary-spanning</t>
         </is>
       </c>
       <c r="AT37" t="n">
-        <v>5.27</v>
+        <v>5.04</v>
       </c>
       <c r="AU37" t="n">
-        <v>0.74</v>
+        <v>1.03</v>
       </c>
       <c r="AV37" t="n">
-        <v>0.96</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AW37" t="n">
-        <v>0.71</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1" s="12">
@@ -5076,7 +5060,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>BSMA0006.1.8</t>
+          <t>BSMA0006.1.10</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -5164,7 +5148,7 @@
         </is>
       </c>
       <c r="AH38" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI38" t="n">
         <v>1</v>
@@ -5203,20 +5187,20 @@
       </c>
       <c r="AS38" t="inlineStr">
         <is>
-          <t>Functional boundary-spanning</t>
+          <t>Cultural boundary-spanning</t>
         </is>
       </c>
       <c r="AT38" t="n">
-        <v>5.51</v>
+        <v>5.22</v>
       </c>
       <c r="AU38" t="n">
-        <v>0.77</v>
+        <v>0.83</v>
       </c>
       <c r="AV38" t="n">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="AW38" t="n">
-        <v>0.55</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1" s="12">
@@ -5237,7 +5221,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>BSMA0006.1.9</t>
+          <t>BSMA0006.1.11</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -5325,7 +5309,7 @@
         </is>
       </c>
       <c r="AH39" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="AI39" t="n">
         <v>1</v>
@@ -5350,34 +5334,34 @@
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Mutual trust</t>
+          <t>Cognition-based mutual trust</t>
         </is>
       </c>
       <c r="AP39" t="n">
-        <v>5.25</v>
+        <v>5.38</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0.68</v>
+        <v>0.64</v>
       </c>
       <c r="AR39" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="AS39" t="inlineStr">
         <is>
-          <t>Linguistic boundary-spanning</t>
+          <t>Expatriates’ boundary-spanning</t>
         </is>
       </c>
       <c r="AT39" t="n">
-        <v>5.04</v>
+        <v>5.27</v>
       </c>
       <c r="AU39" t="n">
-        <v>1.03</v>
+        <v>0.74</v>
       </c>
       <c r="AV39" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="AW39" t="n">
-        <v>0.55</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1" s="12">
@@ -5398,7 +5382,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>BSMA0006.1.10</t>
+          <t>BSMA0006.1.12</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -5486,7 +5470,7 @@
         </is>
       </c>
       <c r="AH40" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI40" t="n">
         <v>1</v>
@@ -5511,34 +5495,34 @@
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Mutual trust</t>
+          <t>Cognition-based mutual trust</t>
         </is>
       </c>
       <c r="AP40" t="n">
-        <v>5.25</v>
+        <v>5.38</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0.68</v>
+        <v>0.64</v>
       </c>
       <c r="AR40" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="AS40" t="inlineStr">
         <is>
-          <t>Cultural boundary-spanning</t>
+          <t>Functional boundary-spanning</t>
         </is>
       </c>
       <c r="AT40" t="n">
-        <v>5.22</v>
+        <v>5.51</v>
       </c>
       <c r="AU40" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AV40" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="AW40" t="n">
-        <v>0.7</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1" s="12">
@@ -5559,7 +5543,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>BSMA0006.1.11</t>
+          <t>BSMA0006.1.13</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -5647,7 +5631,7 @@
         </is>
       </c>
       <c r="AH41" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="AI41" t="n">
         <v>1</v>
@@ -5686,20 +5670,20 @@
       </c>
       <c r="AS41" t="inlineStr">
         <is>
-          <t>Expatriates’ boundary-spanning</t>
+          <t>Linguistic boundary-spanning</t>
         </is>
       </c>
       <c r="AT41" t="n">
-        <v>5.27</v>
+        <v>5.04</v>
       </c>
       <c r="AU41" t="n">
-        <v>0.74</v>
+        <v>1.03</v>
       </c>
       <c r="AV41" t="n">
-        <v>0.96</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AW41" t="n">
-        <v>0.63</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1" s="12">
@@ -5720,7 +5704,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>BSMA0006.1.12</t>
+          <t>BSMA0006.1.14</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -5808,7 +5792,7 @@
         </is>
       </c>
       <c r="AH42" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI42" t="n">
         <v>1</v>
@@ -5847,20 +5831,20 @@
       </c>
       <c r="AS42" t="inlineStr">
         <is>
-          <t>Functional boundary-spanning</t>
+          <t>Cultural boundary-spanning</t>
         </is>
       </c>
       <c r="AT42" t="n">
-        <v>5.51</v>
+        <v>5.22</v>
       </c>
       <c r="AU42" t="n">
-        <v>0.77</v>
+        <v>0.83</v>
       </c>
       <c r="AV42" t="n">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="AW42" t="n">
-        <v>0.53</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1" s="12">
@@ -5881,7 +5865,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>BSMA0006.1.13</t>
+          <t>BSMA0006.1.15</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -5969,7 +5953,7 @@
         </is>
       </c>
       <c r="AH43" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AI43" t="n">
         <v>1</v>
@@ -5979,17 +5963,17 @@
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>3 = Others (e.g. coworker/peer subordinate customer/client)</t>
+          <t>1 = Self-report</t>
         </is>
       </c>
       <c r="AL43" t="inlineStr">
         <is>
-          <t>host-country coworkers</t>
+          <t>expatriates and coworkers</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Liu et al. (2024)</t>
+          <t>McAllister (1995)</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
@@ -6008,20 +5992,20 @@
       </c>
       <c r="AS43" t="inlineStr">
         <is>
-          <t>Linguistic boundary-spanning</t>
+          <t>Mutual trust</t>
         </is>
       </c>
       <c r="AT43" t="n">
-        <v>5.04</v>
+        <v>5.25</v>
       </c>
       <c r="AU43" t="n">
-        <v>1.03</v>
+        <v>0.68</v>
       </c>
       <c r="AV43" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AW43" t="n">
         <v>0.9399999999999999</v>
-      </c>
-      <c r="AW43" t="n">
-        <v>0.47</v>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1" s="12">
@@ -6042,7 +6026,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>BSMA0006.1.14</t>
+          <t>BSMA0006.1.16</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -6130,7 +6114,7 @@
         </is>
       </c>
       <c r="AH44" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="AI44" t="n">
         <v>1</v>
@@ -6155,34 +6139,34 @@
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Cognition-based mutual trust</t>
+          <t>Affect-based mutual trust</t>
         </is>
       </c>
       <c r="AP44" t="n">
-        <v>5.38</v>
+        <v>5.11</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0.64</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR44" t="n">
-        <v>0.8</v>
+        <v>0.87</v>
       </c>
       <c r="AS44" t="inlineStr">
         <is>
-          <t>Cultural boundary-spanning</t>
+          <t>Expatriates’ boundary-spanning</t>
         </is>
       </c>
       <c r="AT44" t="n">
-        <v>5.22</v>
+        <v>5.27</v>
       </c>
       <c r="AU44" t="n">
-        <v>0.83</v>
+        <v>0.74</v>
       </c>
       <c r="AV44" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="AW44" t="n">
-        <v>0.62</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1" s="12">
@@ -6203,7 +6187,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>BSMA0006.1.15</t>
+          <t>BSMA0006.1.17</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -6291,7 +6275,7 @@
         </is>
       </c>
       <c r="AH45" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AI45" t="n">
         <v>1</v>
@@ -6301,49 +6285,49 @@
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>1 = Self-report</t>
+          <t>3 = Others (e.g. coworker/peer subordinate customer/client)</t>
         </is>
       </c>
       <c r="AL45" t="inlineStr">
         <is>
-          <t>expatriates and coworkers</t>
+          <t>host-country coworkers</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>McAllister (1995)</t>
+          <t>Liu et al. (2024)</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Cognition-based mutual trust</t>
+          <t>Affect-based mutual trust</t>
         </is>
       </c>
       <c r="AP45" t="n">
-        <v>5.38</v>
+        <v>5.11</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0.64</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AR45" t="n">
-        <v>0.8</v>
+        <v>0.87</v>
       </c>
       <c r="AS45" t="inlineStr">
         <is>
-          <t>Mutual trust</t>
+          <t>Functional boundary-spanning</t>
         </is>
       </c>
       <c r="AT45" t="n">
-        <v>5.25</v>
+        <v>5.51</v>
       </c>
       <c r="AU45" t="n">
-        <v>0.68</v>
+        <v>0.77</v>
       </c>
       <c r="AV45" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AW45" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1" s="12">
@@ -6364,7 +6348,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>BSMA0006.1.16</t>
+          <t>BSMA0006.1.18</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -6452,7 +6436,7 @@
         </is>
       </c>
       <c r="AH46" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="AI46" t="n">
         <v>1</v>
@@ -6491,20 +6475,20 @@
       </c>
       <c r="AS46" t="inlineStr">
         <is>
-          <t>Expatriates’ boundary-spanning</t>
+          <t>Linguistic boundary-spanning</t>
         </is>
       </c>
       <c r="AT46" t="n">
-        <v>5.27</v>
+        <v>5.04</v>
       </c>
       <c r="AU46" t="n">
-        <v>0.74</v>
+        <v>1.03</v>
       </c>
       <c r="AV46" t="n">
-        <v>0.96</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AW46" t="n">
-        <v>0.7</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1" s="12">
@@ -6525,7 +6509,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>BSMA0006.1.17</t>
+          <t>BSMA0006.1.19</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -6613,7 +6597,7 @@
         </is>
       </c>
       <c r="AH47" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI47" t="n">
         <v>1</v>
@@ -6652,20 +6636,20 @@
       </c>
       <c r="AS47" t="inlineStr">
         <is>
-          <t>Functional boundary-spanning</t>
+          <t>Cultural boundary-spanning</t>
         </is>
       </c>
       <c r="AT47" t="n">
-        <v>5.51</v>
+        <v>5.22</v>
       </c>
       <c r="AU47" t="n">
-        <v>0.77</v>
+        <v>0.83</v>
       </c>
       <c r="AV47" t="n">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="AW47" t="n">
-        <v>0.51</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1" s="12">
@@ -6686,7 +6670,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>BSMA0006.1.18</t>
+          <t>BSMA0006.1.20</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -6774,7 +6758,7 @@
         </is>
       </c>
       <c r="AH48" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AI48" t="n">
         <v>1</v>
@@ -6784,17 +6768,17 @@
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>3 = Others (e.g. coworker/peer subordinate customer/client)</t>
+          <t>1 = Self-report</t>
         </is>
       </c>
       <c r="AL48" t="inlineStr">
         <is>
-          <t>host-country coworkers</t>
+          <t>expatriates and coworkers</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>Liu et al. (2024)</t>
+          <t>McAllister (1995)</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
@@ -6813,20 +6797,20 @@
       </c>
       <c r="AS48" t="inlineStr">
         <is>
-          <t>Linguistic boundary-spanning</t>
+          <t>Mutual trust</t>
         </is>
       </c>
       <c r="AT48" t="n">
-        <v>5.04</v>
+        <v>5.25</v>
       </c>
       <c r="AU48" t="n">
-        <v>1.03</v>
+        <v>0.68</v>
       </c>
       <c r="AV48" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="AW48" t="n">
-        <v>0.57</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1" s="12">
@@ -6847,7 +6831,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>BSMA0006.1.19</t>
+          <t>BSMA0006.1.21</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -6935,7 +6919,7 @@
         </is>
       </c>
       <c r="AH49" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI49" t="n">
         <v>1</v>
@@ -6945,17 +6929,17 @@
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>3 = Others (e.g. coworker/peer subordinate customer/client)</t>
+          <t>1 = Self-report</t>
         </is>
       </c>
       <c r="AL49" t="inlineStr">
         <is>
-          <t>host-country coworkers</t>
+          <t>expatriates and coworkers</t>
         </is>
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Liu et al. (2024)</t>
+          <t>McAllister (1995)</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
@@ -6974,20 +6958,20 @@
       </c>
       <c r="AS49" t="inlineStr">
         <is>
-          <t>Cultural boundary-spanning</t>
+          <t>Cognition-based mutual trust</t>
         </is>
       </c>
       <c r="AT49" t="n">
-        <v>5.22</v>
+        <v>5.38</v>
       </c>
       <c r="AU49" t="n">
-        <v>0.83</v>
+        <v>0.64</v>
       </c>
       <c r="AV49" t="n">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
       <c r="AW49" t="n">
-        <v>0.7</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1" s="12">
@@ -7008,7 +6992,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>BSMA0006.1.20</t>
+          <t>BSMA0006.1.22</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -7096,7 +7080,7 @@
         </is>
       </c>
       <c r="AH50" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="AI50" t="n">
         <v>1</v>
@@ -7106,49 +7090,49 @@
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>1 = Self-report</t>
+          <t>3 = Others (e.g. coworker/peer subordinate customer/client)</t>
         </is>
       </c>
       <c r="AL50" t="inlineStr">
         <is>
-          <t>expatriates and coworkers</t>
+          <t>host-country coworkers</t>
         </is>
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>McAllister (1995)</t>
+          <t>Liu et al. (2024)</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>Affect-based mutual trust</t>
+          <t>Role stressors</t>
         </is>
       </c>
       <c r="AP50" t="n">
-        <v>5.11</v>
+        <v>3.64</v>
       </c>
       <c r="AQ50" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.97</v>
       </c>
       <c r="AR50" t="n">
-        <v>0.87</v>
+        <v>0.93</v>
       </c>
       <c r="AS50" t="inlineStr">
         <is>
-          <t>Mutual trust</t>
+          <t>Expatriates’ boundary-spanning</t>
         </is>
       </c>
       <c r="AT50" t="n">
-        <v>5.25</v>
+        <v>5.27</v>
       </c>
       <c r="AU50" t="n">
-        <v>0.68</v>
+        <v>0.74</v>
       </c>
       <c r="AV50" t="n">
-        <v>0.9</v>
+        <v>0.96</v>
       </c>
       <c r="AW50" t="n">
-        <v>0.95</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1" s="12">
@@ -7169,7 +7153,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>BSMA0006.1.21</t>
+          <t>BSMA0006.1.23</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -7257,7 +7241,7 @@
         </is>
       </c>
       <c r="AH51" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AI51" t="n">
         <v>1</v>
@@ -7267,49 +7251,49 @@
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>1 = Self-report</t>
+          <t>3 = Others (e.g. coworker/peer subordinate customer/client)</t>
         </is>
       </c>
       <c r="AL51" t="inlineStr">
         <is>
-          <t>expatriates and coworkers</t>
+          <t>host-country coworkers</t>
         </is>
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>McAllister (1995)</t>
+          <t>Liu et al. (2024)</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Affect-based mutual trust</t>
+          <t>Role stressors</t>
         </is>
       </c>
       <c r="AP51" t="n">
-        <v>5.11</v>
+        <v>3.64</v>
       </c>
       <c r="AQ51" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.97</v>
       </c>
       <c r="AR51" t="n">
-        <v>0.87</v>
+        <v>0.93</v>
       </c>
       <c r="AS51" t="inlineStr">
         <is>
-          <t>Cognition-based mutual trust</t>
+          <t>Functional boundary-spanning</t>
         </is>
       </c>
       <c r="AT51" t="n">
-        <v>5.38</v>
+        <v>5.51</v>
       </c>
       <c r="AU51" t="n">
-        <v>0.64</v>
+        <v>0.77</v>
       </c>
       <c r="AV51" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="AW51" t="n">
-        <v>0.78</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="52" ht="15.75" customHeight="1" s="12">
@@ -7330,7 +7314,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>BSMA0006.1.22</t>
+          <t>BSMA0006.1.24</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -7418,7 +7402,7 @@
         </is>
       </c>
       <c r="AH52" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="AI52" t="n">
         <v>1</v>
@@ -7457,20 +7441,20 @@
       </c>
       <c r="AS52" t="inlineStr">
         <is>
-          <t>Expatriates’ boundary-spanning</t>
+          <t>Linguistic boundary-spanning</t>
         </is>
       </c>
       <c r="AT52" t="n">
-        <v>5.27</v>
+        <v>5.04</v>
       </c>
       <c r="AU52" t="n">
-        <v>0.74</v>
+        <v>1.03</v>
       </c>
       <c r="AV52" t="n">
-        <v>0.96</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AW52" t="n">
-        <v>0.42</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="53" ht="15.75" customHeight="1" s="12">
@@ -7491,7 +7475,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>BSMA0006.1.23</t>
+          <t>BSMA0006.1.25</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -7579,7 +7563,7 @@
         </is>
       </c>
       <c r="AH53" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI53" t="n">
         <v>1</v>
@@ -7618,17 +7602,17 @@
       </c>
       <c r="AS53" t="inlineStr">
         <is>
-          <t>Functional boundary-spanning</t>
+          <t>Cultural boundary-spanning</t>
         </is>
       </c>
       <c r="AT53" t="n">
-        <v>5.51</v>
+        <v>5.22</v>
       </c>
       <c r="AU53" t="n">
-        <v>0.77</v>
+        <v>0.83</v>
       </c>
       <c r="AV53" t="n">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="AW53" t="n">
         <v>0.4</v>
@@ -7652,7 +7636,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>BSMA0006.1.24</t>
+          <t>BSMA0006.1.26</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -7740,7 +7724,7 @@
         </is>
       </c>
       <c r="AH54" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AI54" t="n">
         <v>1</v>
@@ -7750,17 +7734,17 @@
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>3 = Others (e.g. coworker/peer subordinate customer/client)</t>
+          <t>1 = Self-report</t>
         </is>
       </c>
       <c r="AL54" t="inlineStr">
         <is>
-          <t>host-country coworkers</t>
+          <t>expatriates and coworkers</t>
         </is>
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>Liu et al. (2024)</t>
+          <t>McAllister (1995)</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
@@ -7779,20 +7763,20 @@
       </c>
       <c r="AS54" t="inlineStr">
         <is>
-          <t>Linguistic boundary-spanning</t>
+          <t>Mutual trust</t>
         </is>
       </c>
       <c r="AT54" t="n">
-        <v>5.04</v>
+        <v>5.25</v>
       </c>
       <c r="AU54" t="n">
-        <v>1.03</v>
+        <v>0.68</v>
       </c>
       <c r="AV54" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="AW54" t="n">
-        <v>0.27</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1" s="12">
@@ -7813,7 +7797,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>BSMA0006.1.25</t>
+          <t>BSMA0006.1.27</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -7901,7 +7885,7 @@
         </is>
       </c>
       <c r="AH55" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI55" t="n">
         <v>1</v>
@@ -7911,17 +7895,17 @@
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>3 = Others (e.g. coworker/peer subordinate customer/client)</t>
+          <t>1 = Self-report</t>
         </is>
       </c>
       <c r="AL55" t="inlineStr">
         <is>
-          <t>host-country coworkers</t>
+          <t>expatriates and coworkers</t>
         </is>
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>Liu et al. (2024)</t>
+          <t>McAllister (1995)</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
@@ -7940,20 +7924,20 @@
       </c>
       <c r="AS55" t="inlineStr">
         <is>
-          <t>Cultural boundary-spanning</t>
+          <t>Cognition-based mutual trust</t>
         </is>
       </c>
       <c r="AT55" t="n">
-        <v>5.22</v>
+        <v>5.38</v>
       </c>
       <c r="AU55" t="n">
-        <v>0.83</v>
+        <v>0.64</v>
       </c>
       <c r="AV55" t="n">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
       <c r="AW55" t="n">
-        <v>0.4</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="56" ht="15.75" customHeight="1" s="12">
@@ -7974,7 +7958,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>BSMA0006.1.26</t>
+          <t>BSMA0006.1.28</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -8101,20 +8085,20 @@
       </c>
       <c r="AS56" t="inlineStr">
         <is>
-          <t>Mutual trust</t>
+          <t>Affect-based mutual trust</t>
         </is>
       </c>
       <c r="AT56" t="n">
-        <v>5.25</v>
+        <v>5.11</v>
       </c>
       <c r="AU56" t="n">
-        <v>0.68</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AV56" t="n">
-        <v>0.9</v>
+        <v>0.87</v>
       </c>
       <c r="AW56" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="57" ht="15.75" customHeight="1" s="12">
@@ -8135,7 +8119,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>BSMA0006.1.27</t>
+          <t>BSMA0006.1.29</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -8223,7 +8207,7 @@
         </is>
       </c>
       <c r="AH57" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="AI57" t="n">
         <v>1</v>
@@ -8233,49 +8217,49 @@
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>1 = Self-report</t>
+          <t>3 = Others (e.g. coworker/peer subordinate customer/client)</t>
         </is>
       </c>
       <c r="AL57" t="inlineStr">
         <is>
-          <t>expatriates and coworkers</t>
+          <t>host-country coworkers</t>
         </is>
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>McAllister (1995)</t>
+          <t>Liu et al. (2024)</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>Role stressors</t>
+          <t>Expatriates’ subsidiary identification</t>
         </is>
       </c>
       <c r="AP57" t="n">
-        <v>3.64</v>
+        <v>5.3</v>
       </c>
       <c r="AQ57" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="AR57" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="AS57" t="inlineStr">
         <is>
-          <t>Cognition-based mutual trust</t>
+          <t>Expatriates’ boundary-spanning</t>
         </is>
       </c>
       <c r="AT57" t="n">
-        <v>5.38</v>
+        <v>5.27</v>
       </c>
       <c r="AU57" t="n">
-        <v>0.64</v>
+        <v>0.74</v>
       </c>
       <c r="AV57" t="n">
-        <v>0.8</v>
+        <v>0.96</v>
       </c>
       <c r="AW57" t="n">
-        <v>0.09</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="58" ht="15.75" customHeight="1" s="12">
@@ -8296,7 +8280,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>BSMA0006.1.28</t>
+          <t>BSMA0006.1.30</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -8384,7 +8368,7 @@
         </is>
       </c>
       <c r="AH58" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AI58" t="n">
         <v>1</v>
@@ -8394,49 +8378,49 @@
       </c>
       <c r="AK58" t="inlineStr">
         <is>
-          <t>1 = Self-report</t>
+          <t>3 = Others (e.g. coworker/peer subordinate customer/client)</t>
         </is>
       </c>
       <c r="AL58" t="inlineStr">
         <is>
-          <t>expatriates and coworkers</t>
+          <t>host-country coworkers</t>
         </is>
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>McAllister (1995)</t>
+          <t>Liu et al. (2024)</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>Role stressors</t>
+          <t>Expatriates’ subsidiary identification</t>
         </is>
       </c>
       <c r="AP58" t="n">
-        <v>3.64</v>
+        <v>5.3</v>
       </c>
       <c r="AQ58" t="n">
-        <v>0.97</v>
+        <v>0.95</v>
       </c>
       <c r="AR58" t="n">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="AS58" t="inlineStr">
         <is>
-          <t>Affect-based mutual trust</t>
+          <t>Functional boundary-spanning</t>
         </is>
       </c>
       <c r="AT58" t="n">
-        <v>5.11</v>
+        <v>5.51</v>
       </c>
       <c r="AU58" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="AV58" t="n">
-        <v>0.87</v>
+        <v>0.91</v>
       </c>
       <c r="AW58" t="n">
-        <v>0.17</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="59" ht="15.75" customHeight="1" s="12">
@@ -8457,7 +8441,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>BSMA0006.1.29</t>
+          <t>BSMA0006.1.31</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -8545,7 +8529,7 @@
         </is>
       </c>
       <c r="AH59" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="AI59" t="n">
         <v>1</v>
@@ -8584,20 +8568,20 @@
       </c>
       <c r="AS59" t="inlineStr">
         <is>
-          <t>Expatriates’ boundary-spanning</t>
+          <t>Linguistic boundary-spanning</t>
         </is>
       </c>
       <c r="AT59" t="n">
-        <v>5.27</v>
+        <v>5.04</v>
       </c>
       <c r="AU59" t="n">
-        <v>0.74</v>
+        <v>1.03</v>
       </c>
       <c r="AV59" t="n">
-        <v>0.96</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AW59" t="n">
-        <v>0.45</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="60" ht="15.75" customHeight="1" s="12">
@@ -8618,7 +8602,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>BSMA0006.1.30</t>
+          <t>BSMA0006.1.32</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -8706,7 +8690,7 @@
         </is>
       </c>
       <c r="AH60" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI60" t="n">
         <v>1</v>
@@ -8745,20 +8729,20 @@
       </c>
       <c r="AS60" t="inlineStr">
         <is>
-          <t>Functional boundary-spanning</t>
+          <t>Cultural boundary-spanning</t>
         </is>
       </c>
       <c r="AT60" t="n">
-        <v>5.51</v>
+        <v>5.22</v>
       </c>
       <c r="AU60" t="n">
-        <v>0.77</v>
+        <v>0.83</v>
       </c>
       <c r="AV60" t="n">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="AW60" t="n">
-        <v>0.36</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="61" ht="15.75" customHeight="1" s="12">
@@ -8779,7 +8763,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>BSMA0006.1.31</t>
+          <t>BSMA0006.1.33</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -8867,7 +8851,7 @@
         </is>
       </c>
       <c r="AH61" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AI61" t="n">
         <v>1</v>
@@ -8877,17 +8861,17 @@
       </c>
       <c r="AK61" t="inlineStr">
         <is>
-          <t>3 = Others (e.g. coworker/peer subordinate customer/client)</t>
+          <t>1 = Self-report</t>
         </is>
       </c>
       <c r="AL61" t="inlineStr">
         <is>
-          <t>host-country coworkers</t>
+          <t>expatriates and coworkers</t>
         </is>
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>Liu et al. (2024)</t>
+          <t>McAllister (1995)</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
@@ -8906,20 +8890,20 @@
       </c>
       <c r="AS61" t="inlineStr">
         <is>
-          <t>Linguistic boundary-spanning</t>
+          <t>Mutual trust</t>
         </is>
       </c>
       <c r="AT61" t="n">
-        <v>5.04</v>
+        <v>5.25</v>
       </c>
       <c r="AU61" t="n">
-        <v>1.03</v>
+        <v>0.68</v>
       </c>
       <c r="AV61" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="AW61" t="n">
-        <v>0.36</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="62" ht="15.75" customHeight="1" s="12">
@@ -8940,7 +8924,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>BSMA0006.1.32</t>
+          <t>BSMA0006.1.34</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -9028,7 +9012,7 @@
         </is>
       </c>
       <c r="AH62" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI62" t="n">
         <v>1</v>
@@ -9038,17 +9022,17 @@
       </c>
       <c r="AK62" t="inlineStr">
         <is>
-          <t>3 = Others (e.g. coworker/peer subordinate customer/client)</t>
+          <t>1 = Self-report</t>
         </is>
       </c>
       <c r="AL62" t="inlineStr">
         <is>
-          <t>host-country coworkers</t>
+          <t>expatriates and coworkers</t>
         </is>
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>Liu et al. (2024)</t>
+          <t>McAllister (1995)</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
@@ -9067,20 +9051,20 @@
       </c>
       <c r="AS62" t="inlineStr">
         <is>
-          <t>Cultural boundary-spanning</t>
+          <t>Cognition-based mutual trust</t>
         </is>
       </c>
       <c r="AT62" t="n">
-        <v>5.22</v>
+        <v>5.38</v>
       </c>
       <c r="AU62" t="n">
-        <v>0.83</v>
+        <v>0.64</v>
       </c>
       <c r="AV62" t="n">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
       <c r="AW62" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="63" ht="15.75" customHeight="1" s="12">
@@ -9101,7 +9085,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>BSMA0006.1.33</t>
+          <t>BSMA0006.1.35</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -9228,17 +9212,17 @@
       </c>
       <c r="AS63" t="inlineStr">
         <is>
-          <t>Mutual trust</t>
+          <t>Affect-based mutual trust</t>
         </is>
       </c>
       <c r="AT63" t="n">
-        <v>5.25</v>
+        <v>5.11</v>
       </c>
       <c r="AU63" t="n">
-        <v>0.68</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AV63" t="n">
-        <v>0.9</v>
+        <v>0.87</v>
       </c>
       <c r="AW63" t="n">
         <v>0.46</v>
@@ -9262,7 +9246,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>BSMA0006.1.34</t>
+          <t>BSMA0006.1.36</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -9350,7 +9334,7 @@
         </is>
       </c>
       <c r="AH64" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AI64" t="n">
         <v>1</v>
@@ -9365,12 +9349,12 @@
       </c>
       <c r="AL64" t="inlineStr">
         <is>
-          <t>expatriates and coworkers</t>
+          <t>expatriates</t>
         </is>
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>McAllister (1995)</t>
+          <t>Rizzo et al. (1970); Beehr et al. (1976)</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
@@ -9389,20 +9373,20 @@
       </c>
       <c r="AS64" t="inlineStr">
         <is>
-          <t>Cognition-based mutual trust</t>
+          <t>Role stressors</t>
         </is>
       </c>
       <c r="AT64" t="n">
-        <v>5.38</v>
+        <v>3.64</v>
       </c>
       <c r="AU64" t="n">
-        <v>0.64</v>
+        <v>0.97</v>
       </c>
       <c r="AV64" t="n">
-        <v>0.8</v>
+        <v>0.93</v>
       </c>
       <c r="AW64" t="n">
-        <v>0.42</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="65" ht="15.75" customHeight="1" s="12">
@@ -9423,7 +9407,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>BSMA0006.1.35</t>
+          <t>BSMA0006.1.37</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -9511,7 +9495,7 @@
         </is>
       </c>
       <c r="AH65" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="AI65" t="n">
         <v>1</v>
@@ -9521,49 +9505,49 @@
       </c>
       <c r="AK65" t="inlineStr">
         <is>
-          <t>1 = Self-report</t>
+          <t>3 = Others (e.g. coworker/peer subordinate customer/client)</t>
         </is>
       </c>
       <c r="AL65" t="inlineStr">
         <is>
-          <t>expatriates and coworkers</t>
+          <t>host-country coworkers</t>
         </is>
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>McAllister (1995)</t>
+          <t>Liu et al. (2024)</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
-          <t>Expatriates’ subsidiary identification</t>
+          <t>Coworkers’ MNE identification</t>
         </is>
       </c>
       <c r="AP65" t="n">
-        <v>5.3</v>
+        <v>5.08</v>
       </c>
       <c r="AQ65" t="n">
-        <v>0.95</v>
+        <v>1.06</v>
       </c>
       <c r="AR65" t="n">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="AS65" t="inlineStr">
         <is>
-          <t>Affect-based mutual trust</t>
+          <t>Expatriates’ boundary-spanning</t>
         </is>
       </c>
       <c r="AT65" t="n">
-        <v>5.11</v>
+        <v>5.27</v>
       </c>
       <c r="AU65" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.74</v>
       </c>
       <c r="AV65" t="n">
-        <v>0.87</v>
+        <v>0.96</v>
       </c>
       <c r="AW65" t="n">
-        <v>0.46</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="66" ht="15.75" customHeight="1" s="12">
@@ -9584,7 +9568,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>BSMA0006.1.36</t>
+          <t>BSMA0006.1.38</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -9672,7 +9656,7 @@
         </is>
       </c>
       <c r="AH66" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="AI66" t="n">
         <v>1</v>
@@ -9682,49 +9666,49 @@
       </c>
       <c r="AK66" t="inlineStr">
         <is>
-          <t>1 = Self-report</t>
+          <t>3 = Others (e.g. coworker/peer subordinate customer/client)</t>
         </is>
       </c>
       <c r="AL66" t="inlineStr">
         <is>
-          <t>expatriates</t>
+          <t>host-country coworkers</t>
         </is>
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>Rizzo et al. (1970); Beehr et al. (1976)</t>
+          <t>Liu et al. (2024)</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>Expatriates’ subsidiary identification</t>
+          <t>Coworkers’ MNE identification</t>
         </is>
       </c>
       <c r="AP66" t="n">
-        <v>5.3</v>
+        <v>5.08</v>
       </c>
       <c r="AQ66" t="n">
-        <v>0.95</v>
+        <v>1.06</v>
       </c>
       <c r="AR66" t="n">
-        <v>0.92</v>
+        <v>0.9</v>
       </c>
       <c r="AS66" t="inlineStr">
         <is>
-          <t>Role stressors</t>
+          <t>Functional boundary-spanning</t>
         </is>
       </c>
       <c r="AT66" t="n">
-        <v>3.64</v>
+        <v>5.51</v>
       </c>
       <c r="AU66" t="n">
-        <v>0.97</v>
+        <v>0.77</v>
       </c>
       <c r="AV66" t="n">
-        <v>0.93</v>
+        <v>0.91</v>
       </c>
       <c r="AW66" t="n">
-        <v>0.18</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="67" ht="15.75" customHeight="1" s="12">
@@ -9745,7 +9729,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>BSMA0006.1.37</t>
+          <t>BSMA0006.1.39</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -9833,7 +9817,7 @@
         </is>
       </c>
       <c r="AH67" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="AI67" t="n">
         <v>1</v>
@@ -9872,20 +9856,20 @@
       </c>
       <c r="AS67" t="inlineStr">
         <is>
-          <t>Expatriates’ boundary-spanning</t>
+          <t>Linguistic boundary-spanning</t>
         </is>
       </c>
       <c r="AT67" t="n">
-        <v>5.27</v>
+        <v>5.04</v>
       </c>
       <c r="AU67" t="n">
-        <v>0.74</v>
+        <v>1.03</v>
       </c>
       <c r="AV67" t="n">
-        <v>0.96</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AW67" t="n">
-        <v>0.52</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="68" ht="15.75" customHeight="1" s="12">
@@ -9906,7 +9890,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>BSMA0006.1.38</t>
+          <t>BSMA0006.1.40</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -9994,7 +9978,7 @@
         </is>
       </c>
       <c r="AH68" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI68" t="n">
         <v>1</v>
@@ -10033,20 +10017,20 @@
       </c>
       <c r="AS68" t="inlineStr">
         <is>
-          <t>Functional boundary-spanning</t>
+          <t>Cultural boundary-spanning</t>
         </is>
       </c>
       <c r="AT68" t="n">
-        <v>5.51</v>
+        <v>5.22</v>
       </c>
       <c r="AU68" t="n">
-        <v>0.77</v>
+        <v>0.83</v>
       </c>
       <c r="AV68" t="n">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="AW68" t="n">
-        <v>0.35</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="69" ht="15.75" customHeight="1" s="12">
@@ -10067,7 +10051,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>BSMA0006.1.39</t>
+          <t>BSMA0006.1.41</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -10155,7 +10139,7 @@
         </is>
       </c>
       <c r="AH69" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AI69" t="n">
         <v>1</v>
@@ -10165,17 +10149,17 @@
       </c>
       <c r="AK69" t="inlineStr">
         <is>
-          <t>3 = Others (e.g. coworker/peer subordinate customer/client)</t>
+          <t>1 = Self-report</t>
         </is>
       </c>
       <c r="AL69" t="inlineStr">
         <is>
-          <t>host-country coworkers</t>
+          <t>expatriates and coworkers</t>
         </is>
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>Liu et al. (2024)</t>
+          <t>McAllister (1995)</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
@@ -10194,20 +10178,20 @@
       </c>
       <c r="AS69" t="inlineStr">
         <is>
-          <t>Linguistic boundary-spanning</t>
+          <t>Mutual trust</t>
         </is>
       </c>
       <c r="AT69" t="n">
-        <v>5.04</v>
+        <v>5.25</v>
       </c>
       <c r="AU69" t="n">
-        <v>1.03</v>
+        <v>0.68</v>
       </c>
       <c r="AV69" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="AW69" t="n">
-        <v>0.45</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="70" ht="15.75" customHeight="1" s="12">
@@ -10228,7 +10212,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>BSMA0006.1.40</t>
+          <t>BSMA0006.1.42</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -10316,7 +10300,7 @@
         </is>
       </c>
       <c r="AH70" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI70" t="n">
         <v>1</v>
@@ -10326,17 +10310,17 @@
       </c>
       <c r="AK70" t="inlineStr">
         <is>
-          <t>3 = Others (e.g. coworker/peer subordinate customer/client)</t>
+          <t>1 = Self-report</t>
         </is>
       </c>
       <c r="AL70" t="inlineStr">
         <is>
-          <t>host-country coworkers</t>
+          <t>expatriates and coworkers</t>
         </is>
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>Liu et al. (2024)</t>
+          <t>McAllister (1995)</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
@@ -10355,20 +10339,20 @@
       </c>
       <c r="AS70" t="inlineStr">
         <is>
-          <t>Cultural boundary-spanning</t>
+          <t>Cognition-based mutual trust</t>
         </is>
       </c>
       <c r="AT70" t="n">
-        <v>5.22</v>
+        <v>5.38</v>
       </c>
       <c r="AU70" t="n">
-        <v>0.83</v>
+        <v>0.64</v>
       </c>
       <c r="AV70" t="n">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
       <c r="AW70" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1" s="12">
@@ -10389,7 +10373,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>BSMA0006.1.41</t>
+          <t>BSMA0006.1.43</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -10516,20 +10500,20 @@
       </c>
       <c r="AS71" t="inlineStr">
         <is>
-          <t>Mutual trust</t>
+          <t>Affect-based mutual trust</t>
         </is>
       </c>
       <c r="AT71" t="n">
-        <v>5.25</v>
+        <v>5.11</v>
       </c>
       <c r="AU71" t="n">
-        <v>0.68</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AV71" t="n">
-        <v>0.9</v>
+        <v>0.87</v>
       </c>
       <c r="AW71" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="72" ht="15.75" customHeight="1" s="12">
@@ -10550,7 +10534,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>BSMA0006.1.42</t>
+          <t>BSMA0006.1.44</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -10638,7 +10622,7 @@
         </is>
       </c>
       <c r="AH72" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AI72" t="n">
         <v>1</v>
@@ -10653,12 +10637,12 @@
       </c>
       <c r="AL72" t="inlineStr">
         <is>
-          <t>expatriates and coworkers</t>
+          <t>expatriates</t>
         </is>
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>McAllister (1995)</t>
+          <t>Rizzo et al. (1970); Beehr et al. (1976)</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
@@ -10677,20 +10661,20 @@
       </c>
       <c r="AS72" t="inlineStr">
         <is>
-          <t>Cognition-based mutual trust</t>
+          <t>Role stressors</t>
         </is>
       </c>
       <c r="AT72" t="n">
-        <v>5.38</v>
+        <v>3.64</v>
       </c>
       <c r="AU72" t="n">
-        <v>0.64</v>
+        <v>0.97</v>
       </c>
       <c r="AV72" t="n">
-        <v>0.8</v>
+        <v>0.93</v>
       </c>
       <c r="AW72" t="n">
-        <v>0.54</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="73" ht="15.75" customHeight="1" s="12">
@@ -10711,7 +10695,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>BSMA0006.1.43</t>
+          <t>BSMA0006.1.45</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -10799,7 +10783,7 @@
         </is>
       </c>
       <c r="AH73" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AI73" t="n">
         <v>1</v>
@@ -10814,12 +10798,12 @@
       </c>
       <c r="AL73" t="inlineStr">
         <is>
-          <t>expatriates and coworkers</t>
+          <t>expatriates</t>
         </is>
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>McAllister (1995)</t>
+          <t>Mael &amp; Ashforth (1992)</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
@@ -10838,20 +10822,20 @@
       </c>
       <c r="AS73" t="inlineStr">
         <is>
-          <t>Affect-based mutual trust</t>
+          <t>Expatriates’ subsidiary identification</t>
         </is>
       </c>
       <c r="AT73" t="n">
-        <v>5.11</v>
+        <v>5.3</v>
       </c>
       <c r="AU73" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.95</v>
       </c>
       <c r="AV73" t="n">
-        <v>0.87</v>
+        <v>0.92</v>
       </c>
       <c r="AW73" t="n">
-        <v>0.53</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="74" ht="15.75" customHeight="1" s="12">
@@ -10872,7 +10856,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>BSMA0006.1.44</t>
+          <t>BSMA0006.1.46</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -10960,7 +10944,7 @@
         </is>
       </c>
       <c r="AH74" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="AI74" t="n">
         <v>1</v>
@@ -10970,49 +10954,49 @@
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>1 = Self-report</t>
+          <t>3 = Others (e.g. coworker/peer subordinate customer/client)</t>
         </is>
       </c>
       <c r="AL74" t="inlineStr">
         <is>
-          <t>expatriates</t>
+          <t>host-country coworkers</t>
         </is>
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>Rizzo et al. (1970); Beehr et al. (1976)</t>
+          <t>Liu et al. (2024)</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Coworkers’ MNE identification</t>
+          <t>Expatriates’ emotional exhaustion</t>
         </is>
       </c>
       <c r="AP74" t="n">
-        <v>5.08</v>
+        <v>3.63</v>
       </c>
       <c r="AQ74" t="n">
-        <v>1.06</v>
+        <v>1.49</v>
       </c>
       <c r="AR74" t="n">
-        <v>0.9</v>
+        <v>0.97</v>
       </c>
       <c r="AS74" t="inlineStr">
         <is>
-          <t>Role stressors</t>
+          <t>Expatriates’ boundary-spanning</t>
         </is>
       </c>
       <c r="AT74" t="n">
-        <v>3.64</v>
+        <v>5.27</v>
       </c>
       <c r="AU74" t="n">
-        <v>0.97</v>
+        <v>0.74</v>
       </c>
       <c r="AV74" t="n">
-        <v>0.93</v>
+        <v>0.96</v>
       </c>
       <c r="AW74" t="n">
-        <v>0.03</v>
+        <v>-0.01</v>
       </c>
     </row>
     <row r="75" ht="15.75" customHeight="1" s="12">
@@ -11033,7 +11017,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>BSMA0006.1.45</t>
+          <t>BSMA0006.1.47</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -11121,7 +11105,7 @@
         </is>
       </c>
       <c r="AH75" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AI75" t="n">
         <v>1</v>
@@ -11131,49 +11115,49 @@
       </c>
       <c r="AK75" t="inlineStr">
         <is>
-          <t>1 = Self-report</t>
+          <t>3 = Others (e.g. coworker/peer subordinate customer/client)</t>
         </is>
       </c>
       <c r="AL75" t="inlineStr">
         <is>
-          <t>expatriates</t>
+          <t>host-country coworkers</t>
         </is>
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>Mael &amp; Ashforth (1992)</t>
+          <t>Liu et al. (2024)</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
-          <t>Coworkers’ MNE identification</t>
+          <t>Expatriates’ emotional exhaustion</t>
         </is>
       </c>
       <c r="AP75" t="n">
-        <v>5.08</v>
+        <v>3.63</v>
       </c>
       <c r="AQ75" t="n">
-        <v>1.06</v>
+        <v>1.49</v>
       </c>
       <c r="AR75" t="n">
-        <v>0.9</v>
+        <v>0.97</v>
       </c>
       <c r="AS75" t="inlineStr">
         <is>
-          <t>Expatriates’ subsidiary identification</t>
+          <t>Functional boundary-spanning</t>
         </is>
       </c>
       <c r="AT75" t="n">
-        <v>5.3</v>
+        <v>5.51</v>
       </c>
       <c r="AU75" t="n">
-        <v>0.95</v>
+        <v>0.77</v>
       </c>
       <c r="AV75" t="n">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="AW75" t="n">
-        <v>0.27</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="76" ht="15.75" customHeight="1" s="12">
@@ -11194,7 +11178,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>BSMA0006.1.46</t>
+          <t>BSMA0006.1.48</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -11282,7 +11266,7 @@
         </is>
       </c>
       <c r="AH76" t="n">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="AI76" t="n">
         <v>1</v>
@@ -11321,20 +11305,20 @@
       </c>
       <c r="AS76" t="inlineStr">
         <is>
-          <t>Expatriates’ boundary-spanning</t>
+          <t>Linguistic boundary-spanning</t>
         </is>
       </c>
       <c r="AT76" t="n">
-        <v>5.27</v>
+        <v>5.04</v>
       </c>
       <c r="AU76" t="n">
-        <v>0.74</v>
+        <v>1.03</v>
       </c>
       <c r="AV76" t="n">
-        <v>0.96</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AW76" t="n">
-        <v>-0.01</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="77" ht="15.75" customHeight="1" s="12">
@@ -11355,7 +11339,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>BSMA0006.1.47</t>
+          <t>BSMA0006.1.49</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -11443,7 +11427,7 @@
         </is>
       </c>
       <c r="AH77" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI77" t="n">
         <v>1</v>
@@ -11482,20 +11466,20 @@
       </c>
       <c r="AS77" t="inlineStr">
         <is>
-          <t>Functional boundary-spanning</t>
+          <t>Cultural boundary-spanning</t>
         </is>
       </c>
       <c r="AT77" t="n">
-        <v>5.51</v>
+        <v>5.22</v>
       </c>
       <c r="AU77" t="n">
-        <v>0.77</v>
+        <v>0.83</v>
       </c>
       <c r="AV77" t="n">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="AW77" t="n">
-        <v>0.19</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="78" ht="15.75" customHeight="1" s="12">
@@ -11516,7 +11500,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>BSMA0006.1.48</t>
+          <t>BSMA0006.1.50</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -11604,7 +11588,7 @@
         </is>
       </c>
       <c r="AH78" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AI78" t="n">
         <v>1</v>
@@ -11614,17 +11598,17 @@
       </c>
       <c r="AK78" t="inlineStr">
         <is>
-          <t>3 = Others (e.g. coworker/peer subordinate customer/client)</t>
+          <t>1 = Self-report</t>
         </is>
       </c>
       <c r="AL78" t="inlineStr">
         <is>
-          <t>host-country coworkers</t>
+          <t>expatriates and coworkers</t>
         </is>
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>Liu et al. (2024)</t>
+          <t>McAllister (1995)</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
@@ -11643,20 +11627,20 @@
       </c>
       <c r="AS78" t="inlineStr">
         <is>
-          <t>Linguistic boundary-spanning</t>
+          <t>Mutual trust</t>
         </is>
       </c>
       <c r="AT78" t="n">
-        <v>5.04</v>
+        <v>5.25</v>
       </c>
       <c r="AU78" t="n">
-        <v>1.03</v>
+        <v>0.68</v>
       </c>
       <c r="AV78" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="AW78" t="n">
-        <v>-0.15</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="79" ht="15.75" customHeight="1" s="12">
@@ -11677,7 +11661,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>BSMA0006.1.49</t>
+          <t>BSMA0006.1.51</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -11765,7 +11749,7 @@
         </is>
       </c>
       <c r="AH79" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI79" t="n">
         <v>1</v>
@@ -11775,17 +11759,17 @@
       </c>
       <c r="AK79" t="inlineStr">
         <is>
-          <t>3 = Others (e.g. coworker/peer subordinate customer/client)</t>
+          <t>1 = Self-report</t>
         </is>
       </c>
       <c r="AL79" t="inlineStr">
         <is>
-          <t>host-country coworkers</t>
+          <t>expatriates and coworkers</t>
         </is>
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>Liu et al. (2024)</t>
+          <t>McAllister (1995)</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
@@ -11804,20 +11788,20 @@
       </c>
       <c r="AS79" t="inlineStr">
         <is>
-          <t>Cultural boundary-spanning</t>
+          <t>Cognition-based mutual trust</t>
         </is>
       </c>
       <c r="AT79" t="n">
-        <v>5.22</v>
+        <v>5.38</v>
       </c>
       <c r="AU79" t="n">
-        <v>0.83</v>
+        <v>0.64</v>
       </c>
       <c r="AV79" t="n">
-        <v>0.95</v>
+        <v>0.8</v>
       </c>
       <c r="AW79" t="n">
-        <v>-0.05</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="80" ht="15.75" customHeight="1" s="12">
@@ -11838,7 +11822,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>BSMA0006.1.50</t>
+          <t>BSMA0006.1.52</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -11965,20 +11949,20 @@
       </c>
       <c r="AS80" t="inlineStr">
         <is>
-          <t>Mutual trust</t>
+          <t>Affect-based mutual trust</t>
         </is>
       </c>
       <c r="AT80" t="n">
-        <v>5.25</v>
+        <v>5.11</v>
       </c>
       <c r="AU80" t="n">
-        <v>0.68</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AV80" t="n">
-        <v>0.9</v>
+        <v>0.87</v>
       </c>
       <c r="AW80" t="n">
-        <v>-0.19</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="81" ht="15.75" customHeight="1" s="12">
@@ -11999,7 +11983,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>BSMA0006.1.51</t>
+          <t>BSMA0006.1.53</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -12087,7 +12071,7 @@
         </is>
       </c>
       <c r="AH81" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AI81" t="n">
         <v>1</v>
@@ -12102,12 +12086,12 @@
       </c>
       <c r="AL81" t="inlineStr">
         <is>
-          <t>expatriates and coworkers</t>
+          <t>expatriates</t>
         </is>
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>McAllister (1995)</t>
+          <t>Rizzo et al. (1970); Beehr et al. (1976)</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
@@ -12126,20 +12110,20 @@
       </c>
       <c r="AS81" t="inlineStr">
         <is>
-          <t>Cognition-based mutual trust</t>
+          <t>Role stressors</t>
         </is>
       </c>
       <c r="AT81" t="n">
-        <v>5.38</v>
+        <v>3.64</v>
       </c>
       <c r="AU81" t="n">
-        <v>0.64</v>
+        <v>0.97</v>
       </c>
       <c r="AV81" t="n">
-        <v>0.8</v>
+        <v>0.93</v>
       </c>
       <c r="AW81" t="n">
-        <v>-0.12</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="82" ht="15.75" customHeight="1" s="12">
@@ -12160,7 +12144,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>BSMA0006.1.52</t>
+          <t>BSMA0006.1.54</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -12248,7 +12232,7 @@
         </is>
       </c>
       <c r="AH82" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AI82" t="n">
         <v>1</v>
@@ -12263,12 +12247,12 @@
       </c>
       <c r="AL82" t="inlineStr">
         <is>
-          <t>expatriates and coworkers</t>
+          <t>expatriates</t>
         </is>
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>McAllister (1995)</t>
+          <t>Mael &amp; Ashforth (1992)</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
@@ -12287,20 +12271,20 @@
       </c>
       <c r="AS82" t="inlineStr">
         <is>
-          <t>Affect-based mutual trust</t>
+          <t>Expatriates’ subsidiary identification</t>
         </is>
       </c>
       <c r="AT82" t="n">
-        <v>5.11</v>
+        <v>5.3</v>
       </c>
       <c r="AU82" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.95</v>
       </c>
       <c r="AV82" t="n">
-        <v>0.87</v>
+        <v>0.92</v>
       </c>
       <c r="AW82" t="n">
-        <v>-0.24</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="83" ht="15.75" customHeight="1" s="12">
@@ -12321,7 +12305,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>BSMA0006.1.53</t>
+          <t>BSMA0006.1.56</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -12409,7 +12393,7 @@
         </is>
       </c>
       <c r="AH83" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="AI83" t="n">
         <v>1</v>
@@ -12419,49 +12403,49 @@
       </c>
       <c r="AK83" t="inlineStr">
         <is>
-          <t>1 = Self-report</t>
+          <t>3 = Others (e.g. coworker/peer subordinate customer/client)</t>
         </is>
       </c>
       <c r="AL83" t="inlineStr">
         <is>
-          <t>expatriates</t>
+          <t>host-country coworkers</t>
         </is>
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>Rizzo et al. (1970); Beehr et al. (1976)</t>
+          <t>Liu et al. (2024)</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>Expatriates’ emotional exhaustion</t>
+          <t>Expatriates’ outgroup categorization</t>
         </is>
       </c>
       <c r="AP83" t="n">
-        <v>3.63</v>
+        <v>4.35</v>
       </c>
       <c r="AQ83" t="n">
-        <v>1.49</v>
+        <v>0.97</v>
       </c>
       <c r="AR83" t="n">
-        <v>0.97</v>
+        <v>0.83</v>
       </c>
       <c r="AS83" t="inlineStr">
         <is>
-          <t>Role stressors</t>
+          <t>Expatriates’ boundary-spanning</t>
         </is>
       </c>
       <c r="AT83" t="n">
-        <v>3.64</v>
+        <v>5.27</v>
       </c>
       <c r="AU83" t="n">
-        <v>0.97</v>
+        <v>0.74</v>
       </c>
       <c r="AV83" t="n">
-        <v>0.93</v>
+        <v>0.96</v>
       </c>
       <c r="AW83" t="n">
-        <v>0.38</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="84" ht="15.75" customHeight="1" s="12">
@@ -12482,7 +12466,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>BSMA0006.1.54</t>
+          <t>BSMA0006.1.57</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -12570,7 +12554,7 @@
         </is>
       </c>
       <c r="AH84" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AI84" t="n">
         <v>1</v>
@@ -12580,49 +12564,49 @@
       </c>
       <c r="AK84" t="inlineStr">
         <is>
-          <t>1 = Self-report</t>
+          <t>3 = Others (e.g. coworker/peer subordinate customer/client)</t>
         </is>
       </c>
       <c r="AL84" t="inlineStr">
         <is>
-          <t>expatriates</t>
+          <t>host-country coworkers</t>
         </is>
       </c>
       <c r="AM84" t="inlineStr">
         <is>
-          <t>Mael &amp; Ashforth (1992)</t>
+          <t>Liu et al. (2024)</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
-          <t>Expatriates’ emotional exhaustion</t>
+          <t>Expatriates’ outgroup categorization</t>
         </is>
       </c>
       <c r="AP84" t="n">
-        <v>3.63</v>
+        <v>4.35</v>
       </c>
       <c r="AQ84" t="n">
-        <v>1.49</v>
+        <v>0.97</v>
       </c>
       <c r="AR84" t="n">
-        <v>0.97</v>
+        <v>0.83</v>
       </c>
       <c r="AS84" t="inlineStr">
         <is>
-          <t>Expatriates’ subsidiary identification</t>
+          <t>Functional boundary-spanning</t>
         </is>
       </c>
       <c r="AT84" t="n">
-        <v>5.3</v>
+        <v>5.51</v>
       </c>
       <c r="AU84" t="n">
-        <v>0.95</v>
+        <v>0.77</v>
       </c>
       <c r="AV84" t="n">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="AW84" t="n">
-        <v>-0.21</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="85" ht="15.75" customHeight="1" s="12">
@@ -12643,7 +12627,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>BSMA0006.1.55</t>
+          <t>BSMA0006.1.58</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -12731,7 +12715,7 @@
         </is>
       </c>
       <c r="AH85" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI85" t="n">
         <v>1</v>
@@ -12746,44 +12730,44 @@
       </c>
       <c r="AL85" t="inlineStr">
         <is>
-          <t>coworkers</t>
+          <t>host-country coworkers</t>
         </is>
       </c>
       <c r="AM85" t="inlineStr">
         <is>
-          <t>Mael &amp; Ashforth (1992)</t>
+          <t>Liu et al. (2024)</t>
         </is>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>Expatriates’ emotional exhaustion</t>
+          <t>Expatriates’ outgroup categorization</t>
         </is>
       </c>
       <c r="AP85" t="n">
-        <v>3.63</v>
+        <v>4.35</v>
       </c>
       <c r="AQ85" t="n">
-        <v>1.49</v>
+        <v>0.97</v>
       </c>
       <c r="AR85" t="n">
-        <v>0.97</v>
+        <v>0.83</v>
       </c>
       <c r="AS85" t="inlineStr">
         <is>
-          <t>Coworkers’ MNE identification</t>
+          <t>Linguistic boundary-spanning</t>
         </is>
       </c>
       <c r="AT85" t="n">
-        <v>5.08</v>
+        <v>5.04</v>
       </c>
       <c r="AU85" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AV85" t="n">
-        <v>0.9</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AW85" t="n">
-        <v>-0.21</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="86" ht="15.75" customHeight="1" s="12">
@@ -12804,7 +12788,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>BSMA0006.1.56</t>
+          <t>BSMA0006.1.59</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -12892,7 +12876,7 @@
         </is>
       </c>
       <c r="AH86" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="AI86" t="n">
         <v>1</v>
@@ -12931,20 +12915,20 @@
       </c>
       <c r="AS86" t="inlineStr">
         <is>
-          <t>Expatriates’ boundary-spanning</t>
+          <t>Cultural boundary-spanning</t>
         </is>
       </c>
       <c r="AT86" t="n">
-        <v>5.27</v>
+        <v>5.22</v>
       </c>
       <c r="AU86" t="n">
-        <v>0.74</v>
+        <v>0.83</v>
       </c>
       <c r="AV86" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="AW86" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="87" ht="15.75" customHeight="1" s="12">
@@ -12965,7 +12949,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>BSMA0006.1.57</t>
+          <t>BSMA0006.1.60</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -13053,7 +13037,7 @@
         </is>
       </c>
       <c r="AH87" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AI87" t="n">
         <v>1</v>
@@ -13063,17 +13047,17 @@
       </c>
       <c r="AK87" t="inlineStr">
         <is>
-          <t>3 = Others (e.g. coworker/peer subordinate customer/client)</t>
+          <t>1 = Self-report</t>
         </is>
       </c>
       <c r="AL87" t="inlineStr">
         <is>
-          <t>host-country coworkers</t>
+          <t>expatriates and coworkers</t>
         </is>
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>Liu et al. (2024)</t>
+          <t>McAllister (1995)</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
@@ -13092,20 +13076,20 @@
       </c>
       <c r="AS87" t="inlineStr">
         <is>
-          <t>Functional boundary-spanning</t>
+          <t>Mutual trust</t>
         </is>
       </c>
       <c r="AT87" t="n">
-        <v>5.51</v>
+        <v>5.25</v>
       </c>
       <c r="AU87" t="n">
-        <v>0.77</v>
+        <v>0.68</v>
       </c>
       <c r="AV87" t="n">
-        <v>0.91</v>
+        <v>0.9</v>
       </c>
       <c r="AW87" t="n">
-        <v>0.36</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="88" ht="15.75" customHeight="1" s="12">
@@ -13126,7 +13110,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>BSMA0006.1.58</t>
+          <t>BSMA0006.1.61</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -13214,7 +13198,7 @@
         </is>
       </c>
       <c r="AH88" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AI88" t="n">
         <v>1</v>
@@ -13224,17 +13208,17 @@
       </c>
       <c r="AK88" t="inlineStr">
         <is>
-          <t>3 = Others (e.g. coworker/peer subordinate customer/client)</t>
+          <t>1 = Self-report</t>
         </is>
       </c>
       <c r="AL88" t="inlineStr">
         <is>
-          <t>host-country coworkers</t>
+          <t>expatriates and coworkers</t>
         </is>
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>Liu et al. (2024)</t>
+          <t>McAllister (1995)</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
@@ -13253,20 +13237,20 @@
       </c>
       <c r="AS88" t="inlineStr">
         <is>
-          <t>Linguistic boundary-spanning</t>
+          <t>Cognition-based mutual trust</t>
         </is>
       </c>
       <c r="AT88" t="n">
-        <v>5.04</v>
+        <v>5.38</v>
       </c>
       <c r="AU88" t="n">
-        <v>1.03</v>
+        <v>0.64</v>
       </c>
       <c r="AV88" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="AW88" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="89" ht="15.75" customHeight="1" s="12">
@@ -13287,7 +13271,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>BSMA0006.1.59</t>
+          <t>BSMA0006.1.62</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -13375,7 +13359,7 @@
         </is>
       </c>
       <c r="AH89" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI89" t="n">
         <v>1</v>
@@ -13385,17 +13369,17 @@
       </c>
       <c r="AK89" t="inlineStr">
         <is>
-          <t>3 = Others (e.g. coworker/peer subordinate customer/client)</t>
+          <t>1 = Self-report</t>
         </is>
       </c>
       <c r="AL89" t="inlineStr">
         <is>
-          <t>host-country coworkers</t>
+          <t>expatriates and coworkers</t>
         </is>
       </c>
       <c r="AM89" t="inlineStr">
         <is>
-          <t>Liu et al. (2024)</t>
+          <t>McAllister (1995)</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
@@ -13414,20 +13398,20 @@
       </c>
       <c r="AS89" t="inlineStr">
         <is>
-          <t>Cultural boundary-spanning</t>
+          <t>Affect-based mutual trust</t>
         </is>
       </c>
       <c r="AT89" t="n">
-        <v>5.22</v>
+        <v>5.11</v>
       </c>
       <c r="AU89" t="n">
-        <v>0.83</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AV89" t="n">
-        <v>0.95</v>
+        <v>0.87</v>
       </c>
       <c r="AW89" t="n">
-        <v>0.22</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="90" ht="15.75" customHeight="1" s="12">
@@ -13448,7 +13432,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>BSMA0006.1.60</t>
+          <t>BSMA0006.1.63</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -13536,7 +13520,7 @@
         </is>
       </c>
       <c r="AH90" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AI90" t="n">
         <v>1</v>
@@ -13551,12 +13535,12 @@
       </c>
       <c r="AL90" t="inlineStr">
         <is>
-          <t>expatriates and coworkers</t>
+          <t>expatriates</t>
         </is>
       </c>
       <c r="AM90" t="inlineStr">
         <is>
-          <t>McAllister (1995)</t>
+          <t>Rizzo et al. (1970); Beehr et al. (1976)</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
@@ -13575,20 +13559,20 @@
       </c>
       <c r="AS90" t="inlineStr">
         <is>
-          <t>Mutual trust</t>
+          <t>Role stressors</t>
         </is>
       </c>
       <c r="AT90" t="n">
-        <v>5.25</v>
+        <v>3.64</v>
       </c>
       <c r="AU90" t="n">
-        <v>0.68</v>
+        <v>0.97</v>
       </c>
       <c r="AV90" t="n">
-        <v>0.9</v>
+        <v>0.93</v>
       </c>
       <c r="AW90" t="n">
-        <v>0.08</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="91" ht="15.75" customHeight="1" s="12">
@@ -13609,7 +13593,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>BSMA0006.1.61</t>
+          <t>BSMA0006.1.64</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -13697,7 +13681,7 @@
         </is>
       </c>
       <c r="AH91" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AI91" t="n">
         <v>1</v>
@@ -13712,12 +13696,12 @@
       </c>
       <c r="AL91" t="inlineStr">
         <is>
-          <t>expatriates and coworkers</t>
+          <t>expatriates</t>
         </is>
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>McAllister (1995)</t>
+          <t>Mael &amp; Ashforth (1992)</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
@@ -13736,20 +13720,20 @@
       </c>
       <c r="AS91" t="inlineStr">
         <is>
-          <t>Cognition-based mutual trust</t>
+          <t>Expatriates’ subsidiary identification</t>
         </is>
       </c>
       <c r="AT91" t="n">
-        <v>5.38</v>
+        <v>5.3</v>
       </c>
       <c r="AU91" t="n">
-        <v>0.64</v>
+        <v>0.95</v>
       </c>
       <c r="AV91" t="n">
-        <v>0.8</v>
+        <v>0.92</v>
       </c>
       <c r="AW91" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="92" ht="15.75" customHeight="1" s="12">
@@ -13770,7 +13754,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>BSMA0006.1.62</t>
+          <t>BSMA0006.1.66</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -13858,7 +13842,7 @@
         </is>
       </c>
       <c r="AH92" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AI92" t="n">
         <v>1</v>
@@ -13873,12 +13857,12 @@
       </c>
       <c r="AL92" t="inlineStr">
         <is>
-          <t>expatriates and coworkers</t>
+          <t>expatriates</t>
         </is>
       </c>
       <c r="AM92" t="inlineStr">
         <is>
-          <t>McAllister (1995)</t>
+          <t>Maslach &amp; Jackson (1981)</t>
         </is>
       </c>
       <c r="AO92" t="inlineStr">
@@ -13897,183 +13881,23 @@
       </c>
       <c r="AS92" t="inlineStr">
         <is>
-          <t>Affect-based mutual trust</t>
+          <t>Expatriates’ emotional exhaustion</t>
         </is>
       </c>
       <c r="AT92" t="n">
-        <v>5.11</v>
+        <v>3.63</v>
       </c>
       <c r="AU92" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.49</v>
       </c>
       <c r="AV92" t="n">
-        <v>0.87</v>
+        <v>0.97</v>
       </c>
       <c r="AW92" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.28</v>
       </c>
     </row>
-    <row r="93" ht="15.75" customHeight="1" s="12">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>KY</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>BSMA0006</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>BSMA0006.1</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>BSMA0006.1.63</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>1 = Include</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Expatriates' boundary-spanning: double-edged effects in multinational enterprises</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>Journal of International Business Studies</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>Liu, T., Sekiguchi, T., Qin, J., &amp; Shen, Y. X.</t>
-        </is>
-      </c>
-      <c r="K93" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>1 = Journal article</t>
-        </is>
-      </c>
-      <c r="Q93" t="inlineStr">
-        <is>
-          <t>2 = Longitudinal</t>
-        </is>
-      </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="U93" t="inlineStr">
-        <is>
-          <t>2 = Yes (international)</t>
-        </is>
-      </c>
-      <c r="V93" t="n">
-        <v>177</v>
-      </c>
-      <c r="W93" t="n">
-        <v>33.91</v>
-      </c>
-      <c r="X93" t="n">
-        <v>50.28</v>
-      </c>
-      <c r="Y93" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>Expatriate employees and host-country coworkers in energy engineering MNEs</t>
-        </is>
-      </c>
-      <c r="AA93" t="n">
-        <v>26</v>
-      </c>
-      <c r="AB93" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC93" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD93" t="inlineStr">
-        <is>
-          <t>3 = Others (e.g. coworker/peer subordinate customer/client)</t>
-        </is>
-      </c>
-      <c r="AE93" t="inlineStr">
-        <is>
-          <t>host-country coworkers</t>
-        </is>
-      </c>
-      <c r="AF93" t="inlineStr">
-        <is>
-          <t>Liu et al. (2024) - newly developed</t>
-        </is>
-      </c>
-      <c r="AH93" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI93" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ93" t="n">
-        <v>7</v>
-      </c>
-      <c r="AK93" t="inlineStr">
-        <is>
-          <t>1 = Self-report</t>
-        </is>
-      </c>
-      <c r="AL93" t="inlineStr">
-        <is>
-          <t>expatriates</t>
-        </is>
-      </c>
-      <c r="AM93" t="inlineStr">
-        <is>
-          <t>Rizzo et al. (1970); Beehr et al. (1976)</t>
-        </is>
-      </c>
-      <c r="AO93" t="inlineStr">
-        <is>
-          <t>Expatriates’ outgroup categorization</t>
-        </is>
-      </c>
-      <c r="AP93" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="AQ93" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="AR93" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="AS93" t="inlineStr">
-        <is>
-          <t>Role stressors</t>
-        </is>
-      </c>
-      <c r="AT93" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="AU93" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="AV93" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="AW93" t="n">
-        <v>0.44</v>
-      </c>
-    </row>
+    <row r="93" ht="15.75" customHeight="1" s="12"/>
     <row r="94" ht="15.75" customHeight="1" s="12">
       <c r="A94" t="inlineStr">
         <is>
@@ -14082,320 +13906,31 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>BSMA0006</t>
+          <t>BSMA0007</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>BSMA0006.1</t>
+          <t>BSMA0007.1</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>BSMA0006.1.64</t>
+          <t>BSMA0007.1.1</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>1 = Include</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>Expatriates' boundary-spanning: double-edged effects in multinational enterprises</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>Journal of International Business Studies</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>Liu, T., Sekiguchi, T., Qin, J., &amp; Shen, Y. X.</t>
-        </is>
-      </c>
-      <c r="K94" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L94" t="inlineStr">
-        <is>
-          <t>1 = Journal article</t>
-        </is>
-      </c>
-      <c r="Q94" t="inlineStr">
-        <is>
-          <t>2 = Longitudinal</t>
-        </is>
-      </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="U94" t="inlineStr">
-        <is>
-          <t>2 = Yes (international)</t>
-        </is>
-      </c>
-      <c r="V94" t="n">
-        <v>177</v>
-      </c>
-      <c r="W94" t="n">
-        <v>33.91</v>
-      </c>
-      <c r="X94" t="n">
-        <v>50.28</v>
-      </c>
-      <c r="Y94" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>Expatriate employees and host-country coworkers in energy engineering MNEs</t>
-        </is>
-      </c>
-      <c r="AA94" t="n">
-        <v>26</v>
-      </c>
-      <c r="AB94" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC94" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD94" t="inlineStr">
-        <is>
-          <t>3 = Others (e.g. coworker/peer subordinate customer/client)</t>
-        </is>
-      </c>
-      <c r="AE94" t="inlineStr">
-        <is>
-          <t>host-country coworkers</t>
-        </is>
-      </c>
-      <c r="AF94" t="inlineStr">
-        <is>
-          <t>Liu et al. (2024) - newly developed</t>
-        </is>
-      </c>
-      <c r="AH94" t="n">
-        <v>6</v>
-      </c>
-      <c r="AI94" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ94" t="n">
-        <v>7</v>
-      </c>
-      <c r="AK94" t="inlineStr">
-        <is>
-          <t>1 = Self-report</t>
-        </is>
-      </c>
-      <c r="AL94" t="inlineStr">
-        <is>
-          <t>expatriates</t>
-        </is>
-      </c>
-      <c r="AM94" t="inlineStr">
-        <is>
-          <t>Mael &amp; Ashforth (1992)</t>
-        </is>
-      </c>
-      <c r="AO94" t="inlineStr">
-        <is>
-          <t>Expatriates’ outgroup categorization</t>
-        </is>
-      </c>
-      <c r="AP94" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="AQ94" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="AR94" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="AS94" t="inlineStr">
-        <is>
-          <t>Expatriates’ subsidiary identification</t>
-        </is>
-      </c>
-      <c r="AT94" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AU94" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="AV94" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="AW94" t="n">
-        <v>0.12</v>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>4 = Non-primary study / Theoretical paper</t>
+        </is>
       </c>
     </row>
-    <row r="95" ht="15.75" customHeight="1" s="12">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>KY</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>BSMA0006</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>BSMA0006.1</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>BSMA0006.1.65</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>1 = Include</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Expatriates' boundary-spanning: double-edged effects in multinational enterprises</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>Journal of International Business Studies</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>Liu, T., Sekiguchi, T., Qin, J., &amp; Shen, Y. X.</t>
-        </is>
-      </c>
-      <c r="K95" t="n">
-        <v>2024</v>
-      </c>
-      <c r="L95" t="inlineStr">
-        <is>
-          <t>1 = Journal article</t>
-        </is>
-      </c>
-      <c r="Q95" t="inlineStr">
-        <is>
-          <t>2 = Longitudinal</t>
-        </is>
-      </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>China</t>
-        </is>
-      </c>
-      <c r="U95" t="inlineStr">
-        <is>
-          <t>2 = Yes (international)</t>
-        </is>
-      </c>
-      <c r="V95" t="n">
-        <v>177</v>
-      </c>
-      <c r="W95" t="n">
-        <v>33.91</v>
-      </c>
-      <c r="X95" t="n">
-        <v>50.28</v>
-      </c>
-      <c r="Y95" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>Expatriate employees and host-country coworkers in energy engineering MNEs</t>
-        </is>
-      </c>
-      <c r="AA95" t="n">
-        <v>26</v>
-      </c>
-      <c r="AB95" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC95" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD95" t="inlineStr">
-        <is>
-          <t>3 = Others (e.g. coworker/peer subordinate customer/client)</t>
-        </is>
-      </c>
-      <c r="AE95" t="inlineStr">
-        <is>
-          <t>host-country coworkers</t>
-        </is>
-      </c>
-      <c r="AF95" t="inlineStr">
-        <is>
-          <t>Liu et al. (2024) - newly developed</t>
-        </is>
-      </c>
-      <c r="AH95" t="n">
-        <v>6</v>
-      </c>
-      <c r="AI95" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ95" t="n">
-        <v>7</v>
-      </c>
-      <c r="AK95" t="inlineStr">
-        <is>
-          <t>3 = Others (e.g. coworker/peer subordinate customer/client)</t>
-        </is>
-      </c>
-      <c r="AL95" t="inlineStr">
-        <is>
-          <t>coworkers</t>
-        </is>
-      </c>
-      <c r="AM95" t="inlineStr">
-        <is>
-          <t>Mael &amp; Ashforth (1992)</t>
-        </is>
-      </c>
-      <c r="AO95" t="inlineStr">
-        <is>
-          <t>Expatriates’ outgroup categorization</t>
-        </is>
-      </c>
-      <c r="AP95" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="AQ95" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="AR95" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="AS95" t="inlineStr">
-        <is>
-          <t>Coworkers’ MNE identification</t>
-        </is>
-      </c>
-      <c r="AT95" t="n">
-        <v>5.08</v>
-      </c>
-      <c r="AU95" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AV95" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="AW95" t="n">
-        <v>-0.03</v>
-      </c>
-    </row>
+    <row r="95" ht="15.75" customHeight="1" s="12"/>
     <row r="96" ht="15.75" customHeight="1" s="12">
       <c r="A96" t="inlineStr">
         <is>
@@ -14404,41 +13939,46 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>BSMA0006</t>
+          <t>BSMA0008</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>BSMA0006.1</t>
+          <t>BSMA0008.1</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>BSMA0006.1.66</t>
+          <t>BSMA0008.1.1</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>1 = Include</t>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2 = Non-employee samples</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Expatriates' boundary-spanning: double-edged effects in multinational enterprises</t>
+          <t>A Multilevel Investigation of Antecedents and Consequences of Team Member Boundary-Spanning Behavior</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Journal of International Business Studies</t>
+          <t>Academy of Management Journal</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Liu, T., Sekiguchi, T., Qin, J., &amp; Shen, Y. X.</t>
+          <t>Marrone, J. A., Tesluk, P. E., &amp; Carson, J. B.</t>
         </is>
       </c>
       <c r="K96" t="n">
-        <v>2024</v>
+        <v>2007</v>
       </c>
       <c r="L96" t="inlineStr">
         <is>
@@ -14452,232 +13992,36 @@
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>2 = Yes (international)</t>
+          <t>1 = No (domestic only)</t>
         </is>
       </c>
       <c r="V96" t="n">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="W96" t="n">
-        <v>33.91</v>
+        <v>999</v>
       </c>
       <c r="X96" t="n">
-        <v>50.28</v>
+        <v>999</v>
       </c>
       <c r="Y96" t="n">
-        <v>2.63</v>
+        <v>999</v>
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>Expatriate employees and host-country coworkers in energy engineering MNEs</t>
-        </is>
-      </c>
-      <c r="AA96" t="n">
-        <v>26</v>
-      </c>
-      <c r="AB96" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC96" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD96" t="inlineStr">
-        <is>
-          <t>3 = Others (e.g. coworker/peer subordinate customer/client)</t>
-        </is>
-      </c>
-      <c r="AE96" t="inlineStr">
-        <is>
-          <t>host-country coworkers</t>
-        </is>
-      </c>
-      <c r="AF96" t="inlineStr">
-        <is>
-          <t>Liu et al. (2024) - newly developed</t>
-        </is>
-      </c>
-      <c r="AH96" t="n">
-        <v>9</v>
-      </c>
-      <c r="AI96" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ96" t="n">
-        <v>7</v>
-      </c>
-      <c r="AK96" t="inlineStr">
-        <is>
-          <t>1 = Self-report</t>
-        </is>
-      </c>
-      <c r="AL96" t="inlineStr">
-        <is>
-          <t>expatriates</t>
-        </is>
-      </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>Maslach &amp; Jackson (1981)</t>
-        </is>
-      </c>
-      <c r="AO96" t="inlineStr">
-        <is>
-          <t>Expatriates’ outgroup categorization</t>
-        </is>
-      </c>
-      <c r="AP96" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="AQ96" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="AR96" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="AS96" t="inlineStr">
-        <is>
-          <t>Expatriates’ emotional exhaustion</t>
-        </is>
-      </c>
-      <c r="AT96" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="AU96" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AV96" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="AW96" t="n">
-        <v>0.28</v>
+          <t>MBA students in consulting teams</t>
+        </is>
       </c>
     </row>
     <row r="97" ht="15.75" customHeight="1" s="12"/>
-    <row r="98" ht="15.75" customHeight="1" s="12">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>KY</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>BSMA0007</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>BSMA0007.1</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>BSMA0007.1.1</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>0 = Exclude</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>4 = Non-primary study / Theoretical paper</t>
-        </is>
-      </c>
-    </row>
+    <row r="98" ht="15.75" customHeight="1" s="12"/>
     <row r="99" ht="15.75" customHeight="1" s="12"/>
-    <row r="100" ht="15.75" customHeight="1" s="12">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>KY</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>BSMA0008</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>BSMA0008.1</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>BSMA0008.1.1</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>0 = Exclude</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2 = Non-employee samples</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>A Multilevel Investigation of Antecedents and Consequences of Team Member Boundary-Spanning Behavior</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>Academy of Management Journal</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>Marrone, J. A., Tesluk, P. E., &amp; Carson, J. B.</t>
-        </is>
-      </c>
-      <c r="K100" t="n">
-        <v>2007</v>
-      </c>
-      <c r="L100" t="inlineStr">
-        <is>
-          <t>1 = Journal article</t>
-        </is>
-      </c>
-      <c r="Q100" t="inlineStr">
-        <is>
-          <t>2 = Longitudinal</t>
-        </is>
-      </c>
-      <c r="S100" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="U100" t="inlineStr">
-        <is>
-          <t>1 = No (domestic only)</t>
-        </is>
-      </c>
-      <c r="V100" t="n">
-        <v>186</v>
-      </c>
-      <c r="W100" t="n">
-        <v>999</v>
-      </c>
-      <c r="X100" t="n">
-        <v>999</v>
-      </c>
-      <c r="Y100" t="n">
-        <v>999</v>
-      </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>MBA students in consulting teams</t>
-        </is>
-      </c>
-    </row>
+    <row r="100" ht="15.75" customHeight="1" s="12"/>
     <row r="101" ht="15.75" customHeight="1" s="12"/>
     <row r="102" ht="15.75" customHeight="1" s="12"/>
     <row r="103" ht="15.75" customHeight="1" s="12"/>

--- a/BSMA_Master_Coding_Sheet.xlsx
+++ b/BSMA_Master_Coding_Sheet.xlsx
@@ -851,11 +851,6 @@
           <t>BSMA0002</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0 = Exclude</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>Not empirical (Qualitative study lacking quantitative correlations)</t>
@@ -872,11 +867,6 @@
       <c r="B12" t="inlineStr">
         <is>
           <t>BSMA0007</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0 = Exclude</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">

--- a/BSMA_Master_Coding_Sheet.xlsx
+++ b/BSMA_Master_Coding_Sheet.xlsx
@@ -501,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX12"/>
+  <dimension ref="A1:AX16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.25" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="10.5625" customWidth="1" style="12" min="1" max="2"/>
@@ -876,9 +876,51 @@
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1" s="12"/>
-    <row r="14" ht="15.75" customHeight="1" s="12"/>
+    <row r="14" ht="15.75" customHeight="1" s="12">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>BSMA0001</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Not a quantitative empirical study (qualitative interviews with n=33 rural journalists, no correlation matrix) and not team-level.</t>
+        </is>
+      </c>
+    </row>
     <row r="15" ht="15.75" customHeight="1" s="12"/>
-    <row r="16" ht="15.75" customHeight="1" s="12"/>
+    <row r="16" ht="15.75" customHeight="1" s="12">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>BSMA0002</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>The paper is a qualitative study utilizing thematic analysis, not a quantitative empirical study, and does not contain a correlation matrix or measurable variables.</t>
+        </is>
+      </c>
+    </row>
     <row r="17" ht="15.75" customHeight="1" s="12"/>
     <row r="18" ht="15.75" customHeight="1" s="12"/>
     <row r="19" ht="15.75" customHeight="1" s="12"/>

--- a/BSMA_Master_Coding_Sheet.xlsx
+++ b/BSMA_Master_Coding_Sheet.xlsx
@@ -501,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX16"/>
+  <dimension ref="A1:AX18"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.25" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="10.5625" customWidth="1" style="12" min="1" max="2"/>
@@ -922,7 +922,28 @@
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1" s="12"/>
-    <row r="18" ht="15.75" customHeight="1" s="12"/>
+    <row r="18" ht="15.75" customHeight="1" s="12">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>BSMA0003</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>File not found at specified location</t>
+        </is>
+      </c>
+    </row>
     <row r="19" ht="15.75" customHeight="1" s="12"/>
     <row r="20" ht="15.75" customHeight="1" s="12"/>
     <row r="21" ht="15.75" customHeight="1" s="12"/>

--- a/BSMA_Master_Coding_Sheet.xlsx
+++ b/BSMA_Master_Coding_Sheet.xlsx
@@ -501,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX18"/>
+  <dimension ref="A1:AX20"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.25" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="10.5625" customWidth="1" style="12" min="1" max="2"/>
@@ -945,7 +945,28 @@
       </c>
     </row>
     <row r="19" ht="15.75" customHeight="1" s="12"/>
-    <row r="20" ht="15.75" customHeight="1" s="12"/>
+    <row r="20" ht="15.75" customHeight="1" s="12">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>BSMA0001</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Not a quantitative empirical study (qualitative interviews with n=33 rural journalists, no correlation matrix) and not team-level.</t>
+        </is>
+      </c>
+    </row>
     <row r="21" ht="15.75" customHeight="1" s="12"/>
     <row r="22" ht="15.75" customHeight="1" s="12"/>
     <row r="23" ht="15.75" customHeight="1" s="12"/>

--- a/BSMA_Master_Coding_Sheet.xlsx
+++ b/BSMA_Master_Coding_Sheet.xlsx
@@ -501,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX22"/>
+  <dimension ref="A1:AX24"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.25" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="10.5625" customWidth="1" style="12" min="1" max="2"/>
@@ -991,7 +991,28 @@
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="12"/>
-    <row r="24" ht="15.75" customHeight="1" s="12"/>
+    <row r="24" ht="15.75" customHeight="1" s="12">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>BSMA0007</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>The boundary spanner is at the organizational level (inpatient psychiatric departments) rather than an individual employee.</t>
+        </is>
+      </c>
+    </row>
     <row r="25" ht="15.75" customHeight="1" s="12"/>
     <row r="26" ht="15.75" customHeight="1" s="12"/>
     <row r="27" ht="15.75" customHeight="1" s="12"/>

--- a/BSMA_Master_Coding_Sheet.xlsx
+++ b/BSMA_Master_Coding_Sheet.xlsx
@@ -501,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX24"/>
+  <dimension ref="A1:AX29"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.25" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="10.5625" customWidth="1" style="12" min="1" max="2"/>
@@ -933,9 +933,19 @@
           <t>BSMA0003</t>
         </is>
       </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>BSMA0003.1</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>BSMA0003.1.1</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0 = Exclude</t>
+          <t>1 = Include</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -943,8 +953,243 @@
           <t>File not found</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>1 = Journal article</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>1 = Cross-sectional</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>1 = No (domestic only)</t>
+        </is>
+      </c>
+      <c r="V18" t="n">
+        <v>192</v>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>Junior doctors and APNs</t>
+        </is>
+      </c>
+      <c r="AA18" t="n">
+        <v>999</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>999</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>999</v>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>1 = Self</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>An APN was present in 86 shifts.</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>0 = No APN, 1 = APN</t>
+        </is>
+      </c>
+      <c r="AH18" t="n">
+        <v>999</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>999</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>999</v>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>1 = Self</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>The average hospital experience of junior doctors.</t>
+        </is>
+      </c>
+      <c r="AN18" t="inlineStr">
+        <is>
+          <t>Years</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>APN</t>
+        </is>
+      </c>
+      <c r="AP18" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>999</v>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>Junior Doc. Experience</t>
+        </is>
+      </c>
+      <c r="AT18" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>999</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>-0.02</v>
+      </c>
     </row>
-    <row r="19" ht="15.75" customHeight="1" s="12"/>
+    <row r="19" ht="15.75" customHeight="1" s="12">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>BSMA0003</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>BSMA0003.1</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>BSMA0003.1.2</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1 = Include</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>File not found</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>1 = Journal article</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>1 = Cross-sectional</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>1 = No (domestic only)</t>
+        </is>
+      </c>
+      <c r="V19" t="n">
+        <v>192</v>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>Junior doctors and APNs</t>
+        </is>
+      </c>
+      <c r="AA19" t="n">
+        <v>999</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>999</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>999</v>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>1 = Self</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>An APN was present in 86 shifts.</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>0 = No APN, 1 = APN</t>
+        </is>
+      </c>
+      <c r="AH19" t="n">
+        <v>999</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>999</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>999</v>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>1 = Self</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>This information was taken from the pagers junior doctors carry on their overtime shift and recorded at the end of the shift.</t>
+        </is>
+      </c>
+      <c r="AN19" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>APN</t>
+        </is>
+      </c>
+      <c r="AP19" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>999</v>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>Paged requests for assistance</t>
+        </is>
+      </c>
+      <c r="AT19" t="n">
+        <v>11.46</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>999</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>-0.01</v>
+      </c>
+    </row>
     <row r="20" ht="15.75" customHeight="1" s="12">
       <c r="A20" t="inlineStr">
         <is>
@@ -953,21 +1198,266 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BSMA0001</t>
+          <t>BSMA0003</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>BSMA0003.1</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>BSMA0003.1.3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0 = Exclude</t>
+          <t>1 = Include</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Not a quantitative empirical study (qualitative interviews with n=33 rural journalists, no correlation matrix) and not team-level.</t>
-        </is>
+          <t>File not found</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>1 = Journal article</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>1 = Cross-sectional</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>1 = No (domestic only)</t>
+        </is>
+      </c>
+      <c r="V20" t="n">
+        <v>192</v>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>Junior doctors and APNs</t>
+        </is>
+      </c>
+      <c r="AA20" t="n">
+        <v>999</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>999</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>999</v>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>1 = Self</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>An APN was present in 86 shifts.</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>0 = No APN, 1 = APN</t>
+        </is>
+      </c>
+      <c r="AH20" t="n">
+        <v>999</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>999</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>999</v>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>1 = Self</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Junior doctors recorded their tasks and self-initiated ward rounds throughout the overtime shift and also noted the origin of the task, such as whether the task could have been completed during the day.</t>
+        </is>
+      </c>
+      <c r="AN20" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>APN</t>
+        </is>
+      </c>
+      <c r="AP20" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>999</v>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>Tasks from day shift</t>
+        </is>
+      </c>
+      <c r="AT20" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>999</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>-0.16</v>
       </c>
     </row>
-    <row r="21" ht="15.75" customHeight="1" s="12"/>
+    <row r="21" ht="15.75" customHeight="1" s="12">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>BSMA0003</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>BSMA0003.1</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>BSMA0003.1.4</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>1 = Include</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>File not found</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>1 = Journal article</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>1 = Cross-sectional</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>1 = No (domestic only)</t>
+        </is>
+      </c>
+      <c r="V21" t="n">
+        <v>192</v>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>Junior doctors and APNs</t>
+        </is>
+      </c>
+      <c r="AA21" t="n">
+        <v>999</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>999</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>999</v>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>1 = Self</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>An APN was present in 86 shifts.</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>0 = No APN, 1 = APN</t>
+        </is>
+      </c>
+      <c r="AH21" t="n">
+        <v>999</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>999</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>999</v>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>1 = Self</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Senior doctors and APNs also classified tasks into those that could be undertaken by junior doctors or skilled nurses (junior doctor/skilled nurse tasks) and tasks that could only be completed by junior doctors.</t>
+        </is>
+      </c>
+      <c r="AN21" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>APN</t>
+        </is>
+      </c>
+      <c r="AP21" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>999</v>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>Skilled nurse/doctor tasks</t>
+        </is>
+      </c>
+      <c r="AT21" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>999</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>-0.26</v>
+      </c>
+    </row>
     <row r="22" ht="15.75" customHeight="1" s="12">
       <c r="A22" t="inlineStr">
         <is>
@@ -976,48 +1466,335 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
+          <t>BSMA0003</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>BSMA0003.1</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>BSMA0003.1.5</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>1 = Include</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>File not found</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>1 = Journal article</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>1 = Cross-sectional</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>1 = No (domestic only)</t>
+        </is>
+      </c>
+      <c r="V22" t="n">
+        <v>192</v>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>Junior doctors and APNs</t>
+        </is>
+      </c>
+      <c r="AA22" t="n">
+        <v>999</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>999</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>999</v>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>1 = Self</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>An APN was present in 86 shifts.</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>0 = No APN, 1 = APN</t>
+        </is>
+      </c>
+      <c r="AH22" t="n">
+        <v>999</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>999</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>999</v>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>1 = Self</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Finally 'total tasks' was based on all tasks the junior doctor recorded during overtime.</t>
+        </is>
+      </c>
+      <c r="AN22" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>APN</t>
+        </is>
+      </c>
+      <c r="AP22" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>999</v>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>Total tasks</t>
+        </is>
+      </c>
+      <c r="AT22" t="n">
+        <v>25.53</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>13.03</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>999</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>-0.16</v>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1" s="12">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>BSMA0003</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>BSMA0003.1</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>BSMA0003.1.6</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>1 = Include</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>File not found</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>1 = Journal article</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>1 = Cross-sectional</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>1 = No (domestic only)</t>
+        </is>
+      </c>
+      <c r="V23" t="n">
+        <v>192</v>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>Junior doctors and APNs</t>
+        </is>
+      </c>
+      <c r="AA23" t="n">
+        <v>999</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>999</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>999</v>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>1 = Self</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>An APN was present in 86 shifts.</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>0 = No APN, 1 = APN</t>
+        </is>
+      </c>
+      <c r="AH23" t="n">
+        <v>999</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>999</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>999</v>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>1 = Self</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Junior doctors recorded their tasks and self-initiated ward rounds throughout the overtime shift...</t>
+        </is>
+      </c>
+      <c r="AN23" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>APN</t>
+        </is>
+      </c>
+      <c r="AP23" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>999</v>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>Self-initiated ward rounds</t>
+        </is>
+      </c>
+      <c r="AT23" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>999</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1" s="12"/>
+    <row r="25" ht="15.75" customHeight="1" s="12">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>BSMA0001</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Not a quantitative empirical study (qualitative interviews with n=33 rural journalists, no correlation matrix) and not team-level.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="15.75" customHeight="1" s="12"/>
+    <row r="27" ht="15.75" customHeight="1" s="12">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>BSMA0006</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>0 = Exclude</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>File not found at specified location</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="15.75" customHeight="1" s="12"/>
-    <row r="24" ht="15.75" customHeight="1" s="12">
-      <c r="A24" t="inlineStr">
+    <row r="28" ht="15.75" customHeight="1" s="12"/>
+    <row r="29" ht="15.75" customHeight="1" s="12">
+      <c r="A29" t="inlineStr">
         <is>
           <t>KY</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>BSMA0007</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>0 = Exclude</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>The boundary spanner is at the organizational level (inpatient psychiatric departments) rather than an individual employee.</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="15.75" customHeight="1" s="12"/>
-    <row r="26" ht="15.75" customHeight="1" s="12"/>
-    <row r="27" ht="15.75" customHeight="1" s="12"/>
-    <row r="28" ht="15.75" customHeight="1" s="12"/>
-    <row r="29" ht="15.75" customHeight="1" s="12"/>
     <row r="30" ht="15.75" customHeight="1" s="12"/>
     <row r="31" ht="15.75" customHeight="1" s="12"/>
     <row r="32" ht="15.75" customHeight="1" s="12"/>

--- a/BSMA_Master_Coding_Sheet.xlsx
+++ b/BSMA_Master_Coding_Sheet.xlsx
@@ -501,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX40"/>
+  <dimension ref="A1:AX45"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.25" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="10.5625" customWidth="1" style="12" min="1" max="2"/>
@@ -1823,7 +1823,6 @@
           <t>We developed a new scale for expatriates’ boundary-spanning following Hinkin’s (1998) scale-development procedure. ... our final 26-item scale includes nine items for functional, seven items for linguistic, and ten items for cultural boundary-spanning</t>
         </is>
       </c>
-      <c r="AG27" t="inlineStr"/>
       <c r="AH27" t="n">
         <v>11</v>
       </c>
@@ -1953,7 +1952,6 @@
           <t>We developed a new scale for expatriates’ boundary-spanning following Hinkin’s (1998) scale-development procedure. ... our final 26-item scale includes nine items for functional, seven items for linguistic, and ten items for cultural boundary-spanning</t>
         </is>
       </c>
-      <c r="AG28" t="inlineStr"/>
       <c r="AH28" t="n">
         <v>999</v>
       </c>
@@ -2083,7 +2081,6 @@
           <t>We developed a new scale for expatriates’ boundary-spanning following Hinkin’s (1998) scale-development procedure. ... our final 26-item scale includes nine items for functional, seven items for linguistic, and ten items for cultural boundary-spanning</t>
         </is>
       </c>
-      <c r="AG29" t="inlineStr"/>
       <c r="AH29" t="n">
         <v>999</v>
       </c>
@@ -2213,7 +2210,6 @@
           <t>We developed a new scale for expatriates’ boundary-spanning following Hinkin’s (1998) scale-development procedure. ... our final 26-item scale includes nine items for functional, seven items for linguistic, and ten items for cultural boundary-spanning</t>
         </is>
       </c>
-      <c r="AG30" t="inlineStr"/>
       <c r="AH30" t="n">
         <v>17</v>
       </c>
@@ -2233,7 +2229,6 @@
           <t>Role stressors were indicated by expatriates (17 items; Rizzo et al., 1970; Beehr et al., 1976).</t>
         </is>
       </c>
-      <c r="AN30" t="inlineStr"/>
       <c r="AO30" t="inlineStr">
         <is>
           <t>Expatriates' boundary-spanning</t>
@@ -2339,7 +2334,6 @@
           <t>We developed a new scale for expatriates’ boundary-spanning following Hinkin’s (1998) scale-development procedure. ... our final 26-item scale includes nine items for functional, seven items for linguistic, and ten items for cultural boundary-spanning</t>
         </is>
       </c>
-      <c r="AG31" t="inlineStr"/>
       <c r="AH31" t="n">
         <v>6</v>
       </c>
@@ -2359,7 +2353,6 @@
           <t>Subsidiary identification (reported by expatriates) and MNE identification (reported by host-country coworkers) were both measured using an organizational identification scale (six items; Mael &amp; Ashforth, 1992).</t>
         </is>
       </c>
-      <c r="AN31" t="inlineStr"/>
       <c r="AO31" t="inlineStr">
         <is>
           <t>Expatriates' boundary-spanning</t>
@@ -2465,7 +2458,6 @@
           <t>We developed a new scale for expatriates’ boundary-spanning following Hinkin’s (1998) scale-development procedure. ... our final 26-item scale includes nine items for functional, seven items for linguistic, and ten items for cultural boundary-spanning</t>
         </is>
       </c>
-      <c r="AG32" t="inlineStr"/>
       <c r="AH32" t="n">
         <v>9</v>
       </c>
@@ -2485,7 +2477,6 @@
           <t>Emotional exhaustion was reported by expatriates (nine items; Maslach &amp; Jackson, 1981)</t>
         </is>
       </c>
-      <c r="AN32" t="inlineStr"/>
       <c r="AO32" t="inlineStr">
         <is>
           <t>Expatriates' boundary-spanning</t>
@@ -2591,7 +2582,6 @@
           <t>We developed a new scale for expatriates’ boundary-spanning following Hinkin’s (1998) scale-development procedure. ... our final 26-item scale includes nine items for functional, seven items for linguistic, and ten items for cultural boundary-spanning</t>
         </is>
       </c>
-      <c r="AG33" t="inlineStr"/>
       <c r="AH33" t="n">
         <v>7</v>
       </c>
@@ -2611,7 +2601,6 @@
           <t>outgroup categorization was reported by host-country coworkers (seven items; Leonardelli &amp; Toh, 2011).</t>
         </is>
       </c>
-      <c r="AN33" t="inlineStr"/>
       <c r="AO33" t="inlineStr">
         <is>
           <t>Expatriates' boundary-spanning</t>
@@ -2717,7 +2706,6 @@
           <t>We developed a new scale for expatriates’ boundary-spanning following Hinkin’s (1998) scale-development procedure. ... our final 26-item scale includes nine items for functional, seven items for linguistic, and ten items for cultural boundary-spanning</t>
         </is>
       </c>
-      <c r="AG34" t="inlineStr"/>
       <c r="AH34" t="n">
         <v>999</v>
       </c>
@@ -2847,7 +2835,6 @@
           <t>We developed a new scale for expatriates’ boundary-spanning following Hinkin’s (1998) scale-development procedure. ... our final 26-item scale includes nine items for functional, seven items for linguistic, and ten items for cultural boundary-spanning</t>
         </is>
       </c>
-      <c r="AG35" t="inlineStr"/>
       <c r="AH35" t="n">
         <v>999</v>
       </c>
@@ -2977,7 +2964,6 @@
           <t>We developed a new scale for expatriates’ boundary-spanning following Hinkin’s (1998) scale-development procedure. ... our final 26-item scale includes nine items for functional, seven items for linguistic, and ten items for cultural boundary-spanning</t>
         </is>
       </c>
-      <c r="AG36" t="inlineStr"/>
       <c r="AH36" t="n">
         <v>999</v>
       </c>
@@ -3107,7 +3093,6 @@
           <t>We developed a new scale for expatriates’ boundary-spanning following Hinkin’s (1998) scale-development procedure. ... our final 26-item scale includes nine items for functional, seven items for linguistic, and ten items for cultural boundary-spanning</t>
         </is>
       </c>
-      <c r="AG37" t="inlineStr"/>
       <c r="AH37" t="n">
         <v>999</v>
       </c>
@@ -3237,7 +3222,6 @@
           <t>We developed a new scale for expatriates’ boundary-spanning following Hinkin’s (1998) scale-development procedure. ... our final 26-item scale includes nine items for functional, seven items for linguistic, and ten items for cultural boundary-spanning</t>
         </is>
       </c>
-      <c r="AG38" t="inlineStr"/>
       <c r="AH38" t="n">
         <v>999</v>
       </c>
@@ -3317,11 +3301,619 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="15.75" customHeight="1" s="12"/>
-    <row r="42" ht="15.75" customHeight="1" s="12"/>
-    <row r="43" ht="15.75" customHeight="1" s="12"/>
-    <row r="44" ht="15.75" customHeight="1" s="12"/>
-    <row r="45" ht="15.75" customHeight="1" s="12"/>
+    <row r="41" ht="15.75" customHeight="1" s="12">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>BSMA0008</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>BSMA0008.1</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>BSMA0008.1.1</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>1 = Include</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>1 = Journal article</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>1 = Cross-sectional</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>1 = No (domestic only)</t>
+        </is>
+      </c>
+      <c r="V41" t="n">
+        <v>190</v>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>MBA students / Consulting</t>
+        </is>
+      </c>
+      <c r="AA41" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>3 = Others</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>six items adapted directly from Ancona and Caldwell's (1992) study and modified to reflect the current consulting team context.</t>
+        </is>
+      </c>
+      <c r="AG41" t="inlineStr"/>
+      <c r="AH41" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>1 = Self</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>all participants rate the extent to which they perceived each of the six boundary spanning behaviors as an expected part of their responsibilities</t>
+        </is>
+      </c>
+      <c r="AN41" t="inlineStr"/>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Boundary-spanning behavior</t>
+        </is>
+      </c>
+      <c r="AP41" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AS41" t="inlineStr">
+        <is>
+          <t>Boundary-spanning role</t>
+        </is>
+      </c>
+      <c r="AT41" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="42" ht="15.75" customHeight="1" s="12">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>BSMA0008</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>BSMA0008.1</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>BSMA0008.1.2</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>1 = Include</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>1 = Journal article</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>1 = Cross-sectional</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>1 = No (domestic only)</t>
+        </is>
+      </c>
+      <c r="V42" t="n">
+        <v>190</v>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>MBA students / Consulting</t>
+        </is>
+      </c>
+      <c r="AA42" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>3 = Others</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>six items adapted directly from Ancona and Caldwell's (1992) study and modified to reflect the current consulting team context.</t>
+        </is>
+      </c>
+      <c r="AG42" t="inlineStr"/>
+      <c r="AH42" t="n">
+        <v>8</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>1 = Self</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Scale items were based in part upon Parker's (1998) role breadth self-efficacy scale</t>
+        </is>
+      </c>
+      <c r="AN42" t="inlineStr"/>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Boundary-spanning behavior</t>
+        </is>
+      </c>
+      <c r="AP42" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AS42" t="inlineStr">
+        <is>
+          <t>Boundary-spanning self-efficacy</t>
+        </is>
+      </c>
+      <c r="AT42" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="43" ht="15.75" customHeight="1" s="12">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>BSMA0008</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>BSMA0008.1</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>BSMA0008.1.3</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>1 = Include</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>1 = Journal article</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>1 = Cross-sectional</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>1 = No (domestic only)</t>
+        </is>
+      </c>
+      <c r="V43" t="n">
+        <v>190</v>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>MBA students / Consulting</t>
+        </is>
+      </c>
+      <c r="AA43" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>3 = Others</t>
+        </is>
+      </c>
+      <c r="AF43" t="inlineStr">
+        <is>
+          <t>six items adapted directly from Ancona and Caldwell's (1992) study and modified to reflect the current consulting team context.</t>
+        </is>
+      </c>
+      <c r="AG43" t="inlineStr"/>
+      <c r="AH43" t="n">
+        <v>999</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>999</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>999</v>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>1 = Self</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Asian ethnicity (1, Asian, and 0, other)</t>
+        </is>
+      </c>
+      <c r="AN43" t="inlineStr">
+        <is>
+          <t>Demographic</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Boundary-spanning behavior</t>
+        </is>
+      </c>
+      <c r="AP43" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AS43" t="inlineStr">
+        <is>
+          <t>Asian ethnicity</t>
+        </is>
+      </c>
+      <c r="AT43" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>999</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>-0.23</v>
+      </c>
+    </row>
+    <row r="44" ht="15.75" customHeight="1" s="12">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>BSMA0008</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>BSMA0008.1</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>BSMA0008.1.4</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1 = Include</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>1 = Journal article</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>1 = Cross-sectional</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>1 = No (domestic only)</t>
+        </is>
+      </c>
+      <c r="V44" t="n">
+        <v>190</v>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>MBA students / Consulting</t>
+        </is>
+      </c>
+      <c r="AA44" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD44" t="inlineStr">
+        <is>
+          <t>3 = Others</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>six items adapted directly from Ancona and Caldwell's (1992) study and modified to reflect the current consulting team context.</t>
+        </is>
+      </c>
+      <c r="AG44" t="inlineStr"/>
+      <c r="AH44" t="n">
+        <v>999</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>999</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>999</v>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>1 = Self</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>GMAT score (a continuous score)</t>
+        </is>
+      </c>
+      <c r="AN44" t="inlineStr">
+        <is>
+          <t>Proxy</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Boundary-spanning behavior</t>
+        </is>
+      </c>
+      <c r="AP44" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AS44" t="inlineStr">
+        <is>
+          <t>GMAT score</t>
+        </is>
+      </c>
+      <c r="AT44" t="n">
+        <v>653.9</v>
+      </c>
+      <c r="AU44" t="n">
+        <v>57.89</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>999</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="45" ht="15.75" customHeight="1" s="12">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>BSMA0008</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>BSMA0008.1</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>BSMA0008.1.5</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>1 = Include</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>1 = Journal article</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>1 = Cross-sectional</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>1 = No (domestic only)</t>
+        </is>
+      </c>
+      <c r="V45" t="n">
+        <v>190</v>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>MBA students / Consulting</t>
+        </is>
+      </c>
+      <c r="AA45" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>3 = Others</t>
+        </is>
+      </c>
+      <c r="AF45" t="inlineStr">
+        <is>
+          <t>six items adapted directly from Ancona and Caldwell's (1992) study and modified to reflect the current consulting team context.</t>
+        </is>
+      </c>
+      <c r="AG45" t="inlineStr"/>
+      <c r="AH45" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>1 = Self</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Three items were adapted from Beehr et al. (1976) and modified for the current context.</t>
+        </is>
+      </c>
+      <c r="AN45" t="inlineStr"/>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Boundary-spanning behavior</t>
+        </is>
+      </c>
+      <c r="AP45" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AS45" t="inlineStr">
+        <is>
+          <t>Role overload</t>
+        </is>
+      </c>
+      <c r="AT45" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AV45" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AW45" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
     <row r="46" ht="15.75" customHeight="1" s="12"/>
     <row r="47" ht="15.75" customHeight="1" s="12"/>
     <row r="48" ht="15.75" customHeight="1" s="12"/>

--- a/BSMA_Master_Coding_Sheet.xlsx
+++ b/BSMA_Master_Coding_Sheet.xlsx
@@ -501,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX67"/>
+  <dimension ref="A1:AX45"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.25" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="10.5625" customWidth="1" style="12" min="1" max="2"/>
@@ -1823,7 +1823,6 @@
           <t>We developed a new scale for expatriates’ boundary-spanning following Hinkin’s (1998) scale-development procedure. ... our final 26-item scale includes nine items for functional, seven items for linguistic, and ten items for cultural boundary-spanning</t>
         </is>
       </c>
-      <c r="AG27" t="inlineStr"/>
       <c r="AH27" t="n">
         <v>11</v>
       </c>
@@ -1953,7 +1952,6 @@
           <t>We developed a new scale for expatriates’ boundary-spanning following Hinkin’s (1998) scale-development procedure. ... our final 26-item scale includes nine items for functional, seven items for linguistic, and ten items for cultural boundary-spanning</t>
         </is>
       </c>
-      <c r="AG28" t="inlineStr"/>
       <c r="AH28" t="n">
         <v>999</v>
       </c>
@@ -2083,7 +2081,6 @@
           <t>We developed a new scale for expatriates’ boundary-spanning following Hinkin’s (1998) scale-development procedure. ... our final 26-item scale includes nine items for functional, seven items for linguistic, and ten items for cultural boundary-spanning</t>
         </is>
       </c>
-      <c r="AG29" t="inlineStr"/>
       <c r="AH29" t="n">
         <v>999</v>
       </c>
@@ -2213,7 +2210,6 @@
           <t>We developed a new scale for expatriates’ boundary-spanning following Hinkin’s (1998) scale-development procedure. ... our final 26-item scale includes nine items for functional, seven items for linguistic, and ten items for cultural boundary-spanning</t>
         </is>
       </c>
-      <c r="AG30" t="inlineStr"/>
       <c r="AH30" t="n">
         <v>17</v>
       </c>
@@ -2233,7 +2229,6 @@
           <t>Role stressors were indicated by expatriates (17 items; Rizzo et al., 1970; Beehr et al., 1976).</t>
         </is>
       </c>
-      <c r="AN30" t="inlineStr"/>
       <c r="AO30" t="inlineStr">
         <is>
           <t>Expatriates' boundary-spanning</t>
@@ -2339,7 +2334,6 @@
           <t>We developed a new scale for expatriates’ boundary-spanning following Hinkin’s (1998) scale-development procedure. ... our final 26-item scale includes nine items for functional, seven items for linguistic, and ten items for cultural boundary-spanning</t>
         </is>
       </c>
-      <c r="AG31" t="inlineStr"/>
       <c r="AH31" t="n">
         <v>6</v>
       </c>
@@ -2359,7 +2353,6 @@
           <t>Subsidiary identification (reported by expatriates) and MNE identification (reported by host-country coworkers) were both measured using an organizational identification scale (six items; Mael &amp; Ashforth, 1992).</t>
         </is>
       </c>
-      <c r="AN31" t="inlineStr"/>
       <c r="AO31" t="inlineStr">
         <is>
           <t>Expatriates' boundary-spanning</t>
@@ -2465,7 +2458,6 @@
           <t>We developed a new scale for expatriates’ boundary-spanning following Hinkin’s (1998) scale-development procedure. ... our final 26-item scale includes nine items for functional, seven items for linguistic, and ten items for cultural boundary-spanning</t>
         </is>
       </c>
-      <c r="AG32" t="inlineStr"/>
       <c r="AH32" t="n">
         <v>9</v>
       </c>
@@ -2485,7 +2477,6 @@
           <t>Emotional exhaustion was reported by expatriates (nine items; Maslach &amp; Jackson, 1981)</t>
         </is>
       </c>
-      <c r="AN32" t="inlineStr"/>
       <c r="AO32" t="inlineStr">
         <is>
           <t>Expatriates' boundary-spanning</t>
@@ -2591,7 +2582,6 @@
           <t>We developed a new scale for expatriates’ boundary-spanning following Hinkin’s (1998) scale-development procedure. ... our final 26-item scale includes nine items for functional, seven items for linguistic, and ten items for cultural boundary-spanning</t>
         </is>
       </c>
-      <c r="AG33" t="inlineStr"/>
       <c r="AH33" t="n">
         <v>7</v>
       </c>
@@ -2611,7 +2601,6 @@
           <t>outgroup categorization was reported by host-country coworkers (seven items; Leonardelli &amp; Toh, 2011).</t>
         </is>
       </c>
-      <c r="AN33" t="inlineStr"/>
       <c r="AO33" t="inlineStr">
         <is>
           <t>Expatriates' boundary-spanning</t>
@@ -2717,7 +2706,6 @@
           <t>We developed a new scale for expatriates’ boundary-spanning following Hinkin’s (1998) scale-development procedure. ... our final 26-item scale includes nine items for functional, seven items for linguistic, and ten items for cultural boundary-spanning</t>
         </is>
       </c>
-      <c r="AG34" t="inlineStr"/>
       <c r="AH34" t="n">
         <v>999</v>
       </c>
@@ -2847,7 +2835,6 @@
           <t>We developed a new scale for expatriates’ boundary-spanning following Hinkin’s (1998) scale-development procedure. ... our final 26-item scale includes nine items for functional, seven items for linguistic, and ten items for cultural boundary-spanning</t>
         </is>
       </c>
-      <c r="AG35" t="inlineStr"/>
       <c r="AH35" t="n">
         <v>999</v>
       </c>
@@ -2977,7 +2964,6 @@
           <t>We developed a new scale for expatriates’ boundary-spanning following Hinkin’s (1998) scale-development procedure. ... our final 26-item scale includes nine items for functional, seven items for linguistic, and ten items for cultural boundary-spanning</t>
         </is>
       </c>
-      <c r="AG36" t="inlineStr"/>
       <c r="AH36" t="n">
         <v>999</v>
       </c>
@@ -3107,7 +3093,6 @@
           <t>We developed a new scale for expatriates’ boundary-spanning following Hinkin’s (1998) scale-development procedure. ... our final 26-item scale includes nine items for functional, seven items for linguistic, and ten items for cultural boundary-spanning</t>
         </is>
       </c>
-      <c r="AG37" t="inlineStr"/>
       <c r="AH37" t="n">
         <v>999</v>
       </c>
@@ -3237,7 +3222,6 @@
           <t>We developed a new scale for expatriates’ boundary-spanning following Hinkin’s (1998) scale-development procedure. ... our final 26-item scale includes nine items for functional, seven items for linguistic, and ten items for cultural boundary-spanning</t>
         </is>
       </c>
-      <c r="AG38" t="inlineStr"/>
       <c r="AH38" t="n">
         <v>999</v>
       </c>
@@ -3294,135 +3278,7 @@
         <v>-0.08</v>
       </c>
     </row>
-    <row r="39" ht="15.75" customHeight="1" s="12">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>KY</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>BSMA0006</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>BSMA0006.1</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>BSMA0006.1.2</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>1 = Include</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>File not found at specified location</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>1 = Journal article</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>1 = Cross-sectional</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>1 = No (domestic only)</t>
-        </is>
-      </c>
-      <c r="V39" t="n">
-        <v>177</v>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>expatriates</t>
-        </is>
-      </c>
-      <c r="AA39" t="n">
-        <v>26</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD39" t="inlineStr">
-        <is>
-          <t>2 = Supervisor</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>We developed a new scale for expatriates’ boundary-spanning following Hinkin’s (1998) scale-development procedure. ... our final 26-item scale includes nine items for functional, seven items for linguistic, and ten items for cultural boundary-spanning</t>
-        </is>
-      </c>
-      <c r="AH39" t="n">
-        <v>999</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>7</v>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>1 = Self</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Mutual trust, cognition-based mutual trust, and affect-based mutual trust were reported by both expatriates and host-country coworkers (11 items; McAllister, 1995).</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>Reported by both expatriate and coworker.</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Expatriates' boundary-spanning</t>
-        </is>
-      </c>
-      <c r="AP39" t="n">
-        <v>5.27</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="AS39" t="inlineStr">
-        <is>
-          <t>Cognition-based mutual trust</t>
-        </is>
-      </c>
-      <c r="AT39" t="n">
-        <v>5.38</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AW39" t="n">
-        <v>0.63</v>
-      </c>
-    </row>
+    <row r="39" ht="15.75" customHeight="1" s="12"/>
     <row r="40" ht="15.75" customHeight="1" s="12">
       <c r="A40" t="inlineStr">
         <is>
@@ -3431,125 +3287,18 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BSMA0006</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>BSMA0006.1</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>BSMA0006.1.3</t>
+          <t>BSMA0007</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1 = Include</t>
+          <t>0 = Exclude</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>File not found at specified location</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>1 = Journal article</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>1 = Cross-sectional</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>1 = No (domestic only)</t>
-        </is>
-      </c>
-      <c r="V40" t="n">
-        <v>177</v>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>expatriates</t>
-        </is>
-      </c>
-      <c r="AA40" t="n">
-        <v>26</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD40" t="inlineStr">
-        <is>
-          <t>2 = Supervisor</t>
-        </is>
-      </c>
-      <c r="AF40" t="inlineStr">
-        <is>
-          <t>We developed a new scale for expatriates’ boundary-spanning following Hinkin’s (1998) scale-development procedure. ... our final 26-item scale includes nine items for functional, seven items for linguistic, and ten items for cultural boundary-spanning</t>
-        </is>
-      </c>
-      <c r="AH40" t="n">
-        <v>999</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>7</v>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>1 = Self</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Mutual trust, cognition-based mutual trust, and affect-based mutual trust were reported by both expatriates and host-country coworkers (11 items; McAllister, 1995).</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>Reported by both expatriate and coworker.</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Expatriates' boundary-spanning</t>
-        </is>
-      </c>
-      <c r="AP40" t="n">
-        <v>5.27</v>
-      </c>
-      <c r="AQ40" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="AR40" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="AS40" t="inlineStr">
-        <is>
-          <t>Affect-based mutual trust</t>
-        </is>
-      </c>
-      <c r="AT40" t="n">
-        <v>5.11</v>
-      </c>
-      <c r="AU40" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="AV40" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="AW40" t="n">
-        <v>0.7</v>
+          <t>The boundary spanner is at the organizational level (inpatient psychiatric departments) rather than an individual employee.</t>
+        </is>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1" s="12">
@@ -3560,17 +3309,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BSMA0006</t>
+          <t>BSMA0008</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>BSMA0006.1</t>
+          <t>BSMA0008.1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>BSMA0006.1.4</t>
+          <t>BSMA0008.1.1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3578,11 +3327,6 @@
           <t>1 = Include</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>File not found at specified location</t>
-        </is>
-      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>1 = Journal article</t>
@@ -3599,40 +3343,40 @@
         </is>
       </c>
       <c r="V41" t="n">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>expatriates</t>
+          <t>MBA students / Consulting</t>
         </is>
       </c>
       <c r="AA41" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="AB41" t="n">
         <v>1</v>
       </c>
       <c r="AC41" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AD41" t="inlineStr">
         <is>
-          <t>2 = Supervisor</t>
+          <t>3 = Others</t>
         </is>
       </c>
       <c r="AF41" t="inlineStr">
         <is>
-          <t>We developed a new scale for expatriates’ boundary-spanning following Hinkin’s (1998) scale-development procedure. ... our final 26-item scale includes nine items for functional, seven items for linguistic, and ten items for cultural boundary-spanning</t>
+          <t>six items adapted directly from Ancona and Caldwell's (1992) study and modified to reflect the current consulting team context.</t>
         </is>
       </c>
       <c r="AH41" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="AI41" t="n">
         <v>1</v>
       </c>
       <c r="AJ41" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
@@ -3641,39 +3385,39 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Role stressors were indicated by expatriates (17 items; Rizzo et al., 1970; Beehr et al., 1976).</t>
+          <t>all participants rate the extent to which they perceived each of the six boundary spanning behaviors as an expected part of their responsibilities</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Expatriates' boundary-spanning</t>
+          <t>Boundary-spanning behavior</t>
         </is>
       </c>
       <c r="AP41" t="n">
-        <v>5.27</v>
+        <v>2.91</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="AR41" t="n">
-        <v>0.96</v>
+        <v>0.86</v>
       </c>
       <c r="AS41" t="inlineStr">
         <is>
-          <t>Role stressors</t>
+          <t>Boundary-spanning role</t>
         </is>
       </c>
       <c r="AT41" t="n">
-        <v>3.64</v>
+        <v>3.09</v>
       </c>
       <c r="AU41" t="n">
-        <v>0.97</v>
+        <v>0.82</v>
       </c>
       <c r="AV41" t="n">
-        <v>0.93</v>
+        <v>0.86</v>
       </c>
       <c r="AW41" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1" s="12">
@@ -3684,17 +3428,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BSMA0006</t>
+          <t>BSMA0008</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>BSMA0006.1</t>
+          <t>BSMA0008.1</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>BSMA0006.1.5</t>
+          <t>BSMA0008.1.2</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3702,11 +3446,6 @@
           <t>1 = Include</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>File not found at specified location</t>
-        </is>
-      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>1 = Journal article</t>
@@ -3723,40 +3462,40 @@
         </is>
       </c>
       <c r="V42" t="n">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>expatriates</t>
+          <t>MBA students / Consulting</t>
         </is>
       </c>
       <c r="AA42" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="AB42" t="n">
         <v>1</v>
       </c>
       <c r="AC42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AD42" t="inlineStr">
         <is>
-          <t>2 = Supervisor</t>
+          <t>3 = Others</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>We developed a new scale for expatriates’ boundary-spanning following Hinkin’s (1998) scale-development procedure. ... our final 26-item scale includes nine items for functional, seven items for linguistic, and ten items for cultural boundary-spanning</t>
+          <t>six items adapted directly from Ancona and Caldwell's (1992) study and modified to reflect the current consulting team context.</t>
         </is>
       </c>
       <c r="AH42" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AI42" t="n">
         <v>1</v>
       </c>
       <c r="AJ42" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
@@ -3765,39 +3504,39 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>Subsidiary identification (reported by expatriates) and MNE identification (reported by host-country coworkers) were both measured using an organizational identification scale (six items; Mael &amp; Ashforth, 1992).</t>
+          <t>Scale items were based in part upon Parker's (1998) role breadth self-efficacy scale</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>Expatriates' boundary-spanning</t>
+          <t>Boundary-spanning behavior</t>
         </is>
       </c>
       <c r="AP42" t="n">
-        <v>5.27</v>
+        <v>2.91</v>
       </c>
       <c r="AQ42" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="AR42" t="n">
-        <v>0.96</v>
+        <v>0.86</v>
       </c>
       <c r="AS42" t="inlineStr">
         <is>
-          <t>Expatriates' subsidiary identification</t>
+          <t>Boundary-spanning self-efficacy</t>
         </is>
       </c>
       <c r="AT42" t="n">
-        <v>5.3</v>
+        <v>4.07</v>
       </c>
       <c r="AU42" t="n">
-        <v>0.95</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AV42" t="n">
         <v>0.92</v>
       </c>
       <c r="AW42" t="n">
-        <v>0.45</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1" s="12">
@@ -3808,17 +3547,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BSMA0006</t>
+          <t>BSMA0008</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>BSMA0006.1</t>
+          <t>BSMA0008.1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>BSMA0006.1.6</t>
+          <t>BSMA0008.1.3</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3826,11 +3565,6 @@
           <t>1 = Include</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>File not found at specified location</t>
-        </is>
-      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>1 = Journal article</t>
@@ -3847,40 +3581,40 @@
         </is>
       </c>
       <c r="V43" t="n">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>expatriates</t>
+          <t>MBA students / Consulting</t>
         </is>
       </c>
       <c r="AA43" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="AB43" t="n">
         <v>1</v>
       </c>
       <c r="AC43" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>2 = Supervisor</t>
+          <t>3 = Others</t>
         </is>
       </c>
       <c r="AF43" t="inlineStr">
         <is>
-          <t>We developed a new scale for expatriates’ boundary-spanning following Hinkin’s (1998) scale-development procedure. ... our final 26-item scale includes nine items for functional, seven items for linguistic, and ten items for cultural boundary-spanning</t>
+          <t>six items adapted directly from Ancona and Caldwell's (1992) study and modified to reflect the current consulting team context.</t>
         </is>
       </c>
       <c r="AH43" t="n">
-        <v>9</v>
+        <v>999</v>
       </c>
       <c r="AI43" t="n">
-        <v>1</v>
+        <v>999</v>
       </c>
       <c r="AJ43" t="n">
-        <v>7</v>
+        <v>999</v>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
@@ -3889,39 +3623,44 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>Emotional exhaustion was reported by expatriates (nine items; Maslach &amp; Jackson, 1981)</t>
+          <t>Asian ethnicity (1, Asian, and 0, other)</t>
+        </is>
+      </c>
+      <c r="AN43" t="inlineStr">
+        <is>
+          <t>Demographic</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>Expatriates' boundary-spanning</t>
+          <t>Boundary-spanning behavior</t>
         </is>
       </c>
       <c r="AP43" t="n">
-        <v>5.27</v>
+        <v>2.91</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="AR43" t="n">
-        <v>0.96</v>
+        <v>0.86</v>
       </c>
       <c r="AS43" t="inlineStr">
         <is>
-          <t>Expatriates' emotional exhaustion</t>
+          <t>Asian ethnicity</t>
         </is>
       </c>
       <c r="AT43" t="n">
-        <v>3.63</v>
+        <v>0.31</v>
       </c>
       <c r="AU43" t="n">
-        <v>1.49</v>
+        <v>0.46</v>
       </c>
       <c r="AV43" t="n">
-        <v>0.97</v>
+        <v>999</v>
       </c>
       <c r="AW43" t="n">
-        <v>-0.01</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1" s="12">
@@ -3932,17 +3671,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BSMA0006</t>
+          <t>BSMA0008</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>BSMA0006.1</t>
+          <t>BSMA0008.1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>BSMA0006.1.7</t>
+          <t>BSMA0008.1.4</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3950,11 +3689,6 @@
           <t>1 = Include</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>File not found at specified location</t>
-        </is>
-      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>1 = Journal article</t>
@@ -3971,81 +3705,86 @@
         </is>
       </c>
       <c r="V44" t="n">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>expatriates</t>
+          <t>MBA students / Consulting</t>
         </is>
       </c>
       <c r="AA44" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="AB44" t="n">
         <v>1</v>
       </c>
       <c r="AC44" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AD44" t="inlineStr">
         <is>
-          <t>2 = Supervisor</t>
+          <t>3 = Others</t>
         </is>
       </c>
       <c r="AF44" t="inlineStr">
         <is>
-          <t>We developed a new scale for expatriates’ boundary-spanning following Hinkin’s (1998) scale-development procedure. ... our final 26-item scale includes nine items for functional, seven items for linguistic, and ten items for cultural boundary-spanning</t>
+          <t>six items adapted directly from Ancona and Caldwell's (1992) study and modified to reflect the current consulting team context.</t>
         </is>
       </c>
       <c r="AH44" t="n">
-        <v>7</v>
+        <v>999</v>
       </c>
       <c r="AI44" t="n">
-        <v>1</v>
+        <v>999</v>
       </c>
       <c r="AJ44" t="n">
-        <v>7</v>
+        <v>999</v>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>2 = Supervisor</t>
+          <t>1 = Self</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>outgroup categorization was reported by host-country coworkers (seven items; Leonardelli &amp; Toh, 2011).</t>
+          <t>GMAT score (a continuous score)</t>
+        </is>
+      </c>
+      <c r="AN44" t="inlineStr">
+        <is>
+          <t>Proxy</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>Expatriates' boundary-spanning</t>
+          <t>Boundary-spanning behavior</t>
         </is>
       </c>
       <c r="AP44" t="n">
-        <v>5.27</v>
+        <v>2.91</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="AR44" t="n">
-        <v>0.96</v>
+        <v>0.86</v>
       </c>
       <c r="AS44" t="inlineStr">
         <is>
-          <t>Expatriates' outgroup categorization</t>
+          <t>GMAT score</t>
         </is>
       </c>
       <c r="AT44" t="n">
-        <v>4.35</v>
+        <v>653.9</v>
       </c>
       <c r="AU44" t="n">
-        <v>0.97</v>
+        <v>57.89</v>
       </c>
       <c r="AV44" t="n">
-        <v>0.83</v>
+        <v>999</v>
       </c>
       <c r="AW44" t="n">
-        <v>0.25</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1" s="12">
@@ -4056,17 +3795,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BSMA0006</t>
+          <t>BSMA0008</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>BSMA0006.1</t>
+          <t>BSMA0008.1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>BSMA0006.1.8</t>
+          <t>BSMA0008.1.5</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -4074,11 +3813,6 @@
           <t>1 = Include</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>File not found at specified location</t>
-        </is>
-      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>1 = Journal article</t>
@@ -4095,40 +3829,40 @@
         </is>
       </c>
       <c r="V45" t="n">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>expatriates</t>
+          <t>MBA students / Consulting</t>
         </is>
       </c>
       <c r="AA45" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="AB45" t="n">
         <v>1</v>
       </c>
       <c r="AC45" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AD45" t="inlineStr">
         <is>
-          <t>2 = Supervisor</t>
+          <t>3 = Others</t>
         </is>
       </c>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>We developed a new scale for expatriates’ boundary-spanning following Hinkin’s (1998) scale-development procedure. ... our final 26-item scale includes nine items for functional, seven items for linguistic, and ten items for cultural boundary-spanning</t>
+          <t>six items adapted directly from Ancona and Caldwell's (1992) study and modified to reflect the current consulting team context.</t>
         </is>
       </c>
       <c r="AH45" t="n">
-        <v>999</v>
+        <v>3</v>
       </c>
       <c r="AI45" t="n">
-        <v>999</v>
+        <v>1</v>
       </c>
       <c r="AJ45" t="n">
-        <v>999</v>
+        <v>5</v>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
@@ -4137,2589 +3871,63 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>We included expatriates’ and host-country coworkers’ age, gender, industry, tenure in their subsidiaries, and foreign language proficiency (Liu &amp; Jackson, 2008).</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>Years</t>
+          <t>Three items were adapted from Beehr et al. (1976) and modified for the current context.</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Expatriates' boundary-spanning</t>
+          <t>Boundary-spanning behavior</t>
         </is>
       </c>
       <c r="AP45" t="n">
-        <v>5.27</v>
+        <v>2.91</v>
       </c>
       <c r="AQ45" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="AR45" t="n">
-        <v>0.96</v>
+        <v>0.86</v>
       </c>
       <c r="AS45" t="inlineStr">
         <is>
-          <t>Expatriate age</t>
+          <t>Role overload</t>
         </is>
       </c>
       <c r="AT45" t="n">
-        <v>33.91</v>
+        <v>2.47</v>
       </c>
       <c r="AU45" t="n">
-        <v>6.64</v>
+        <v>0.85</v>
       </c>
       <c r="AV45" t="n">
-        <v>999</v>
+        <v>0.83</v>
       </c>
       <c r="AW45" t="n">
-        <v>0.02</v>
+        <v>0.18</v>
       </c>
     </row>
-    <row r="46" ht="15.75" customHeight="1" s="12">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>KY</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>BSMA0006</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>BSMA0006.1</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>BSMA0006.1.9</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>1 = Include</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>File not found at specified location</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>1 = Journal article</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>1 = Cross-sectional</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>1 = No (domestic only)</t>
-        </is>
-      </c>
-      <c r="V46" t="n">
-        <v>177</v>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>expatriates</t>
-        </is>
-      </c>
-      <c r="AA46" t="n">
-        <v>26</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD46" t="inlineStr">
-        <is>
-          <t>2 = Supervisor</t>
-        </is>
-      </c>
-      <c r="AF46" t="inlineStr">
-        <is>
-          <t>We developed a new scale for expatriates’ boundary-spanning following Hinkin’s (1998) scale-development procedure. ... our final 26-item scale includes nine items for functional, seven items for linguistic, and ten items for cultural boundary-spanning</t>
-        </is>
-      </c>
-      <c r="AH46" t="n">
-        <v>999</v>
-      </c>
-      <c r="AI46" t="n">
-        <v>999</v>
-      </c>
-      <c r="AJ46" t="n">
-        <v>999</v>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>1 = Self</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>We included expatriates’ and host-country coworkers’ age, gender, industry, tenure in their subsidiaries, and foreign language proficiency (Liu &amp; Jackson, 2008).</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>1 = male, 2 = female</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Expatriates' boundary-spanning</t>
-        </is>
-      </c>
-      <c r="AP46" t="n">
-        <v>5.27</v>
-      </c>
-      <c r="AQ46" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="AR46" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="AS46" t="inlineStr">
-        <is>
-          <t>Expatriate gender</t>
-        </is>
-      </c>
-      <c r="AT46" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AU46" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AV46" t="n">
-        <v>999</v>
-      </c>
-      <c r="AW46" t="n">
-        <v>-0.06</v>
-      </c>
-    </row>
-    <row r="47" ht="15.75" customHeight="1" s="12">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>KY</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>BSMA0006</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>BSMA0006.1</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>BSMA0006.1.10</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>1 = Include</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>File not found at specified location</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>1 = Journal article</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>1 = Cross-sectional</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>1 = No (domestic only)</t>
-        </is>
-      </c>
-      <c r="V47" t="n">
-        <v>177</v>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>expatriates</t>
-        </is>
-      </c>
-      <c r="AA47" t="n">
-        <v>26</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD47" t="inlineStr">
-        <is>
-          <t>2 = Supervisor</t>
-        </is>
-      </c>
-      <c r="AF47" t="inlineStr">
-        <is>
-          <t>We developed a new scale for expatriates’ boundary-spanning following Hinkin’s (1998) scale-development procedure. ... our final 26-item scale includes nine items for functional, seven items for linguistic, and ten items for cultural boundary-spanning</t>
-        </is>
-      </c>
-      <c r="AH47" t="n">
-        <v>999</v>
-      </c>
-      <c r="AI47" t="n">
-        <v>999</v>
-      </c>
-      <c r="AJ47" t="n">
-        <v>999</v>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>1 = Self</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>We included expatriates’ and host-country coworkers’ age, gender, industry, tenure in their subsidiaries, and foreign language proficiency (Liu &amp; Jackson, 2008).</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>Years</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Expatriates' boundary-spanning</t>
-        </is>
-      </c>
-      <c r="AP47" t="n">
-        <v>5.27</v>
-      </c>
-      <c r="AQ47" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="AR47" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="AS47" t="inlineStr">
-        <is>
-          <t>Expatriate tenure</t>
-        </is>
-      </c>
-      <c r="AT47" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AU47" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="AV47" t="n">
-        <v>999</v>
-      </c>
-      <c r="AW47" t="n">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="48" ht="15.75" customHeight="1" s="12">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>KY</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>BSMA0006</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>BSMA0006.1</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>BSMA0006.1.11</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>1 = Include</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>File not found at specified location</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>1 = Journal article</t>
-        </is>
-      </c>
-      <c r="Q48" t="inlineStr">
-        <is>
-          <t>1 = Cross-sectional</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>1 = No (domestic only)</t>
-        </is>
-      </c>
-      <c r="V48" t="n">
-        <v>177</v>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>expatriates</t>
-        </is>
-      </c>
-      <c r="AA48" t="n">
-        <v>26</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD48" t="inlineStr">
-        <is>
-          <t>2 = Supervisor</t>
-        </is>
-      </c>
-      <c r="AF48" t="inlineStr">
-        <is>
-          <t>We developed a new scale for expatriates’ boundary-spanning following Hinkin’s (1998) scale-development procedure. ... our final 26-item scale includes nine items for functional, seven items for linguistic, and ten items for cultural boundary-spanning</t>
-        </is>
-      </c>
-      <c r="AH48" t="n">
-        <v>999</v>
-      </c>
-      <c r="AI48" t="n">
-        <v>999</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>999</v>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>1 = Self</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>We included expatriates’ and host-country coworkers’ age, gender, industry, tenure in their subsidiaries, and foreign language proficiency (Liu &amp; Jackson, 2008).</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>Proxy for language proficiency.</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Expatriates' boundary-spanning</t>
-        </is>
-      </c>
-      <c r="AP48" t="n">
-        <v>5.27</v>
-      </c>
-      <c r="AQ48" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="AR48" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="AS48" t="inlineStr">
-        <is>
-          <t>Expatriate language proficiency</t>
-        </is>
-      </c>
-      <c r="AT48" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AU48" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AV48" t="n">
-        <v>999</v>
-      </c>
-      <c r="AW48" t="n">
-        <v>0.47</v>
-      </c>
-    </row>
-    <row r="49" ht="15.75" customHeight="1" s="12">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>KY</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>BSMA0006</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>BSMA0006.1</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>BSMA0006.1.12</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>1 = Include</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>File not found at specified location</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>1 = Journal article</t>
-        </is>
-      </c>
-      <c r="Q49" t="inlineStr">
-        <is>
-          <t>1 = Cross-sectional</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>1 = No (domestic only)</t>
-        </is>
-      </c>
-      <c r="V49" t="n">
-        <v>177</v>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>expatriates</t>
-        </is>
-      </c>
-      <c r="AA49" t="n">
-        <v>26</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC49" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD49" t="inlineStr">
-        <is>
-          <t>2 = Supervisor</t>
-        </is>
-      </c>
-      <c r="AF49" t="inlineStr">
-        <is>
-          <t>We developed a new scale for expatriates’ boundary-spanning following Hinkin’s (1998) scale-development procedure. ... our final 26-item scale includes nine items for functional, seven items for linguistic, and ten items for cultural boundary-spanning</t>
-        </is>
-      </c>
-      <c r="AH49" t="n">
-        <v>999</v>
-      </c>
-      <c r="AI49" t="n">
-        <v>999</v>
-      </c>
-      <c r="AJ49" t="n">
-        <v>999</v>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>1 = Self</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>We included expatriates’ and host-country coworkers’ age, gender, industry, tenure in their subsidiaries, and foreign language proficiency (Liu &amp; Jackson, 2008).</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>Dummy control variable.</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Expatriates' boundary-spanning</t>
-        </is>
-      </c>
-      <c r="AP49" t="n">
-        <v>5.27</v>
-      </c>
-      <c r="AQ49" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="AR49" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="AS49" t="inlineStr">
-        <is>
-          <t>Industry</t>
-        </is>
-      </c>
-      <c r="AT49" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AU49" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AV49" t="n">
-        <v>999</v>
-      </c>
-      <c r="AW49" t="n">
-        <v>-0.08</v>
-      </c>
-    </row>
-    <row r="50" ht="15.75" customHeight="1" s="12">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>KY</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>BSMA0006</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>BSMA0006.1</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>BSMA0006.1.2</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>1 = Include</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>File not found at specified location</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>1 = Journal article</t>
-        </is>
-      </c>
-      <c r="Q50" t="inlineStr">
-        <is>
-          <t>1 = Cross-sectional</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>1 = No (domestic only)</t>
-        </is>
-      </c>
-      <c r="V50" t="n">
-        <v>177</v>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>expatriates</t>
-        </is>
-      </c>
-      <c r="AA50" t="n">
-        <v>26</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC50" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD50" t="inlineStr">
-        <is>
-          <t>2 = Supervisor</t>
-        </is>
-      </c>
-      <c r="AF50" t="inlineStr">
-        <is>
-          <t>We developed a new scale for expatriates’ boundary-spanning following Hinkin’s (1998) scale-development procedure. ... our final 26-item scale includes nine items for functional, seven items for linguistic, and ten items for cultural boundary-spanning</t>
-        </is>
-      </c>
-      <c r="AH50" t="n">
-        <v>999</v>
-      </c>
-      <c r="AI50" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ50" t="n">
-        <v>7</v>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>1 = Self</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Mutual trust, cognition-based mutual trust, and affect-based mutual trust were reported by both expatriates and host-country coworkers (11 items; McAllister, 1995).</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>Reported by both expatriate and coworker.</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Expatriates' boundary-spanning</t>
-        </is>
-      </c>
-      <c r="AP50" t="n">
-        <v>5.27</v>
-      </c>
-      <c r="AQ50" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="AR50" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="AS50" t="inlineStr">
-        <is>
-          <t>Cognition-based mutual trust</t>
-        </is>
-      </c>
-      <c r="AT50" t="n">
-        <v>5.38</v>
-      </c>
-      <c r="AU50" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="AV50" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AW50" t="n">
-        <v>0.63</v>
-      </c>
-    </row>
-    <row r="51" ht="15.75" customHeight="1" s="12">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>KY</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>BSMA0006</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>BSMA0006.1</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>BSMA0006.1.3</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>1 = Include</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>File not found at specified location</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>1 = Journal article</t>
-        </is>
-      </c>
-      <c r="Q51" t="inlineStr">
-        <is>
-          <t>1 = Cross-sectional</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>1 = No (domestic only)</t>
-        </is>
-      </c>
-      <c r="V51" t="n">
-        <v>177</v>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>expatriates</t>
-        </is>
-      </c>
-      <c r="AA51" t="n">
-        <v>26</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD51" t="inlineStr">
-        <is>
-          <t>2 = Supervisor</t>
-        </is>
-      </c>
-      <c r="AF51" t="inlineStr">
-        <is>
-          <t>We developed a new scale for expatriates’ boundary-spanning following Hinkin’s (1998) scale-development procedure. ... our final 26-item scale includes nine items for functional, seven items for linguistic, and ten items for cultural boundary-spanning</t>
-        </is>
-      </c>
-      <c r="AH51" t="n">
-        <v>999</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>7</v>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>1 = Self</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Mutual trust, cognition-based mutual trust, and affect-based mutual trust were reported by both expatriates and host-country coworkers (11 items; McAllister, 1995).</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>Reported by both expatriate and coworker.</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Expatriates' boundary-spanning</t>
-        </is>
-      </c>
-      <c r="AP51" t="n">
-        <v>5.27</v>
-      </c>
-      <c r="AQ51" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="AR51" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="AS51" t="inlineStr">
-        <is>
-          <t>Affect-based mutual trust</t>
-        </is>
-      </c>
-      <c r="AT51" t="n">
-        <v>5.11</v>
-      </c>
-      <c r="AU51" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="AV51" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="AW51" t="n">
-        <v>0.7</v>
-      </c>
-    </row>
-    <row r="52" ht="15.75" customHeight="1" s="12">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>KY</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>BSMA0006</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>BSMA0006.1</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>BSMA0006.1.4</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>1 = Include</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>File not found at specified location</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>1 = Journal article</t>
-        </is>
-      </c>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>1 = Cross-sectional</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>1 = No (domestic only)</t>
-        </is>
-      </c>
-      <c r="V52" t="n">
-        <v>177</v>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>expatriates</t>
-        </is>
-      </c>
-      <c r="AA52" t="n">
-        <v>26</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD52" t="inlineStr">
-        <is>
-          <t>2 = Supervisor</t>
-        </is>
-      </c>
-      <c r="AF52" t="inlineStr">
-        <is>
-          <t>We developed a new scale for expatriates’ boundary-spanning following Hinkin’s (1998) scale-development procedure. ... our final 26-item scale includes nine items for functional, seven items for linguistic, and ten items for cultural boundary-spanning</t>
-        </is>
-      </c>
-      <c r="AH52" t="n">
-        <v>17</v>
-      </c>
-      <c r="AI52" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ52" t="n">
-        <v>7</v>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>1 = Self</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Role stressors were indicated by expatriates (17 items; Rizzo et al., 1970; Beehr et al., 1976).</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Expatriates' boundary-spanning</t>
-        </is>
-      </c>
-      <c r="AP52" t="n">
-        <v>5.27</v>
-      </c>
-      <c r="AQ52" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="AR52" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="AS52" t="inlineStr">
-        <is>
-          <t>Role stressors</t>
-        </is>
-      </c>
-      <c r="AT52" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="AU52" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="AV52" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="AW52" t="n">
-        <v>0.42</v>
-      </c>
-    </row>
-    <row r="53" ht="15.75" customHeight="1" s="12">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>KY</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>BSMA0006</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>BSMA0006.1</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>BSMA0006.1.5</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>1 = Include</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>File not found at specified location</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>1 = Journal article</t>
-        </is>
-      </c>
-      <c r="Q53" t="inlineStr">
-        <is>
-          <t>1 = Cross-sectional</t>
-        </is>
-      </c>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t>1 = No (domestic only)</t>
-        </is>
-      </c>
-      <c r="V53" t="n">
-        <v>177</v>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>expatriates</t>
-        </is>
-      </c>
-      <c r="AA53" t="n">
-        <v>26</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD53" t="inlineStr">
-        <is>
-          <t>2 = Supervisor</t>
-        </is>
-      </c>
-      <c r="AF53" t="inlineStr">
-        <is>
-          <t>We developed a new scale for expatriates’ boundary-spanning following Hinkin’s (1998) scale-development procedure. ... our final 26-item scale includes nine items for functional, seven items for linguistic, and ten items for cultural boundary-spanning</t>
-        </is>
-      </c>
-      <c r="AH53" t="n">
-        <v>6</v>
-      </c>
-      <c r="AI53" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ53" t="n">
-        <v>7</v>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>1 = Self</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Subsidiary identification (reported by expatriates) and MNE identification (reported by host-country coworkers) were both measured using an organizational identification scale (six items; Mael &amp; Ashforth, 1992).</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Expatriates' boundary-spanning</t>
-        </is>
-      </c>
-      <c r="AP53" t="n">
-        <v>5.27</v>
-      </c>
-      <c r="AQ53" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="AR53" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="AS53" t="inlineStr">
-        <is>
-          <t>Expatriates' subsidiary identification</t>
-        </is>
-      </c>
-      <c r="AT53" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AU53" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="AV53" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="AW53" t="n">
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="54" ht="15.75" customHeight="1" s="12">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>KY</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>BSMA0006</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>BSMA0006.1</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>BSMA0006.1.6</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>1 = Include</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>File not found at specified location</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>1 = Journal article</t>
-        </is>
-      </c>
-      <c r="Q54" t="inlineStr">
-        <is>
-          <t>1 = Cross-sectional</t>
-        </is>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>1 = No (domestic only)</t>
-        </is>
-      </c>
-      <c r="V54" t="n">
-        <v>177</v>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>expatriates</t>
-        </is>
-      </c>
-      <c r="AA54" t="n">
-        <v>26</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD54" t="inlineStr">
-        <is>
-          <t>2 = Supervisor</t>
-        </is>
-      </c>
-      <c r="AF54" t="inlineStr">
-        <is>
-          <t>We developed a new scale for expatriates’ boundary-spanning following Hinkin’s (1998) scale-development procedure. ... our final 26-item scale includes nine items for functional, seven items for linguistic, and ten items for cultural boundary-spanning</t>
-        </is>
-      </c>
-      <c r="AH54" t="n">
-        <v>9</v>
-      </c>
-      <c r="AI54" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ54" t="n">
-        <v>7</v>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>1 = Self</t>
-        </is>
-      </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>Emotional exhaustion was reported by expatriates (nine items; Maslach &amp; Jackson, 1981)</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Expatriates' boundary-spanning</t>
-        </is>
-      </c>
-      <c r="AP54" t="n">
-        <v>5.27</v>
-      </c>
-      <c r="AQ54" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="AR54" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="AS54" t="inlineStr">
-        <is>
-          <t>Expatriates' emotional exhaustion</t>
-        </is>
-      </c>
-      <c r="AT54" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="AU54" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AV54" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="AW54" t="n">
-        <v>-0.01</v>
-      </c>
-    </row>
-    <row r="55" ht="15.75" customHeight="1" s="12">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>KY</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>BSMA0006</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>BSMA0006.1</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>BSMA0006.1.7</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>1 = Include</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>File not found at specified location</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>1 = Journal article</t>
-        </is>
-      </c>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>1 = Cross-sectional</t>
-        </is>
-      </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>1 = No (domestic only)</t>
-        </is>
-      </c>
-      <c r="V55" t="n">
-        <v>177</v>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>expatriates</t>
-        </is>
-      </c>
-      <c r="AA55" t="n">
-        <v>26</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD55" t="inlineStr">
-        <is>
-          <t>2 = Supervisor</t>
-        </is>
-      </c>
-      <c r="AF55" t="inlineStr">
-        <is>
-          <t>We developed a new scale for expatriates’ boundary-spanning following Hinkin’s (1998) scale-development procedure. ... our final 26-item scale includes nine items for functional, seven items for linguistic, and ten items for cultural boundary-spanning</t>
-        </is>
-      </c>
-      <c r="AH55" t="n">
-        <v>7</v>
-      </c>
-      <c r="AI55" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ55" t="n">
-        <v>7</v>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>2 = Supervisor</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>outgroup categorization was reported by host-country coworkers (seven items; Leonardelli &amp; Toh, 2011).</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Expatriates' boundary-spanning</t>
-        </is>
-      </c>
-      <c r="AP55" t="n">
-        <v>5.27</v>
-      </c>
-      <c r="AQ55" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="AR55" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="AS55" t="inlineStr">
-        <is>
-          <t>Expatriates' outgroup categorization</t>
-        </is>
-      </c>
-      <c r="AT55" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="AU55" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="AV55" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="AW55" t="n">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="56" ht="15.75" customHeight="1" s="12">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>KY</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>BSMA0006</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>BSMA0006.1</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>BSMA0006.1.8</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>1 = Include</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>File not found at specified location</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>1 = Journal article</t>
-        </is>
-      </c>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>1 = Cross-sectional</t>
-        </is>
-      </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>1 = No (domestic only)</t>
-        </is>
-      </c>
-      <c r="V56" t="n">
-        <v>177</v>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>expatriates</t>
-        </is>
-      </c>
-      <c r="AA56" t="n">
-        <v>26</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC56" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD56" t="inlineStr">
-        <is>
-          <t>2 = Supervisor</t>
-        </is>
-      </c>
-      <c r="AF56" t="inlineStr">
-        <is>
-          <t>We developed a new scale for expatriates’ boundary-spanning following Hinkin’s (1998) scale-development procedure. ... our final 26-item scale includes nine items for functional, seven items for linguistic, and ten items for cultural boundary-spanning</t>
-        </is>
-      </c>
-      <c r="AH56" t="n">
-        <v>999</v>
-      </c>
-      <c r="AI56" t="n">
-        <v>999</v>
-      </c>
-      <c r="AJ56" t="n">
-        <v>999</v>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>1 = Self</t>
-        </is>
-      </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>We included expatriates’ and host-country coworkers’ age, gender, industry, tenure in their subsidiaries, and foreign language proficiency (Liu &amp; Jackson, 2008).</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>Years</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Expatriates' boundary-spanning</t>
-        </is>
-      </c>
-      <c r="AP56" t="n">
-        <v>5.27</v>
-      </c>
-      <c r="AQ56" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="AR56" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="AS56" t="inlineStr">
-        <is>
-          <t>Expatriate age</t>
-        </is>
-      </c>
-      <c r="AT56" t="n">
-        <v>33.91</v>
-      </c>
-      <c r="AU56" t="n">
-        <v>6.64</v>
-      </c>
-      <c r="AV56" t="n">
-        <v>999</v>
-      </c>
-      <c r="AW56" t="n">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="57" ht="15.75" customHeight="1" s="12">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>KY</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>BSMA0006</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>BSMA0006.1</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>BSMA0006.1.9</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>1 = Include</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>File not found at specified location</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>1 = Journal article</t>
-        </is>
-      </c>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>1 = Cross-sectional</t>
-        </is>
-      </c>
-      <c r="U57" t="inlineStr">
-        <is>
-          <t>1 = No (domestic only)</t>
-        </is>
-      </c>
-      <c r="V57" t="n">
-        <v>177</v>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>expatriates</t>
-        </is>
-      </c>
-      <c r="AA57" t="n">
-        <v>26</v>
-      </c>
-      <c r="AB57" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC57" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD57" t="inlineStr">
-        <is>
-          <t>2 = Supervisor</t>
-        </is>
-      </c>
-      <c r="AF57" t="inlineStr">
-        <is>
-          <t>We developed a new scale for expatriates’ boundary-spanning following Hinkin’s (1998) scale-development procedure. ... our final 26-item scale includes nine items for functional, seven items for linguistic, and ten items for cultural boundary-spanning</t>
-        </is>
-      </c>
-      <c r="AH57" t="n">
-        <v>999</v>
-      </c>
-      <c r="AI57" t="n">
-        <v>999</v>
-      </c>
-      <c r="AJ57" t="n">
-        <v>999</v>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>1 = Self</t>
-        </is>
-      </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>We included expatriates’ and host-country coworkers’ age, gender, industry, tenure in their subsidiaries, and foreign language proficiency (Liu &amp; Jackson, 2008).</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>1 = male, 2 = female</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Expatriates' boundary-spanning</t>
-        </is>
-      </c>
-      <c r="AP57" t="n">
-        <v>5.27</v>
-      </c>
-      <c r="AQ57" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="AR57" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="AS57" t="inlineStr">
-        <is>
-          <t>Expatriate gender</t>
-        </is>
-      </c>
-      <c r="AT57" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AU57" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AV57" t="n">
-        <v>999</v>
-      </c>
-      <c r="AW57" t="n">
-        <v>-0.06</v>
-      </c>
-    </row>
-    <row r="58" ht="15.75" customHeight="1" s="12">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>KY</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>BSMA0006</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>BSMA0006.1</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>BSMA0006.1.10</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>1 = Include</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>File not found at specified location</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>1 = Journal article</t>
-        </is>
-      </c>
-      <c r="Q58" t="inlineStr">
-        <is>
-          <t>1 = Cross-sectional</t>
-        </is>
-      </c>
-      <c r="U58" t="inlineStr">
-        <is>
-          <t>1 = No (domestic only)</t>
-        </is>
-      </c>
-      <c r="V58" t="n">
-        <v>177</v>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>expatriates</t>
-        </is>
-      </c>
-      <c r="AA58" t="n">
-        <v>26</v>
-      </c>
-      <c r="AB58" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC58" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD58" t="inlineStr">
-        <is>
-          <t>2 = Supervisor</t>
-        </is>
-      </c>
-      <c r="AF58" t="inlineStr">
-        <is>
-          <t>We developed a new scale for expatriates’ boundary-spanning following Hinkin’s (1998) scale-development procedure. ... our final 26-item scale includes nine items for functional, seven items for linguistic, and ten items for cultural boundary-spanning</t>
-        </is>
-      </c>
-      <c r="AH58" t="n">
-        <v>999</v>
-      </c>
-      <c r="AI58" t="n">
-        <v>999</v>
-      </c>
-      <c r="AJ58" t="n">
-        <v>999</v>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>1 = Self</t>
-        </is>
-      </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>We included expatriates’ and host-country coworkers’ age, gender, industry, tenure in their subsidiaries, and foreign language proficiency (Liu &amp; Jackson, 2008).</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>Years</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Expatriates' boundary-spanning</t>
-        </is>
-      </c>
-      <c r="AP58" t="n">
-        <v>5.27</v>
-      </c>
-      <c r="AQ58" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="AR58" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="AS58" t="inlineStr">
-        <is>
-          <t>Expatriate tenure</t>
-        </is>
-      </c>
-      <c r="AT58" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AU58" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="AV58" t="n">
-        <v>999</v>
-      </c>
-      <c r="AW58" t="n">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="59" ht="15.75" customHeight="1" s="12">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>KY</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>BSMA0006</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>BSMA0006.1</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>BSMA0006.1.11</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>1 = Include</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>File not found at specified location</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>1 = Journal article</t>
-        </is>
-      </c>
-      <c r="Q59" t="inlineStr">
-        <is>
-          <t>1 = Cross-sectional</t>
-        </is>
-      </c>
-      <c r="U59" t="inlineStr">
-        <is>
-          <t>1 = No (domestic only)</t>
-        </is>
-      </c>
-      <c r="V59" t="n">
-        <v>177</v>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>expatriates</t>
-        </is>
-      </c>
-      <c r="AA59" t="n">
-        <v>26</v>
-      </c>
-      <c r="AB59" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC59" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD59" t="inlineStr">
-        <is>
-          <t>2 = Supervisor</t>
-        </is>
-      </c>
-      <c r="AF59" t="inlineStr">
-        <is>
-          <t>We developed a new scale for expatriates’ boundary-spanning following Hinkin’s (1998) scale-development procedure. ... our final 26-item scale includes nine items for functional, seven items for linguistic, and ten items for cultural boundary-spanning</t>
-        </is>
-      </c>
-      <c r="AH59" t="n">
-        <v>999</v>
-      </c>
-      <c r="AI59" t="n">
-        <v>999</v>
-      </c>
-      <c r="AJ59" t="n">
-        <v>999</v>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>1 = Self</t>
-        </is>
-      </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>We included expatriates’ and host-country coworkers’ age, gender, industry, tenure in their subsidiaries, and foreign language proficiency (Liu &amp; Jackson, 2008).</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>Proxy for language proficiency.</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Expatriates' boundary-spanning</t>
-        </is>
-      </c>
-      <c r="AP59" t="n">
-        <v>5.27</v>
-      </c>
-      <c r="AQ59" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="AR59" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="AS59" t="inlineStr">
-        <is>
-          <t>Expatriate language proficiency</t>
-        </is>
-      </c>
-      <c r="AT59" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AU59" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AV59" t="n">
-        <v>999</v>
-      </c>
-      <c r="AW59" t="n">
-        <v>0.47</v>
-      </c>
-    </row>
-    <row r="60" ht="15.75" customHeight="1" s="12">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>KY</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>BSMA0006</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>BSMA0006.1</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>BSMA0006.1.12</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>1 = Include</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>File not found at specified location</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>1 = Journal article</t>
-        </is>
-      </c>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t>1 = Cross-sectional</t>
-        </is>
-      </c>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>1 = No (domestic only)</t>
-        </is>
-      </c>
-      <c r="V60" t="n">
-        <v>177</v>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>expatriates</t>
-        </is>
-      </c>
-      <c r="AA60" t="n">
-        <v>26</v>
-      </c>
-      <c r="AB60" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC60" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD60" t="inlineStr">
-        <is>
-          <t>2 = Supervisor</t>
-        </is>
-      </c>
-      <c r="AF60" t="inlineStr">
-        <is>
-          <t>We developed a new scale for expatriates’ boundary-spanning following Hinkin’s (1998) scale-development procedure. ... our final 26-item scale includes nine items for functional, seven items for linguistic, and ten items for cultural boundary-spanning</t>
-        </is>
-      </c>
-      <c r="AH60" t="n">
-        <v>999</v>
-      </c>
-      <c r="AI60" t="n">
-        <v>999</v>
-      </c>
-      <c r="AJ60" t="n">
-        <v>999</v>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>1 = Self</t>
-        </is>
-      </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>We included expatriates’ and host-country coworkers’ age, gender, industry, tenure in their subsidiaries, and foreign language proficiency (Liu &amp; Jackson, 2008).</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>Dummy control variable.</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Expatriates' boundary-spanning</t>
-        </is>
-      </c>
-      <c r="AP60" t="n">
-        <v>5.27</v>
-      </c>
-      <c r="AQ60" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="AR60" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="AS60" t="inlineStr">
-        <is>
-          <t>Industry</t>
-        </is>
-      </c>
-      <c r="AT60" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AU60" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="AV60" t="n">
-        <v>999</v>
-      </c>
-      <c r="AW60" t="n">
-        <v>-0.08</v>
-      </c>
-    </row>
+    <row r="46" ht="15.75" customHeight="1" s="12"/>
+    <row r="47" ht="15.75" customHeight="1" s="12"/>
+    <row r="48" ht="15.75" customHeight="1" s="12"/>
+    <row r="49" ht="15.75" customHeight="1" s="12"/>
+    <row r="50" ht="15.75" customHeight="1" s="12"/>
+    <row r="51" ht="15.75" customHeight="1" s="12"/>
+    <row r="52" ht="15.75" customHeight="1" s="12"/>
+    <row r="53" ht="15.75" customHeight="1" s="12"/>
+    <row r="54" ht="15.75" customHeight="1" s="12"/>
+    <row r="55" ht="15.75" customHeight="1" s="12"/>
+    <row r="56" ht="15.75" customHeight="1" s="12"/>
+    <row r="57" ht="15.75" customHeight="1" s="12"/>
+    <row r="58" ht="15.75" customHeight="1" s="12"/>
+    <row r="59" ht="15.75" customHeight="1" s="12"/>
+    <row r="60" ht="15.75" customHeight="1" s="12"/>
     <row r="61" ht="15.75" customHeight="1" s="12"/>
-    <row r="62" ht="15.75" customHeight="1" s="12">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>KY</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>BSMA0007</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>0 = Exclude</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>The boundary spanner is at the organizational level (inpatient psychiatric departments) rather than an individual employee.</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="15.75" customHeight="1" s="12">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>KY</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>BSMA0008</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>BSMA0008.1</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>BSMA0008.1.1</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>1 = Include</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>1 = Journal article</t>
-        </is>
-      </c>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>1 = Cross-sectional</t>
-        </is>
-      </c>
-      <c r="U63" t="inlineStr">
-        <is>
-          <t>1 = No (domestic only)</t>
-        </is>
-      </c>
-      <c r="V63" t="n">
-        <v>190</v>
-      </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>MBA students / Consulting</t>
-        </is>
-      </c>
-      <c r="AA63" t="n">
-        <v>6</v>
-      </c>
-      <c r="AB63" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC63" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD63" t="inlineStr">
-        <is>
-          <t>3 = Others</t>
-        </is>
-      </c>
-      <c r="AF63" t="inlineStr">
-        <is>
-          <t>six items adapted directly from Ancona and Caldwell's (1992) study and modified to reflect the current consulting team context.</t>
-        </is>
-      </c>
-      <c r="AH63" t="n">
-        <v>6</v>
-      </c>
-      <c r="AI63" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ63" t="n">
-        <v>5</v>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>1 = Self</t>
-        </is>
-      </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>all participants rate the extent to which they perceived each of the six boundary spanning behaviors as an expected part of their responsibilities</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Boundary-spanning behavior</t>
-        </is>
-      </c>
-      <c r="AP63" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AQ63" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AR63" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="AS63" t="inlineStr">
-        <is>
-          <t>Boundary-spanning role</t>
-        </is>
-      </c>
-      <c r="AT63" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="AU63" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="AV63" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="AW63" t="n">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="64" ht="15.75" customHeight="1" s="12">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>KY</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>BSMA0008</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>BSMA0008.1</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>BSMA0008.1.2</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>1 = Include</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>1 = Journal article</t>
-        </is>
-      </c>
-      <c r="Q64" t="inlineStr">
-        <is>
-          <t>1 = Cross-sectional</t>
-        </is>
-      </c>
-      <c r="U64" t="inlineStr">
-        <is>
-          <t>1 = No (domestic only)</t>
-        </is>
-      </c>
-      <c r="V64" t="n">
-        <v>190</v>
-      </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>MBA students / Consulting</t>
-        </is>
-      </c>
-      <c r="AA64" t="n">
-        <v>6</v>
-      </c>
-      <c r="AB64" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC64" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD64" t="inlineStr">
-        <is>
-          <t>3 = Others</t>
-        </is>
-      </c>
-      <c r="AF64" t="inlineStr">
-        <is>
-          <t>six items adapted directly from Ancona and Caldwell's (1992) study and modified to reflect the current consulting team context.</t>
-        </is>
-      </c>
-      <c r="AH64" t="n">
-        <v>8</v>
-      </c>
-      <c r="AI64" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ64" t="n">
-        <v>5</v>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>1 = Self</t>
-        </is>
-      </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>Scale items were based in part upon Parker's (1998) role breadth self-efficacy scale</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Boundary-spanning behavior</t>
-        </is>
-      </c>
-      <c r="AP64" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AQ64" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AR64" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="AS64" t="inlineStr">
-        <is>
-          <t>Boundary-spanning self-efficacy</t>
-        </is>
-      </c>
-      <c r="AT64" t="n">
-        <v>4.07</v>
-      </c>
-      <c r="AU64" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="AV64" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="AW64" t="n">
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="65" ht="15.75" customHeight="1" s="12">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>KY</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>BSMA0008</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>BSMA0008.1</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>BSMA0008.1.3</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>1 = Include</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>1 = Journal article</t>
-        </is>
-      </c>
-      <c r="Q65" t="inlineStr">
-        <is>
-          <t>1 = Cross-sectional</t>
-        </is>
-      </c>
-      <c r="U65" t="inlineStr">
-        <is>
-          <t>1 = No (domestic only)</t>
-        </is>
-      </c>
-      <c r="V65" t="n">
-        <v>190</v>
-      </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>MBA students / Consulting</t>
-        </is>
-      </c>
-      <c r="AA65" t="n">
-        <v>6</v>
-      </c>
-      <c r="AB65" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC65" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD65" t="inlineStr">
-        <is>
-          <t>3 = Others</t>
-        </is>
-      </c>
-      <c r="AF65" t="inlineStr">
-        <is>
-          <t>six items adapted directly from Ancona and Caldwell's (1992) study and modified to reflect the current consulting team context.</t>
-        </is>
-      </c>
-      <c r="AH65" t="n">
-        <v>999</v>
-      </c>
-      <c r="AI65" t="n">
-        <v>999</v>
-      </c>
-      <c r="AJ65" t="n">
-        <v>999</v>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>1 = Self</t>
-        </is>
-      </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>Asian ethnicity (1, Asian, and 0, other)</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>Demographic</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Boundary-spanning behavior</t>
-        </is>
-      </c>
-      <c r="AP65" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AQ65" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AR65" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="AS65" t="inlineStr">
-        <is>
-          <t>Asian ethnicity</t>
-        </is>
-      </c>
-      <c r="AT65" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="AU65" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="AV65" t="n">
-        <v>999</v>
-      </c>
-      <c r="AW65" t="n">
-        <v>-0.23</v>
-      </c>
-    </row>
-    <row r="66" ht="15.75" customHeight="1" s="12">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>KY</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>BSMA0008</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>BSMA0008.1</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>BSMA0008.1.4</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>1 = Include</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t>1 = Journal article</t>
-        </is>
-      </c>
-      <c r="Q66" t="inlineStr">
-        <is>
-          <t>1 = Cross-sectional</t>
-        </is>
-      </c>
-      <c r="U66" t="inlineStr">
-        <is>
-          <t>1 = No (domestic only)</t>
-        </is>
-      </c>
-      <c r="V66" t="n">
-        <v>190</v>
-      </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>MBA students / Consulting</t>
-        </is>
-      </c>
-      <c r="AA66" t="n">
-        <v>6</v>
-      </c>
-      <c r="AB66" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC66" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD66" t="inlineStr">
-        <is>
-          <t>3 = Others</t>
-        </is>
-      </c>
-      <c r="AF66" t="inlineStr">
-        <is>
-          <t>six items adapted directly from Ancona and Caldwell's (1992) study and modified to reflect the current consulting team context.</t>
-        </is>
-      </c>
-      <c r="AH66" t="n">
-        <v>999</v>
-      </c>
-      <c r="AI66" t="n">
-        <v>999</v>
-      </c>
-      <c r="AJ66" t="n">
-        <v>999</v>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>1 = Self</t>
-        </is>
-      </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>GMAT score (a continuous score)</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>Proxy</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Boundary-spanning behavior</t>
-        </is>
-      </c>
-      <c r="AP66" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AQ66" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AR66" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="AS66" t="inlineStr">
-        <is>
-          <t>GMAT score</t>
-        </is>
-      </c>
-      <c r="AT66" t="n">
-        <v>653.9</v>
-      </c>
-      <c r="AU66" t="n">
-        <v>57.89</v>
-      </c>
-      <c r="AV66" t="n">
-        <v>999</v>
-      </c>
-      <c r="AW66" t="n">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="67" ht="15.75" customHeight="1" s="12">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>KY</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>BSMA0008</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>BSMA0008.1</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>BSMA0008.1.5</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>1 = Include</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t>1 = Journal article</t>
-        </is>
-      </c>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>1 = Cross-sectional</t>
-        </is>
-      </c>
-      <c r="U67" t="inlineStr">
-        <is>
-          <t>1 = No (domestic only)</t>
-        </is>
-      </c>
-      <c r="V67" t="n">
-        <v>190</v>
-      </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>MBA students / Consulting</t>
-        </is>
-      </c>
-      <c r="AA67" t="n">
-        <v>6</v>
-      </c>
-      <c r="AB67" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC67" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD67" t="inlineStr">
-        <is>
-          <t>3 = Others</t>
-        </is>
-      </c>
-      <c r="AF67" t="inlineStr">
-        <is>
-          <t>six items adapted directly from Ancona and Caldwell's (1992) study and modified to reflect the current consulting team context.</t>
-        </is>
-      </c>
-      <c r="AH67" t="n">
-        <v>3</v>
-      </c>
-      <c r="AI67" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ67" t="n">
-        <v>5</v>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>1 = Self</t>
-        </is>
-      </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>Three items were adapted from Beehr et al. (1976) and modified for the current context.</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Boundary-spanning behavior</t>
-        </is>
-      </c>
-      <c r="AP67" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="AQ67" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AR67" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="AS67" t="inlineStr">
-        <is>
-          <t>Role overload</t>
-        </is>
-      </c>
-      <c r="AT67" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="AU67" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="AV67" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="AW67" t="n">
-        <v>0.18</v>
-      </c>
-    </row>
+    <row r="62" ht="15.75" customHeight="1" s="12"/>
+    <row r="63" ht="15.75" customHeight="1" s="12"/>
+    <row r="64" ht="15.75" customHeight="1" s="12"/>
+    <row r="65" ht="15.75" customHeight="1" s="12"/>
+    <row r="66" ht="15.75" customHeight="1" s="12"/>
+    <row r="67" ht="15.75" customHeight="1" s="12"/>
     <row r="68" ht="15.75" customHeight="1" s="12"/>
     <row r="69" ht="15.75" customHeight="1" s="12"/>
     <row r="70" ht="15.75" customHeight="1" s="12"/>

--- a/BSMA_Master_Coding_Sheet.xlsx
+++ b/BSMA_Master_Coding_Sheet.xlsx
@@ -501,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX3"/>
+  <dimension ref="A1:AX5"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.25" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="10.5625" customWidth="1" style="12" min="1" max="2"/>
@@ -828,8 +828,66 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="15.75" customHeight="1" s="12"/>
-    <row r="5" ht="15.75" customHeight="1" s="12"/>
+    <row r="4" ht="15.75" customHeight="1" s="12">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>File not found</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1" s="12">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Qualitative study; no quantitative boundary spanning data</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>It is ok to be interrupted; it is my job</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Qualitative Research in Organizations and Management: An International Journal</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>De Alwis et al.</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>2022</v>
+      </c>
+    </row>
     <row r="6" ht="15.75" customHeight="1" s="12"/>
     <row r="7" ht="15.75" customHeight="1" s="12"/>
     <row r="8" ht="15.75" customHeight="1" s="12"/>

--- a/BSMA_Master_Coding_Sheet.xlsx
+++ b/BSMA_Master_Coding_Sheet.xlsx
@@ -501,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX8"/>
+  <dimension ref="A1:AX9"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.25" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="10.5625" customWidth="1" style="12" min="1" max="2"/>
@@ -859,6 +859,16 @@
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1" s="12">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BSMA0002</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>0 = Exclude</t>
@@ -953,7 +963,36 @@
         <v>1973</v>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1" s="12"/>
+    <row r="9" ht="15.75" customHeight="1" s="12">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Not quantitative empirical (qualitative interviews without a correlation matrix).</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>‘Everything else is public relations’: How rural journalists draw the boundary between journalism and public relations in rural communities</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Mass Communication &amp; Society</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Mildred F. Perreault, Jessica Walsh, Louisa Lincoln, Gregory Perreault, Ruth Moon</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>2023</v>
+      </c>
+    </row>
     <row r="10" ht="15.75" customHeight="1" s="12"/>
     <row r="11" ht="15.75" customHeight="1" s="12"/>
     <row r="12" ht="15.75" customHeight="1" s="12"/>

--- a/BSMA_Master_Coding_Sheet.xlsx
+++ b/BSMA_Master_Coding_Sheet.xlsx
@@ -501,7 +501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX9"/>
+  <dimension ref="A1:AX10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.25" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="10.5625" customWidth="1" style="12" min="1" max="2"/>
@@ -993,7 +993,41 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="10" ht="15.75" customHeight="1" s="12"/>
+    <row r="10" ht="15.75" customHeight="1" s="12">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BSMA0007</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0 = Exclude</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Boundary spanner is a department (team level)</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>A Comparative Organizational Study of Performance and Size Correlates in Inpatient Psychiatric Departments</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Administrative Science Quarterly</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Hrebiniak et al.</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>1973</v>
+      </c>
+    </row>
     <row r="11" ht="15.75" customHeight="1" s="12"/>
     <row r="12" ht="15.75" customHeight="1" s="12"/>
     <row r="13" ht="15.75" customHeight="1" s="12"/>

--- a/BSMA_Master_Coding_Sheet.xlsx
+++ b/BSMA_Master_Coding_Sheet.xlsx
@@ -829,14 +829,29 @@
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1" s="12">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>BSMA0001</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>BSMA0001.1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>BSMA0001.1.1</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0 = Exclude</t>
+          <t>1 = Include</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -856,11 +871,105 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Lee et al.</t>
+          <t>Lee</t>
         </is>
       </c>
       <c r="K4" t="n">
         <v>2023</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>1 = Journal article</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>1 = Cross-sectional</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>1 = No (domestic only)</t>
+        </is>
+      </c>
+      <c r="V4" t="n">
+        <v>383</v>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>manufacturing, telecommunication, and service sectors</t>
+        </is>
+      </c>
+      <c r="AA4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>2 = Supervisor</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>Leader boundary-spanning behavior was measured with 6 items developed by Marrone et al. [36].</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>2 = Supervisor</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>To assess the perception of abusive supervision, we used a shortened five-item version of Tepper [27,79].</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Leader Boundary-Spanning Behavior</t>
+        </is>
+      </c>
+      <c r="AP4" t="n">
+        <v>5.31</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>Abusive Supervision</t>
+        </is>
+      </c>
+      <c r="AT4" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>-0.57</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1" s="12"/>

--- a/BSMA_Master_Coding_Sheet.xlsx
+++ b/BSMA_Master_Coding_Sheet.xlsx
@@ -861,7 +861,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Leader Boundary-Spanning Behavior and Employee Voice Behavior: The Job Demands-Resources Perspective</t>
+          <t>Leader Boundary-Spanning Behavior and Employee Voice Behavior: The Job Demands–Resources Perspective</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Lee</t>
+          <t>Lee et al.</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -897,7 +897,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>manufacturing, telecommunication, and service sectors</t>
+          <t>Various industries</t>
         </is>
       </c>
       <c r="AA4" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>Leader boundary-spanning behavior was measured with 6 items developed by Marrone et al. [36].</t>
+          <t>measured with 6 items developed by Marrone et al. [ 36].</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr"/>
@@ -936,7 +936,7 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>To assess the perception of abusive supervision, we used a shortened five-item version of Tepper [27,79].</t>
+          <t>shortened ﬁve-item version of Tepper [ 27,79].</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr"/>

--- a/BSMA_Master_Coding_Sheet.xlsx
+++ b/BSMA_Master_Coding_Sheet.xlsx
@@ -972,7 +972,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>“'Everything else is public relations'”: How rural journalists draw the boundary between journalism and public relations in rural communities</t>
+          <t>“‘Everything else is public relations’”: How rural journalists draw the boundary between journalism and public relations in rural communities</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">

--- a/BSMA_Master_Coding_Sheet.xlsx
+++ b/BSMA_Master_Coding_Sheet.xlsx
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX18"/>
+  <dimension ref="A1:AX24"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.25" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="10.5625" customWidth="1" style="9" min="1" max="2"/>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Liu et al.</t>
+          <t>LIU Songbo &amp; LI Yuhui</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>High-tech park employees</t>
+          <t>employees from high-tech enterprises</t>
         </is>
       </c>
       <c r="AA12" t="n">
@@ -1662,10 +1662,14 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>员工的跨界行为 采用的是 Marrone 等(2007) 开发的量表。原量表共 6个条目 , 我们删除了原量表中专门针对样本 (咨询团队 )特点设计的 1个条目 , 所以共 5个条目 , 比如 “我会从团队外部人那里为我们团队寻求建议 ”等。</t>
-        </is>
-      </c>
-      <c r="AG12" t="inlineStr"/>
+          <t>采用的是 Marrone 等(2007)开发的量表。原量表共 6个条目 , 我们删除了原量表中专门针对样本 (咨询团队 )特点设计的 1个条目 , 所以共 5个条目 , 比如 “我会从团队外部人那里为我们团队寻求建议 ”等。</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>5 items adapted from Marrone et al. (2007) 6-item scale, 1 item deleted</t>
+        </is>
+      </c>
       <c r="AH12" t="n">
         <v>999</v>
       </c>
@@ -1675,8 +1679,10 @@
       <c r="AJ12" t="n">
         <v>999</v>
       </c>
-      <c r="AK12" t="n">
-        <v>999</v>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>1 = Self</t>
+        </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
@@ -1690,7 +1696,7 @@
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>员工跨界行为</t>
+          <t>Employee boundary-spanning behavior</t>
         </is>
       </c>
       <c r="AP12" t="n">
@@ -1704,7 +1710,7 @@
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>员工年龄</t>
+          <t>Employee Age</t>
         </is>
       </c>
       <c r="AT12" t="n">
@@ -1758,7 +1764,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Liu et al.</t>
+          <t>LIU Songbo &amp; LI Yuhui</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1784,7 +1790,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>High-tech park employees</t>
+          <t>employees from high-tech enterprises</t>
         </is>
       </c>
       <c r="AA13" t="n">
@@ -1803,10 +1809,14 @@
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>员工的跨界行为 采用的是 Marrone 等(2007) 开发的量表。原量表共 6个条目 , 我们删除了原量表中专门针对样本 (咨询团队 )特点设计的 1个条目 , 所以共 5个条目 , 比如 “我会从团队外部人那里为我们团队寻求建议 ”等。</t>
-        </is>
-      </c>
-      <c r="AG13" t="inlineStr"/>
+          <t>采用的是 Marrone 等(2007)开发的量表。原量表共 6个条目 , 我们删除了原量表中专门针对样本 (咨询团队 )特点设计的 1个条目 , 所以共 5个条目 , 比如 “我会从团队外部人那里为我们团队寻求建议 ”等。</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>5 items adapted from Marrone et al. (2007) 6-item scale, 1 item deleted</t>
+        </is>
+      </c>
       <c r="AH13" t="n">
         <v>999</v>
       </c>
@@ -1816,8 +1826,10 @@
       <c r="AJ13" t="n">
         <v>999</v>
       </c>
-      <c r="AK13" t="n">
-        <v>999</v>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>1 = Self</t>
+        </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
@@ -1826,12 +1838,12 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>1 = male, 0 = female</t>
+          <t>0 = Female, 1 = Male</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>员工跨界行为</t>
+          <t>Employee boundary-spanning behavior</t>
         </is>
       </c>
       <c r="AP13" t="n">
@@ -1845,7 +1857,7 @@
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>员工性别</t>
+          <t>Employee Gender</t>
         </is>
       </c>
       <c r="AT13" t="n">
@@ -1899,7 +1911,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Liu et al.</t>
+          <t>LIU Songbo &amp; LI Yuhui</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1925,7 +1937,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>High-tech park employees</t>
+          <t>employees from high-tech enterprises</t>
         </is>
       </c>
       <c r="AA14" t="n">
@@ -1944,10 +1956,14 @@
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>员工的跨界行为 采用的是 Marrone 等(2007) 开发的量表。原量表共 6个条目 , 我们删除了原量表中专门针对样本 (咨询团队 )特点设计的 1个条目 , 所以共 5个条目 , 比如 “我会从团队外部人那里为我们团队寻求建议 ”等。</t>
-        </is>
-      </c>
-      <c r="AG14" t="inlineStr"/>
+          <t>采用的是 Marrone 等(2007)开发的量表。原量表共 6个条目 , 我们删除了原量表中专门针对样本 (咨询团队 )特点设计的 1个条目 , 所以共 5个条目 , 比如 “我会从团队外部人那里为我们团队寻求建议 ”等。</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>5 items adapted from Marrone et al. (2007) 6-item scale, 1 item deleted</t>
+        </is>
+      </c>
       <c r="AH14" t="n">
         <v>999</v>
       </c>
@@ -1957,8 +1973,10 @@
       <c r="AJ14" t="n">
         <v>999</v>
       </c>
-      <c r="AK14" t="n">
-        <v>999</v>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>1 = Self</t>
+        </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
@@ -1967,12 +1985,12 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>1 (high school and below) to 6 (doctoral degree)</t>
+          <t>Coded 1 (High school and below) to 6 (Doctorate)</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>员工跨界行为</t>
+          <t>Employee boundary-spanning behavior</t>
         </is>
       </c>
       <c r="AP14" t="n">
@@ -1986,7 +2004,7 @@
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>教育程度</t>
+          <t>Employee Education</t>
         </is>
       </c>
       <c r="AT14" t="n">
@@ -2040,7 +2058,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Liu et al.</t>
+          <t>LIU Songbo &amp; LI Yuhui</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -2066,7 +2084,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>High-tech park employees</t>
+          <t>employees from high-tech enterprises</t>
         </is>
       </c>
       <c r="AA15" t="n">
@@ -2085,10 +2103,14 @@
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>员工的跨界行为 采用的是 Marrone 等(2007) 开发的量表。原量表共 6个条目 , 我们删除了原量表中专门针对样本 (咨询团队 )特点设计的 1个条目 , 所以共 5个条目 , 比如 “我会从团队外部人那里为我们团队寻求建议 ”等。</t>
-        </is>
-      </c>
-      <c r="AG15" t="inlineStr"/>
+          <t>采用的是 Marrone 等(2007)开发的量表。原量表共 6个条目 , 我们删除了原量表中专门针对样本 (咨询团队 )特点设计的 1个条目 , 所以共 5个条目 , 比如 “我会从团队外部人那里为我们团队寻求建议 ”等。</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>5 items adapted from Marrone et al. (2007) 6-item scale, 1 item deleted</t>
+        </is>
+      </c>
       <c r="AH15" t="n">
         <v>999</v>
       </c>
@@ -2098,8 +2120,10 @@
       <c r="AJ15" t="n">
         <v>999</v>
       </c>
-      <c r="AK15" t="n">
-        <v>999</v>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>1 = Self</t>
+        </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
@@ -2113,7 +2137,7 @@
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>员工跨界行为</t>
+          <t>Employee boundary-spanning behavior</t>
         </is>
       </c>
       <c r="AP15" t="n">
@@ -2127,7 +2151,7 @@
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>本团队工作时间</t>
+          <t>Team Tenure</t>
         </is>
       </c>
       <c r="AT15" t="n">
@@ -2181,7 +2205,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Liu et al.</t>
+          <t>LIU Songbo &amp; LI Yuhui</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -2207,7 +2231,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>High-tech park employees</t>
+          <t>employees from high-tech enterprises</t>
         </is>
       </c>
       <c r="AA16" t="n">
@@ -2226,10 +2250,14 @@
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>员工的跨界行为 采用的是 Marrone 等(2007) 开发的量表。原量表共 6个条目 , 我们删除了原量表中专门针对样本 (咨询团队 )特点设计的 1个条目 , 所以共 5个条目 , 比如 “我会从团队外部人那里为我们团队寻求建议 ”等。</t>
-        </is>
-      </c>
-      <c r="AG16" t="inlineStr"/>
+          <t>采用的是 Marrone 等(2007)开发的量表。原量表共 6个条目 , 我们删除了原量表中专门针对样本 (咨询团队 )特点设计的 1个条目 , 所以共 5个条目 , 比如 “我会从团队外部人那里为我们团队寻求建议 ”等。</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>5 items adapted from Marrone et al. (2007) 6-item scale, 1 item deleted</t>
+        </is>
+      </c>
       <c r="AH16" t="n">
         <v>3</v>
       </c>
@@ -2246,13 +2274,13 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>集体主义 采用 Ilies, Wagner 和Morgeson (2007) 使用过的量表 , 共3个条目 , 比如 “比起独自工作来说 , 我更愿意和同事一起工作 ”等。</t>
+          <t>集体主义   采用 Ilies, Wagner 和Morgeson (2007) 使用过的量表 , 共3个条目 , 比如 “比起独自工作来说 , 我更愿意和同事一起工作 ”等。在本研究中使用 Likert 7 点测量方法 , 1表示 “非常不同意 ”, 7表示 “非常同意 ”。</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr"/>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>员工跨界行为</t>
+          <t>Employee boundary-spanning behavior</t>
         </is>
       </c>
       <c r="AP16" t="n">
@@ -2266,7 +2294,7 @@
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>集体主义导向</t>
+          <t>Collectivism orientation</t>
         </is>
       </c>
       <c r="AT16" t="n">
@@ -2320,7 +2348,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Liu et al.</t>
+          <t>LIU Songbo &amp; LI Yuhui</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -2346,7 +2374,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>High-tech park employees</t>
+          <t>employees from high-tech enterprises</t>
         </is>
       </c>
       <c r="AA17" t="n">
@@ -2365,10 +2393,14 @@
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>员工的跨界行为 采用的是 Marrone 等(2007) 开发的量表。原量表共 6个条目 , 我们删除了原量表中专门针对样本 (咨询团队 )特点设计的 1个条目 , 所以共 5个条目 , 比如 “我会从团队外部人那里为我们团队寻求建议 ”等。</t>
-        </is>
-      </c>
-      <c r="AG17" t="inlineStr"/>
+          <t>采用的是 Marrone 等(2007)开发的量表。原量表共 6个条目 , 我们删除了原量表中专门针对样本 (咨询团队 )特点设计的 1个条目 , 所以共 5个条目 , 比如 “我会从团队外部人那里为我们团队寻求建议 ”等。</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>5 items adapted from Marrone et al. (2007) 6-item scale, 1 item deleted</t>
+        </is>
+      </c>
       <c r="AH17" t="n">
         <v>2</v>
       </c>
@@ -2385,17 +2417,13 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>咨询网络中心性 采用的是 Sparrowe 等(2001) 采用的点入中心性 (in-degree centrality, Borgatti, Everett, &amp; Freeman, 1992) 的测量方法。为了收集整体网络数据 , 我们在每个团队中都列上了所有成员的名字 , 然后要求员工对其同事进行评价。量表共 2个条目 , 比如 “你向 (某某 )寻求有关工作的帮助或建议吗 ”。我们关心的是这种关系的强度 (strength), 所以通过 Likert 5 点来进行测量 , 1表示 “从不 ”, 5表示 “总是 ”。</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>Advice network centrality</t>
-        </is>
-      </c>
+          <t>咨询网络中心性   采用的是 Sparrowe 等(2001) 采用的点入中心性 (in-degree centrality, Borgatti, Everett, &amp; Freeman, 1992) 的测量方法。为了收集整体 network 数据 , 我们在每个团队中都列上了所有成员的名字 , 然后要求员工对其同事进行评价。量表共 2个条目 , 比如 “你向 (某某 )寻求有关工作的帮助或建议吗 ”。我们关心的是这种关系的强度 (strength), 所以通过 Likert 5 点来进行测量 , 1表示 “从不 ”, 5表示“总是 ”。所谓点入中心性是相对于点出中心性 (out-degree centrality, 员工本人评价的与自己其他成员的关系 )而言的 , 指的是每个员工来自团队中其他成员评价的网络地位的均值。</t>
+        </is>
+      </c>
+      <c r="AN17" t="inlineStr"/>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>员工跨界行为</t>
+          <t>Employee boundary-spanning behavior</t>
         </is>
       </c>
       <c r="AP17" t="n">
@@ -2409,7 +2437,7 @@
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>网络中心性</t>
+          <t>Advice network centrality</t>
         </is>
       </c>
       <c r="AT17" t="n">
@@ -2463,7 +2491,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Liu et al.</t>
+          <t>LIU Songbo &amp; LI Yuhui</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -2489,7 +2517,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>High-tech park employees</t>
+          <t>employees from high-tech enterprises</t>
         </is>
       </c>
       <c r="AA18" t="n">
@@ -2508,10 +2536,14 @@
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>员工的跨界行为 采用的是 Marrone 等(2007) 开发的量表。原量表共 6个条目 , 我们删除了原量表中专门针对样本 (咨询团队 )特点设计的 1个条目 , 所以共 5个条目 , 比如 “我会从团队外部人那里为我们团队寻求建议 ”等。</t>
-        </is>
-      </c>
-      <c r="AG18" t="inlineStr"/>
+          <t>采用的是 Marrone 等(2007)开发的量表。原量表共 6个条目 , 我们删除了原量表中专门针对样本 (咨询团队 )特点设计的 1个条目 , 所以共 5个条目 , 比如 “我会从团队外部人那里为我们团队寻求建议 ”等。</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>5 items adapted from Marrone et al. (2007) 6-item scale, 1 item deleted</t>
+        </is>
+      </c>
       <c r="AH18" t="n">
         <v>4</v>
       </c>
@@ -2528,13 +2560,13 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>任务绩效 采用的是 Liden, Wayne 和Stilwell (1993) 开发的量表 , 共4个条目 , 比如 “这名员工能够充分完成分配的任务 ”等, 由领导填写。</t>
+          <t>任务绩效  采用的是 Liden, Wayne 和Stilwell (1993) 开发的量表 , 共4个条目 , 比如 “这名员工能够充分完成分配的任务 ”等, 由领导填写。在本研究中使用 Likert7 点测量方法 , 1表示 “非常不同意 ”, 7表示 “非常同意 ”。</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr"/>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>员工跨界行为</t>
+          <t>Employee boundary-spanning behavior</t>
         </is>
       </c>
       <c r="AP18" t="n">
@@ -2548,7 +2580,7 @@
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>任务绩效</t>
+          <t>Task performance</t>
         </is>
       </c>
       <c r="AT18" t="n">
@@ -2564,12 +2596,842 @@
         <v>0.31</v>
       </c>
     </row>
-    <row r="19" ht="15.75" customHeight="1" s="9"/>
-    <row r="20" ht="15.75" customHeight="1" s="9"/>
-    <row r="21" ht="15.75" customHeight="1" s="9"/>
-    <row r="22" ht="15.75" customHeight="1" s="9"/>
-    <row r="23" ht="15.75" customHeight="1" s="9"/>
-    <row r="24" ht="15.75" customHeight="1" s="9"/>
+    <row r="19" ht="15.75" customHeight="1" s="9">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>BSMA0004</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>BSMA0004.1</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>BSMA0004.1.2</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1 = Include</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>A Longitudinal Study on the Impact Mechanism of Employees’ Boundary Spanning Behavior: Roles of Centrality and Collectivism</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Acta Psychologica Sinica</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Liu et al.</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>2014</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>1 = Journal article</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>2 = Longitudinal/time-lagged</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>1 = No (domestic only)</t>
+        </is>
+      </c>
+      <c r="V19" t="n">
+        <v>292</v>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>High-tech park employees</t>
+        </is>
+      </c>
+      <c r="AA19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>1 = Self</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>员工的跨界行为 采用的是 Marrone 等(2007) 开发的量表。原量表共 6个条目 , 我们删除了原量表中专门针对样本 (咨询团队 )特点设计的 1个条目 , 所以共 5个条目 , 比如 “我会从团队外部人那里为我们团队寻求建议 ”等。</t>
+        </is>
+      </c>
+      <c r="AH19" t="n">
+        <v>999</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>999</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>999</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>999</v>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="AN19" t="inlineStr">
+        <is>
+          <t>1 = male, 0 = female</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>员工跨界行为</t>
+        </is>
+      </c>
+      <c r="AP19" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0.869</v>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>员工性别</t>
+        </is>
+      </c>
+      <c r="AT19" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>999</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="20" ht="15.75" customHeight="1" s="9">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>BSMA0004</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>BSMA0004.1</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>BSMA0004.1.3</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1 = Include</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>A Longitudinal Study on the Impact Mechanism of Employees’ Boundary Spanning Behavior: Roles of Centrality and Collectivism</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Acta Psychologica Sinica</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Liu et al.</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>2014</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>1 = Journal article</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>2 = Longitudinal/time-lagged</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>1 = No (domestic only)</t>
+        </is>
+      </c>
+      <c r="V20" t="n">
+        <v>292</v>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>High-tech park employees</t>
+        </is>
+      </c>
+      <c r="AA20" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>1 = Self</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>员工的跨界行为 采用的是 Marrone 等(2007) 开发的量表。原量表共 6个条目 , 我们删除了原量表中专门针对样本 (咨询团队 )特点设计的 1个条目 , 所以共 5个条目 , 比如 “我会从团队外部人那里为我们团队寻求建议 ”等。</t>
+        </is>
+      </c>
+      <c r="AH20" t="n">
+        <v>999</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>999</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>999</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>999</v>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="AN20" t="inlineStr">
+        <is>
+          <t>1 (high school and below) to 6 (doctoral degree)</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>员工跨界行为</t>
+        </is>
+      </c>
+      <c r="AP20" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0.869</v>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>教育程度</t>
+        </is>
+      </c>
+      <c r="AT20" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>999</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1" s="9">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>BSMA0004</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>BSMA0004.1</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>BSMA0004.1.4</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>1 = Include</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>A Longitudinal Study on the Impact Mechanism of Employees’ Boundary Spanning Behavior: Roles of Centrality and Collectivism</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Acta Psychologica Sinica</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Liu et al.</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>2014</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>1 = Journal article</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>2 = Longitudinal/time-lagged</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>1 = No (domestic only)</t>
+        </is>
+      </c>
+      <c r="V21" t="n">
+        <v>292</v>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>High-tech park employees</t>
+        </is>
+      </c>
+      <c r="AA21" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>1 = Self</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>员工的跨界行为 采用的是 Marrone 等(2007) 开发的量表。原量表共 6个条目 , 我们删除了原量表中专门针对样本 (咨询团队 )特点设计的 1个条目 , 所以共 5个条目 , 比如 “我会从团队外部人那里为我们团队寻求建议 ”等。</t>
+        </is>
+      </c>
+      <c r="AH21" t="n">
+        <v>999</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>999</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>999</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>999</v>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="AN21" t="inlineStr">
+        <is>
+          <t>Months</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>员工跨界行为</t>
+        </is>
+      </c>
+      <c r="AP21" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0.869</v>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>本团队工作时间</t>
+        </is>
+      </c>
+      <c r="AT21" t="n">
+        <v>20.64</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>18.47</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>999</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="22" ht="15.75" customHeight="1" s="9">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>BSMA0004</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>BSMA0004.1</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>BSMA0004.1.5</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>1 = Include</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>A Longitudinal Study on the Impact Mechanism of Employees’ Boundary Spanning Behavior: Roles of Centrality and Collectivism</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Acta Psychologica Sinica</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Liu et al.</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>2014</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>1 = Journal article</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>2 = Longitudinal/time-lagged</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>1 = No (domestic only)</t>
+        </is>
+      </c>
+      <c r="V22" t="n">
+        <v>292</v>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>High-tech park employees</t>
+        </is>
+      </c>
+      <c r="AA22" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>1 = Self</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>员工的跨界行为 采用的是 Marrone 等(2007) 开发的量表。原量表共 6个条目 , 我们删除了原量表中专门针对样本 (咨询团队 )特点设计的 1个条目 , 所以共 5个条目 , 比如 “我会从团队外部人那里为我们团队寻求建议 ”等。</t>
+        </is>
+      </c>
+      <c r="AH22" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>7</v>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>1 = Self</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>集体主义 采用 Ilies, Wagner 和Morgeson (2007) 使用过的量表 , 共3个条目 , 比如 “比起独自工作来说 , 我更愿意和同事一起工作 ”等。</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>员工跨界行为</t>
+        </is>
+      </c>
+      <c r="AP22" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0.869</v>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>集体主义导向</t>
+        </is>
+      </c>
+      <c r="AT22" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>0.891</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1" s="9">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>BSMA0004</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>BSMA0004.1</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>BSMA0004.1.6</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>1 = Include</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>A Longitudinal Study on the Impact Mechanism of Employees’ Boundary Spanning Behavior: Roles of Centrality and Collectivism</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Acta Psychologica Sinica</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Liu et al.</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>2014</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>1 = Journal article</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>2 = Longitudinal/time-lagged</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>1 = No (domestic only)</t>
+        </is>
+      </c>
+      <c r="V23" t="n">
+        <v>292</v>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>High-tech park employees</t>
+        </is>
+      </c>
+      <c r="AA23" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>1 = Self</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>员工的跨界行为 采用的是 Marrone 等(2007) 开发的量表。原量表共 6个条目 , 我们删除了原量表中专门针对样本 (咨询团队 )特点设计的 1个条目 , 所以共 5个条目 , 比如 “我会从团队外部人那里为我们团队寻求建议 ”等。</t>
+        </is>
+      </c>
+      <c r="AH23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>3 = Others</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>咨询网络中心性 采用的是 Sparrowe 等(2001) 采用的点入中心性 (in-degree centrality, Borgatti, Everett, &amp; Freeman, 1992) 的测量方法。为了收集整体网络数据 , 我们在每个团队中都列上了所有成员的名字 , 然后要求员工对其同事进行评价。量表共 2个条目 , 比如 “你向 (某某 )寻求有关工作的帮助或建议吗 ”。我们关心的是这种关系的强度 (strength), 所以通过 Likert 5 点来进行测量 , 1表示 “从不 ”, 5表示 “总是 ”。</t>
+        </is>
+      </c>
+      <c r="AN23" t="inlineStr">
+        <is>
+          <t>Advice network centrality</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>员工跨界行为</t>
+        </is>
+      </c>
+      <c r="AP23" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0.869</v>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>网络中心性</t>
+        </is>
+      </c>
+      <c r="AT23" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>0.869</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1" s="9">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>BSMA0004</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>BSMA0004.1</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>BSMA0004.1.7</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>1 = Include</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>A Longitudinal Study on the Impact Mechanism of Employees’ Boundary Spanning Behavior: Roles of Centrality and Collectivism</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Acta Psychologica Sinica</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Liu et al.</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>2014</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>1 = Journal article</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>2 = Longitudinal/time-lagged</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>1 = No (domestic only)</t>
+        </is>
+      </c>
+      <c r="V24" t="n">
+        <v>292</v>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>High-tech park employees</t>
+        </is>
+      </c>
+      <c r="AA24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>1 = Self</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>员工的跨界行为 采用的是 Marrone 等(2007) 开发的量表。原量表共 6个条目 , 我们删除了原量表中专门针对样本 (咨询团队 )特点设计的 1个条目 , 所以共 5个条目 , 比如 “我会从团队外部人那里为我们团队寻求建议 ”等。</t>
+        </is>
+      </c>
+      <c r="AH24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>7</v>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>2 = Supervisor</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>任务绩效 采用的是 Liden, Wayne 和Stilwell (1993) 开发的量表 , 共4个条目 , 比如 “这名员工能够充分完成分配的任务 ”等, 由领导填写。</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>员工跨界行为</t>
+        </is>
+      </c>
+      <c r="AP24" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>0.869</v>
+      </c>
+      <c r="AS24" t="inlineStr">
+        <is>
+          <t>任务绩效</t>
+        </is>
+      </c>
+      <c r="AT24" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>0.919</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>0.31</v>
+      </c>
+    </row>
     <row r="25" ht="15.75" customHeight="1" s="9"/>
     <row r="26" ht="15.75" customHeight="1" s="9"/>
     <row r="27" ht="15.75" customHeight="1" s="9"/>

--- a/BSMA_Master_Coding_Sheet.xlsx
+++ b/BSMA_Master_Coding_Sheet.xlsx
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX24"/>
+  <dimension ref="A1:AX18"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.25" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="10.5625" customWidth="1" style="9" min="1" max="2"/>
@@ -2277,7 +2277,6 @@
           <t>集体主义   采用 Ilies, Wagner 和Morgeson (2007) 使用过的量表 , 共3个条目 , 比如 “比起独自工作来说 , 我更愿意和同事一起工作 ”等。在本研究中使用 Likert 7 点测量方法 , 1表示 “非常不同意 ”, 7表示 “非常同意 ”。</t>
         </is>
       </c>
-      <c r="AN16" t="inlineStr"/>
       <c r="AO16" t="inlineStr">
         <is>
           <t>Employee boundary-spanning behavior</t>
@@ -2420,7 +2419,6 @@
           <t>咨询网络中心性   采用的是 Sparrowe 等(2001) 采用的点入中心性 (in-degree centrality, Borgatti, Everett, &amp; Freeman, 1992) 的测量方法。为了收集整体 network 数据 , 我们在每个团队中都列上了所有成员的名字 , 然后要求员工对其同事进行评价。量表共 2个条目 , 比如 “你向 (某某 )寻求有关工作的帮助或建议吗 ”。我们关心的是这种关系的强度 (strength), 所以通过 Likert 5 点来进行测量 , 1表示 “从不 ”, 5表示“总是 ”。所谓点入中心性是相对于点出中心性 (out-degree centrality, 员工本人评价的与自己其他成员的关系 )而言的 , 指的是每个员工来自团队中其他成员评价的网络地位的均值。</t>
         </is>
       </c>
-      <c r="AN17" t="inlineStr"/>
       <c r="AO17" t="inlineStr">
         <is>
           <t>Employee boundary-spanning behavior</t>
@@ -2563,7 +2561,6 @@
           <t>任务绩效  采用的是 Liden, Wayne 和Stilwell (1993) 开发的量表 , 共4个条目 , 比如 “这名员工能够充分完成分配的任务 ”等, 由领导填写。在本研究中使用 Likert7 点测量方法 , 1表示 “非常不同意 ”, 7表示 “非常同意 ”。</t>
         </is>
       </c>
-      <c r="AN18" t="inlineStr"/>
       <c r="AO18" t="inlineStr">
         <is>
           <t>Employee boundary-spanning behavior</t>
@@ -2596,842 +2593,12 @@
         <v>0.31</v>
       </c>
     </row>
-    <row r="19" ht="15.75" customHeight="1" s="9">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>KY</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>BSMA0004</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>BSMA0004.1</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>BSMA0004.1.2</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>1 = Include</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>A Longitudinal Study on the Impact Mechanism of Employees’ Boundary Spanning Behavior: Roles of Centrality and Collectivism</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Acta Psychologica Sinica</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Liu et al.</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>2014</v>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>1 = Journal article</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>2 = Longitudinal/time-lagged</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>1 = No (domestic only)</t>
-        </is>
-      </c>
-      <c r="V19" t="n">
-        <v>292</v>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>High-tech park employees</t>
-        </is>
-      </c>
-      <c r="AA19" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>1 = Self</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>员工的跨界行为 采用的是 Marrone 等(2007) 开发的量表。原量表共 6个条目 , 我们删除了原量表中专门针对样本 (咨询团队 )特点设计的 1个条目 , 所以共 5个条目 , 比如 “我会从团队外部人那里为我们团队寻求建议 ”等。</t>
-        </is>
-      </c>
-      <c r="AH19" t="n">
-        <v>999</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>999</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>999</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>999</v>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>999</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>1 = male, 0 = female</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>员工跨界行为</t>
-        </is>
-      </c>
-      <c r="AP19" t="n">
-        <v>4.98</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>0.869</v>
-      </c>
-      <c r="AS19" t="inlineStr">
-        <is>
-          <t>员工性别</t>
-        </is>
-      </c>
-      <c r="AT19" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>999</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>-0.06</v>
-      </c>
-    </row>
-    <row r="20" ht="15.75" customHeight="1" s="9">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>KY</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>BSMA0004</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>BSMA0004.1</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>BSMA0004.1.3</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>1 = Include</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>A Longitudinal Study on the Impact Mechanism of Employees’ Boundary Spanning Behavior: Roles of Centrality and Collectivism</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Acta Psychologica Sinica</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Liu et al.</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>2014</v>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>1 = Journal article</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>2 = Longitudinal/time-lagged</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>1 = No (domestic only)</t>
-        </is>
-      </c>
-      <c r="V20" t="n">
-        <v>292</v>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>High-tech park employees</t>
-        </is>
-      </c>
-      <c r="AA20" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD20" t="inlineStr">
-        <is>
-          <t>1 = Self</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>员工的跨界行为 采用的是 Marrone 等(2007) 开发的量表。原量表共 6个条目 , 我们删除了原量表中专门针对样本 (咨询团队 )特点设计的 1个条目 , 所以共 5个条目 , 比如 “我会从团队外部人那里为我们团队寻求建议 ”等。</t>
-        </is>
-      </c>
-      <c r="AH20" t="n">
-        <v>999</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>999</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>999</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>999</v>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>999</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>1 (high school and below) to 6 (doctoral degree)</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>员工跨界行为</t>
-        </is>
-      </c>
-      <c r="AP20" t="n">
-        <v>4.98</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>0.869</v>
-      </c>
-      <c r="AS20" t="inlineStr">
-        <is>
-          <t>教育程度</t>
-        </is>
-      </c>
-      <c r="AT20" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>999</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1" s="9">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>KY</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>BSMA0004</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>BSMA0004.1</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>BSMA0004.1.4</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>1 = Include</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>A Longitudinal Study on the Impact Mechanism of Employees’ Boundary Spanning Behavior: Roles of Centrality and Collectivism</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Acta Psychologica Sinica</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Liu et al.</t>
-        </is>
-      </c>
-      <c r="K21" t="n">
-        <v>2014</v>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>1 = Journal article</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>2 = Longitudinal/time-lagged</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>1 = No (domestic only)</t>
-        </is>
-      </c>
-      <c r="V21" t="n">
-        <v>292</v>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>High-tech park employees</t>
-        </is>
-      </c>
-      <c r="AA21" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD21" t="inlineStr">
-        <is>
-          <t>1 = Self</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>员工的跨界行为 采用的是 Marrone 等(2007) 开发的量表。原量表共 6个条目 , 我们删除了原量表中专门针对样本 (咨询团队 )特点设计的 1个条目 , 所以共 5个条目 , 比如 “我会从团队外部人那里为我们团队寻求建议 ”等。</t>
-        </is>
-      </c>
-      <c r="AH21" t="n">
-        <v>999</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>999</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>999</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>999</v>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>999</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>Months</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>员工跨界行为</t>
-        </is>
-      </c>
-      <c r="AP21" t="n">
-        <v>4.98</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>0.869</v>
-      </c>
-      <c r="AS21" t="inlineStr">
-        <is>
-          <t>本团队工作时间</t>
-        </is>
-      </c>
-      <c r="AT21" t="n">
-        <v>20.64</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>18.47</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>999</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="22" ht="15.75" customHeight="1" s="9">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>KY</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>BSMA0004</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>BSMA0004.1</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>BSMA0004.1.5</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>1 = Include</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>A Longitudinal Study on the Impact Mechanism of Employees’ Boundary Spanning Behavior: Roles of Centrality and Collectivism</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Acta Psychologica Sinica</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Liu et al.</t>
-        </is>
-      </c>
-      <c r="K22" t="n">
-        <v>2014</v>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>1 = Journal article</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>2 = Longitudinal/time-lagged</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>1 = No (domestic only)</t>
-        </is>
-      </c>
-      <c r="V22" t="n">
-        <v>292</v>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>High-tech park employees</t>
-        </is>
-      </c>
-      <c r="AA22" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD22" t="inlineStr">
-        <is>
-          <t>1 = Self</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>员工的跨界行为 采用的是 Marrone 等(2007) 开发的量表。原量表共 6个条目 , 我们删除了原量表中专门针对样本 (咨询团队 )特点设计的 1个条目 , 所以共 5个条目 , 比如 “我会从团队外部人那里为我们团队寻求建议 ”等。</t>
-        </is>
-      </c>
-      <c r="AH22" t="n">
-        <v>3</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>7</v>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>1 = Self</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>集体主义 采用 Ilies, Wagner 和Morgeson (2007) 使用过的量表 , 共3个条目 , 比如 “比起独自工作来说 , 我更愿意和同事一起工作 ”等。</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>员工跨界行为</t>
-        </is>
-      </c>
-      <c r="AP22" t="n">
-        <v>4.98</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>0.869</v>
-      </c>
-      <c r="AS22" t="inlineStr">
-        <is>
-          <t>集体主义导向</t>
-        </is>
-      </c>
-      <c r="AT22" t="n">
-        <v>5.84</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>0.891</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="23" ht="15.75" customHeight="1" s="9">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>KY</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>BSMA0004</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>BSMA0004.1</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>BSMA0004.1.6</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>1 = Include</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>A Longitudinal Study on the Impact Mechanism of Employees’ Boundary Spanning Behavior: Roles of Centrality and Collectivism</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Acta Psychologica Sinica</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Liu et al.</t>
-        </is>
-      </c>
-      <c r="K23" t="n">
-        <v>2014</v>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>1 = Journal article</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>2 = Longitudinal/time-lagged</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>1 = No (domestic only)</t>
-        </is>
-      </c>
-      <c r="V23" t="n">
-        <v>292</v>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>High-tech park employees</t>
-        </is>
-      </c>
-      <c r="AA23" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD23" t="inlineStr">
-        <is>
-          <t>1 = Self</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>员工的跨界行为 采用的是 Marrone 等(2007) 开发的量表。原量表共 6个条目 , 我们删除了原量表中专门针对样本 (咨询团队 )特点设计的 1个条目 , 所以共 5个条目 , 比如 “我会从团队外部人那里为我们团队寻求建议 ”等。</t>
-        </is>
-      </c>
-      <c r="AH23" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>5</v>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>3 = Others</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>咨询网络中心性 采用的是 Sparrowe 等(2001) 采用的点入中心性 (in-degree centrality, Borgatti, Everett, &amp; Freeman, 1992) 的测量方法。为了收集整体网络数据 , 我们在每个团队中都列上了所有成员的名字 , 然后要求员工对其同事进行评价。量表共 2个条目 , 比如 “你向 (某某 )寻求有关工作的帮助或建议吗 ”。我们关心的是这种关系的强度 (strength), 所以通过 Likert 5 点来进行测量 , 1表示 “从不 ”, 5表示 “总是 ”。</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>Advice network centrality</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>员工跨界行为</t>
-        </is>
-      </c>
-      <c r="AP23" t="n">
-        <v>4.98</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>0.869</v>
-      </c>
-      <c r="AS23" t="inlineStr">
-        <is>
-          <t>网络中心性</t>
-        </is>
-      </c>
-      <c r="AT23" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>0.869</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>0.27</v>
-      </c>
-    </row>
-    <row r="24" ht="15.75" customHeight="1" s="9">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>KY</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>BSMA0004</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>BSMA0004.1</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>BSMA0004.1.7</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>1 = Include</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>A Longitudinal Study on the Impact Mechanism of Employees’ Boundary Spanning Behavior: Roles of Centrality and Collectivism</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Acta Psychologica Sinica</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Liu et al.</t>
-        </is>
-      </c>
-      <c r="K24" t="n">
-        <v>2014</v>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>1 = Journal article</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>2 = Longitudinal/time-lagged</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>1 = No (domestic only)</t>
-        </is>
-      </c>
-      <c r="V24" t="n">
-        <v>292</v>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>High-tech park employees</t>
-        </is>
-      </c>
-      <c r="AA24" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD24" t="inlineStr">
-        <is>
-          <t>1 = Self</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr">
-        <is>
-          <t>员工的跨界行为 采用的是 Marrone 等(2007) 开发的量表。原量表共 6个条目 , 我们删除了原量表中专门针对样本 (咨询团队 )特点设计的 1个条目 , 所以共 5个条目 , 比如 “我会从团队外部人那里为我们团队寻求建议 ”等。</t>
-        </is>
-      </c>
-      <c r="AH24" t="n">
-        <v>4</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>7</v>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>2 = Supervisor</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>任务绩效 采用的是 Liden, Wayne 和Stilwell (1993) 开发的量表 , 共4个条目 , 比如 “这名员工能够充分完成分配的任务 ”等, 由领导填写。</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>员工跨界行为</t>
-        </is>
-      </c>
-      <c r="AP24" t="n">
-        <v>4.98</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>0.869</v>
-      </c>
-      <c r="AS24" t="inlineStr">
-        <is>
-          <t>任务绩效</t>
-        </is>
-      </c>
-      <c r="AT24" t="n">
-        <v>5.57</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>0.919</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>0.31</v>
-      </c>
-    </row>
+    <row r="19" ht="15.75" customHeight="1" s="9"/>
+    <row r="20" ht="15.75" customHeight="1" s="9"/>
+    <row r="21" ht="15.75" customHeight="1" s="9"/>
+    <row r="22" ht="15.75" customHeight="1" s="9"/>
+    <row r="23" ht="15.75" customHeight="1" s="9"/>
+    <row r="24" ht="15.75" customHeight="1" s="9"/>
     <row r="25" ht="15.75" customHeight="1" s="9"/>
     <row r="26" ht="15.75" customHeight="1" s="9"/>
     <row r="27" ht="15.75" customHeight="1" s="9"/>

--- a/BSMA_Master_Coding_Sheet.xlsx
+++ b/BSMA_Master_Coding_Sheet.xlsx
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX18"/>
+  <dimension ref="A1:AX11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.25" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="10.5625" customWidth="1" style="9" min="1" max="2"/>
@@ -1579,1020 +1579,13 @@
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1" s="9"/>
-    <row r="12" ht="15.75" customHeight="1" s="9">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>KY</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>BSMA0004</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>BSMA0004.1</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>BSMA0004.1.1</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>1 = Include</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>A Longitudinal Study on the Impact Mechanism of Employees’ Boundary Spanning Behavior: Roles of Centrality and Collectivism</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Acta Psychologica Sinica</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>LIU Songbo &amp; LI Yuhui</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>2014</v>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>1 = Journal article</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>2 = Longitudinal/time-lagged</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>1 = No (domestic only)</t>
-        </is>
-      </c>
-      <c r="V12" t="n">
-        <v>292</v>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>employees from high-tech enterprises</t>
-        </is>
-      </c>
-      <c r="AA12" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD12" t="inlineStr">
-        <is>
-          <t>1 = Self</t>
-        </is>
-      </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>采用的是 Marrone 等(2007)开发的量表。原量表共 6个条目 , 我们删除了原量表中专门针对样本 (咨询团队 )特点设计的 1个条目 , 所以共 5个条目 , 比如 “我会从团队外部人那里为我们团队寻求建议 ”等。</t>
-        </is>
-      </c>
-      <c r="AG12" t="inlineStr">
-        <is>
-          <t>5 items adapted from Marrone et al. (2007) 6-item scale, 1 item deleted</t>
-        </is>
-      </c>
-      <c r="AH12" t="n">
-        <v>999</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>999</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>999</v>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>1 = Self</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>999</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>Years</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Employee boundary-spanning behavior</t>
-        </is>
-      </c>
-      <c r="AP12" t="n">
-        <v>4.98</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>0.869</v>
-      </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>Employee Age</t>
-        </is>
-      </c>
-      <c r="AT12" t="n">
-        <v>28.74</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>5.43</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>999</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>-0.08</v>
-      </c>
-    </row>
-    <row r="13" ht="15.75" customHeight="1" s="9">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>KY</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>BSMA0004</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>BSMA0004.1</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>BSMA0004.1.2</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>1 = Include</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>A Longitudinal Study on the Impact Mechanism of Employees’ Boundary Spanning Behavior: Roles of Centrality and Collectivism</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Acta Psychologica Sinica</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>LIU Songbo &amp; LI Yuhui</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>2014</v>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>1 = Journal article</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>2 = Longitudinal/time-lagged</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>1 = No (domestic only)</t>
-        </is>
-      </c>
-      <c r="V13" t="n">
-        <v>292</v>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>employees from high-tech enterprises</t>
-        </is>
-      </c>
-      <c r="AA13" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>1 = Self</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>采用的是 Marrone 等(2007)开发的量表。原量表共 6个条目 , 我们删除了原量表中专门针对样本 (咨询团队 )特点设计的 1个条目 , 所以共 5个条目 , 比如 “我会从团队外部人那里为我们团队寻求建议 ”等。</t>
-        </is>
-      </c>
-      <c r="AG13" t="inlineStr">
-        <is>
-          <t>5 items adapted from Marrone et al. (2007) 6-item scale, 1 item deleted</t>
-        </is>
-      </c>
-      <c r="AH13" t="n">
-        <v>999</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>999</v>
-      </c>
-      <c r="AJ13" t="n">
-        <v>999</v>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>1 = Self</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>999</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>0 = Female, 1 = Male</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Employee boundary-spanning behavior</t>
-        </is>
-      </c>
-      <c r="AP13" t="n">
-        <v>4.98</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>0.869</v>
-      </c>
-      <c r="AS13" t="inlineStr">
-        <is>
-          <t>Employee Gender</t>
-        </is>
-      </c>
-      <c r="AT13" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>999</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>-0.06</v>
-      </c>
-    </row>
-    <row r="14" ht="15.75" customHeight="1" s="9">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>KY</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>BSMA0004</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>BSMA0004.1</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>BSMA0004.1.3</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>1 = Include</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>A Longitudinal Study on the Impact Mechanism of Employees’ Boundary Spanning Behavior: Roles of Centrality and Collectivism</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Acta Psychologica Sinica</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>LIU Songbo &amp; LI Yuhui</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>2014</v>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>1 = Journal article</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>2 = Longitudinal/time-lagged</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>1 = No (domestic only)</t>
-        </is>
-      </c>
-      <c r="V14" t="n">
-        <v>292</v>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>employees from high-tech enterprises</t>
-        </is>
-      </c>
-      <c r="AA14" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>1 = Self</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>采用的是 Marrone 等(2007)开发的量表。原量表共 6个条目 , 我们删除了原量表中专门针对样本 (咨询团队 )特点设计的 1个条目 , 所以共 5个条目 , 比如 “我会从团队外部人那里为我们团队寻求建议 ”等。</t>
-        </is>
-      </c>
-      <c r="AG14" t="inlineStr">
-        <is>
-          <t>5 items adapted from Marrone et al. (2007) 6-item scale, 1 item deleted</t>
-        </is>
-      </c>
-      <c r="AH14" t="n">
-        <v>999</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>999</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>999</v>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>1 = Self</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>999</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>Coded 1 (High school and below) to 6 (Doctorate)</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Employee boundary-spanning behavior</t>
-        </is>
-      </c>
-      <c r="AP14" t="n">
-        <v>4.98</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>0.869</v>
-      </c>
-      <c r="AS14" t="inlineStr">
-        <is>
-          <t>Employee Education</t>
-        </is>
-      </c>
-      <c r="AT14" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>999</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="15" ht="15.75" customHeight="1" s="9">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>KY</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>BSMA0004</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>BSMA0004.1</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>BSMA0004.1.4</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>1 = Include</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>A Longitudinal Study on the Impact Mechanism of Employees’ Boundary Spanning Behavior: Roles of Centrality and Collectivism</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Acta Psychologica Sinica</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>LIU Songbo &amp; LI Yuhui</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>2014</v>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>1 = Journal article</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>2 = Longitudinal/time-lagged</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>1 = No (domestic only)</t>
-        </is>
-      </c>
-      <c r="V15" t="n">
-        <v>292</v>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>employees from high-tech enterprises</t>
-        </is>
-      </c>
-      <c r="AA15" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>1 = Self</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>采用的是 Marrone 等(2007)开发的量表。原量表共 6个条目 , 我们删除了原量表中专门针对样本 (咨询团队 )特点设计的 1个条目 , 所以共 5个条目 , 比如 “我会从团队外部人那里为我们团队寻求建议 ”等。</t>
-        </is>
-      </c>
-      <c r="AG15" t="inlineStr">
-        <is>
-          <t>5 items adapted from Marrone et al. (2007) 6-item scale, 1 item deleted</t>
-        </is>
-      </c>
-      <c r="AH15" t="n">
-        <v>999</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>999</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>999</v>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>1 = Self</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>999</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>Months</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Employee boundary-spanning behavior</t>
-        </is>
-      </c>
-      <c r="AP15" t="n">
-        <v>4.98</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>0.869</v>
-      </c>
-      <c r="AS15" t="inlineStr">
-        <is>
-          <t>Team Tenure</t>
-        </is>
-      </c>
-      <c r="AT15" t="n">
-        <v>20.64</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>18.47</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>999</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>0.03</v>
-      </c>
-    </row>
-    <row r="16" ht="15.75" customHeight="1" s="9">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>KY</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>BSMA0004</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>BSMA0004.1</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>BSMA0004.1.5</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>1 = Include</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>A Longitudinal Study on the Impact Mechanism of Employees’ Boundary Spanning Behavior: Roles of Centrality and Collectivism</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Acta Psychologica Sinica</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>LIU Songbo &amp; LI Yuhui</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>2014</v>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>1 = Journal article</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>2 = Longitudinal/time-lagged</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>1 = No (domestic only)</t>
-        </is>
-      </c>
-      <c r="V16" t="n">
-        <v>292</v>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>employees from high-tech enterprises</t>
-        </is>
-      </c>
-      <c r="AA16" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>1 = Self</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>采用的是 Marrone 等(2007)开发的量表。原量表共 6个条目 , 我们删除了原量表中专门针对样本 (咨询团队 )特点设计的 1个条目 , 所以共 5个条目 , 比如 “我会从团队外部人那里为我们团队寻求建议 ”等。</t>
-        </is>
-      </c>
-      <c r="AG16" t="inlineStr">
-        <is>
-          <t>5 items adapted from Marrone et al. (2007) 6-item scale, 1 item deleted</t>
-        </is>
-      </c>
-      <c r="AH16" t="n">
-        <v>3</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>7</v>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>1 = Self</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>集体主义   采用 Ilies, Wagner 和Morgeson (2007) 使用过的量表 , 共3个条目 , 比如 “比起独自工作来说 , 我更愿意和同事一起工作 ”等。在本研究中使用 Likert 7 点测量方法 , 1表示 “非常不同意 ”, 7表示 “非常同意 ”。</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Employee boundary-spanning behavior</t>
-        </is>
-      </c>
-      <c r="AP16" t="n">
-        <v>4.98</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>0.869</v>
-      </c>
-      <c r="AS16" t="inlineStr">
-        <is>
-          <t>Collectivism orientation</t>
-        </is>
-      </c>
-      <c r="AT16" t="n">
-        <v>5.84</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>0.891</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="17" ht="15.75" customHeight="1" s="9">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>KY</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>BSMA0004</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>BSMA0004.1</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>BSMA0004.1.6</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>1 = Include</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>A Longitudinal Study on the Impact Mechanism of Employees’ Boundary Spanning Behavior: Roles of Centrality and Collectivism</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Acta Psychologica Sinica</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>LIU Songbo &amp; LI Yuhui</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>2014</v>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>1 = Journal article</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>2 = Longitudinal/time-lagged</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>1 = No (domestic only)</t>
-        </is>
-      </c>
-      <c r="V17" t="n">
-        <v>292</v>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>employees from high-tech enterprises</t>
-        </is>
-      </c>
-      <c r="AA17" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>1 = Self</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>采用的是 Marrone 等(2007)开发的量表。原量表共 6个条目 , 我们删除了原量表中专门针对样本 (咨询团队 )特点设计的 1个条目 , 所以共 5个条目 , 比如 “我会从团队外部人那里为我们团队寻求建议 ”等。</t>
-        </is>
-      </c>
-      <c r="AG17" t="inlineStr">
-        <is>
-          <t>5 items adapted from Marrone et al. (2007) 6-item scale, 1 item deleted</t>
-        </is>
-      </c>
-      <c r="AH17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>5</v>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>3 = Others</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>咨询网络中心性   采用的是 Sparrowe 等(2001) 采用的点入中心性 (in-degree centrality, Borgatti, Everett, &amp; Freeman, 1992) 的测量方法。为了收集整体 network 数据 , 我们在每个团队中都列上了所有成员的名字 , 然后要求员工对其同事进行评价。量表共 2个条目 , 比如 “你向 (某某 )寻求有关工作的帮助或建议吗 ”。我们关心的是这种关系的强度 (strength), 所以通过 Likert 5 点来进行测量 , 1表示 “从不 ”, 5表示“总是 ”。所谓点入中心性是相对于点出中心性 (out-degree centrality, 员工本人评价的与自己其他成员的关系 )而言的 , 指的是每个员工来自团队中其他成员评价的网络地位的均值。</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Employee boundary-spanning behavior</t>
-        </is>
-      </c>
-      <c r="AP17" t="n">
-        <v>4.98</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>0.869</v>
-      </c>
-      <c r="AS17" t="inlineStr">
-        <is>
-          <t>Advice network centrality</t>
-        </is>
-      </c>
-      <c r="AT17" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>0.869</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>0.27</v>
-      </c>
-    </row>
-    <row r="18" ht="15.75" customHeight="1" s="9">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>KY</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>BSMA0004</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>BSMA0004.1</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>BSMA0004.1.7</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>1 = Include</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>A Longitudinal Study on the Impact Mechanism of Employees’ Boundary Spanning Behavior: Roles of Centrality and Collectivism</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Acta Psychologica Sinica</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>LIU Songbo &amp; LI Yuhui</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>2014</v>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>1 = Journal article</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>2 = Longitudinal/time-lagged</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>1 = No (domestic only)</t>
-        </is>
-      </c>
-      <c r="V18" t="n">
-        <v>292</v>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>employees from high-tech enterprises</t>
-        </is>
-      </c>
-      <c r="AA18" t="n">
-        <v>5</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>1 = Self</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>采用的是 Marrone 等(2007)开发的量表。原量表共 6个条目 , 我们删除了原量表中专门针对样本 (咨询团队 )特点设计的 1个条目 , 所以共 5个条目 , 比如 “我会从团队外部人那里为我们团队寻求建议 ”等。</t>
-        </is>
-      </c>
-      <c r="AG18" t="inlineStr">
-        <is>
-          <t>5 items adapted from Marrone et al. (2007) 6-item scale, 1 item deleted</t>
-        </is>
-      </c>
-      <c r="AH18" t="n">
-        <v>4</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>7</v>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>2 = Supervisor</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>任务绩效  采用的是 Liden, Wayne 和Stilwell (1993) 开发的量表 , 共4个条目 , 比如 “这名员工能够充分完成分配的任务 ”等, 由领导填写。在本研究中使用 Likert7 点测量方法 , 1表示 “非常不同意 ”, 7表示 “非常同意 ”。</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Employee boundary-spanning behavior</t>
-        </is>
-      </c>
-      <c r="AP18" t="n">
-        <v>4.98</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>0.869</v>
-      </c>
-      <c r="AS18" t="inlineStr">
-        <is>
-          <t>Task performance</t>
-        </is>
-      </c>
-      <c r="AT18" t="n">
-        <v>5.57</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>0.8100000000000001</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>0.919</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>0.31</v>
-      </c>
-    </row>
+    <row r="12" ht="15.75" customHeight="1" s="9"/>
+    <row r="13" ht="15.75" customHeight="1" s="9"/>
+    <row r="14" ht="15.75" customHeight="1" s="9"/>
+    <row r="15" ht="15.75" customHeight="1" s="9"/>
+    <row r="16" ht="15.75" customHeight="1" s="9"/>
+    <row r="17" ht="15.75" customHeight="1" s="9"/>
+    <row r="18" ht="15.75" customHeight="1" s="9"/>
     <row r="19" ht="15.75" customHeight="1" s="9"/>
     <row r="20" ht="15.75" customHeight="1" s="9"/>
     <row r="21" ht="15.75" customHeight="1" s="9"/>

--- a/BSMA_Master_Coding_Sheet.xlsx
+++ b/BSMA_Master_Coding_Sheet.xlsx
@@ -982,7 +982,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Firm-level boundary spanning (Precedent #002): Focal spanner is the firm, not an individual.</t>
+          <t>99 = Other (specify in Notes)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1002,6 +1002,11 @@
       </c>
       <c r="K6" t="n">
         <v>2025</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Firm-level boundary spanning (not individual-level). Focal spanner is the firm.</t>
+        </is>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1" s="9"/>
@@ -1023,7 +1028,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Team-level boundary spanning: Focal spanner is the team (N=49 interorganizational teams), not an individual.</t>
+          <t>99 = Other (specify in Notes)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1043,6 +1048,11 @@
       </c>
       <c r="K8" t="n">
         <v>2011</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Team-level boundary spanning (not individual-level). Focal spanner is the team (N=49).</t>
+        </is>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1" s="9"/>
